--- a/exports/master_sheet.xlsx
+++ b/exports/master_sheet.xlsx
@@ -433,7 +433,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q9"/>
+  <dimension ref="A1:Q129"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -553,50 +553,31 @@
           <t>No</t>
         </is>
       </c>
-      <c r="C2" s="2" t="inlineStr">
-        <is>
-          <t>Infectious Disease</t>
-        </is>
-      </c>
+      <c r="C2" s="2" t="inlineStr"/>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>Multidrug Resistant Falciparum Malaria Treatment Strategy</t>
+          <t>2022 Pakistan Flooding</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Both claims share the same epistemic source and signal a **layered resistance-mitigation doctrine**:
-- **Claim 1** operates at the *policy/system level* — diversifying the first-line treatment portfolio to reduce selective pressure from any single regimen across a population.
-- **Claim 2** operates at the *patient/regimen level* — adding a third active drug to overwhelm parasites with partial resistance to artemisinin or its partner drug.
-Together they form a coherent escalation logic:
-&gt; Artemisinin partial resistance → ACT partner drug resistance → neither monotherapy nor dual ACT sufficient → deploy TDC *and* rotate multiple first-line options across endemic settings.
----</t>
+          <t>Entity misclassified. "2022 Pakistan flooding" is a climate/disaster event, not a drug, biologic, or therapeutic agent. Current claim corpus links event to [[plasmodium-vivax]] malaria outbreak in [[pakistan]] [c:2b54307f] (pending review) [c:83021500] (pending review). Reclassify entity as `event` or `epidemiologic-determinant`. No medication note can be authored from this corpus.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr"/>
       <c r="G2" s="2" t="inlineStr"/>
-      <c r="H2" s="2" t="inlineStr"/>
+      <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t>_Not applicable._ For epidemiologic mechanism: flooding → vector habitat expansion → [[anopheles]] proliferation → [[plasmodium-vivax]] transmission surge in endemic setting [c:2b54307f] (pending review, expert_opinion) [c:83021500] (pending review, expert_opinion). Belongs in event/determinant note, not medication note.</t>
+        </is>
+      </c>
       <c r="I2" s="2" t="inlineStr"/>
       <c r="J2" s="2" t="inlineStr"/>
       <c r="K2" s="2" t="inlineStr"/>
       <c r="L2" s="2" t="inlineStr"/>
-      <c r="M2" s="2" t="inlineStr">
-        <is>
-          <t>**Source:** PMID:34267045 | *Artemisinin and multidrug-resistant Plasmodium falciparum — a threat for malaria control and elimination.*
----</t>
-        </is>
-      </c>
+      <c r="M2" s="2" t="inlineStr"/>
       <c r="N2" s="2" t="inlineStr"/>
-      <c r="O2" s="2" t="inlineStr">
-        <is>
-          <t>Both claims share the same epistemic source and signal a **layered resistance-mitigation doctrine**:
-- **Claim 1** operates at the *policy/system level* — diversifying the first-line treatment portfolio to reduce selective pressure from any single regimen across a population.
-- **Claim 2** operates at the *patient/regimen level* — adding a third active drug to overwhelm parasites with partial resistance to artemisinin or its partner drug.
-Together they form a coherent escalation logic:
-&gt; Artemisinin partial resistance → ACT partner drug resistance → neither monotherapy nor dual ACT sufficient → deploy TDC *and* rotate multiple first-line options across endemic settings.
----</t>
-        </is>
-      </c>
+      <c r="O2" s="2" t="inlineStr"/>
       <c r="P2" s="2" t="inlineStr"/>
       <c r="Q2" s="2" t="inlineStr"/>
     </row>
@@ -611,45 +592,26 @@
           <t>No</t>
         </is>
       </c>
-      <c r="C3" s="2" t="inlineStr">
-        <is>
-          <t>Infectious Disease</t>
-        </is>
-      </c>
+      <c r="C3" s="2" t="inlineStr"/>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>P Falciparum Parasites</t>
+          <t>8 Aminoquinolines</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>PfCRT (Plasmodium falciparum Chloroquine Resistance Transporter) mutations confer cross-resistance across three clinically important antimalarials: **chloroquine**, **amodiaquine**, and **piperaquine**. All three claims share identical evidence provenance and certainty tier.
----</t>
+          <t>Class of antimalarial agents targeting dormant liver-stage parasites ([[plasmodium-vivax]] and [[plasmodium-ovale]] [[hypnozoites]]). Class entry — individual members (e.g. [[primaquine]], [[tafenoquine]]) carry their own dose, safety, and G6PD-screening detail. Note documents class-level claims only.</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr"/>
       <c r="G3" s="2" t="inlineStr"/>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>PfCRT is a digestive vacuole membrane transporter. Mutations (canonical: K76T, plus haplotype-dependent variants) alter drug efflux, reducing intravacuolar drug accumulation. This single genetic locus therefore undermines multiple drug classes:
-| Drug | Class | Resistance claim |
-|---|---|---|
-| Chloroquine | 4-aminoquinoline | ✓ (69c306c2 vs. wild-type) |
-| Amodiaquine | 4-aminoquinoline | ✓ (6dcc1181 vs. wild-type) |
-| Piperaquine | Bisquinoline | ✓ (6dcc1181... wait — e882169f vs. wild-type) |
-Chloroquine and amodiaquine share structural similarity — cross-resistance expected. Piperaquine resistance via PfCRT is structurally distinct and clinically more alarming: piperaquine is the partner drug in DHA-PPQ (dihydroartemisinin-piperaquine), a frontline ACT.
----</t>
+          <t>8-aminoquinolines act on dormant liver-stage [[hypnozoites]] of [[plasmodium-vivax]], clearing reservoir responsible for relapse [c:e637b70b] _(pending review)_. Hypnozoite kill = mechanism behind relapse prevention in vivax and ovale infection [c:029dc12c] _(pending review)_. Downstream molecular target (oxidative metabolite generation, mitochondrial disruption) not supported by current claim corpus.</t>
         </is>
       </c>
       <c r="I3" s="2" t="inlineStr"/>
-      <c r="J3" s="2" t="inlineStr">
-        <is>
-          <t>- **ACT partner drug compromise:** PfCRT-mutant parasites resisting piperaquine threaten DHA-PPQ efficacy — especially critical given concurrent kelch13-mediated artemisinin partial resistance in Southeast Asia.
-- **4-aminoquinoline ACTs:** CQ and AQ resistance via PfCRT is well-established; ASAQ (artesunate-amodiaquine) remains effective in Africa where PfCRT haplotypes differ from Asian strains.
-- **Regional haplotype dependence:** Effect sizes unspecified in claims; resistance magnitude varies by PfCRT haplotype (e.g., CVIET vs. SVMNT).
----</t>
-        </is>
-      </c>
+      <c r="J3" s="2" t="inlineStr"/>
       <c r="K3" s="2" t="inlineStr"/>
       <c r="L3" s="2" t="inlineStr"/>
       <c r="M3" s="2" t="inlineStr"/>
@@ -669,42 +631,31 @@
           <t>No</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>Infectious Disease</t>
-        </is>
-      </c>
+      <c r="C4" s="2" t="inlineStr"/>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>Plasmodium Falciparum Isolates</t>
+          <t>Adults</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Angola *P. falciparum* isolates in Lubango show low but non-negligible CNV in both *pfmdr1* and *pfpm2* (~9% each). No dominant amplification signal. Continued molecular surveillance warranted as artemisinin-based combination therapy scales.</t>
+          <t>Entity "adults" misclassified as medication. Supplied claims describe parasitic infections in adult populations, not pharmacologic agents. No drug, biologic, or therapeutic agent present in corpus. Note rendered as placeholder; downstream exporter should reroute entity to population/demographic table, not Medications sheet.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr"/>
       <c r="G4" s="2" t="inlineStr"/>
-      <c r="H4" s="2" t="inlineStr"/>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>_No mechanism claims in current corpus._</t>
+        </is>
+      </c>
       <c r="I4" s="2" t="inlineStr"/>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>- **pfmdr1** amplification → reduced sensitivity to **lumefantrine** (artemether-lumefantrine partner drug); also linked to **mefloquine** resistance
-- **pfpm2** amplification → **piperaquine** resistance (dihydroartemisinin-piperaquine failure)
-- Low prevalence suggests current first-line regimens retain efficacy in this population — but not zero pressure
----</t>
-        </is>
-      </c>
+      <c r="J4" s="2" t="inlineStr"/>
       <c r="K4" s="2" t="inlineStr"/>
       <c r="L4" s="2" t="inlineStr"/>
       <c r="M4" s="2" t="inlineStr"/>
       <c r="N4" s="2" t="inlineStr"/>
-      <c r="O4" s="2" t="inlineStr">
-        <is>
-          <t>Angola *P. falciparum* isolates in Lubango show low but non-negligible CNV in both *pfmdr1* and *pfpm2* (~9% each). No dominant amplification signal. Continued molecular surveillance warranted as artemisinin-based combination therapy scales.</t>
-        </is>
-      </c>
+      <c r="O4" s="2" t="inlineStr"/>
       <c r="P4" s="2" t="inlineStr"/>
       <c r="Q4" s="2" t="inlineStr"/>
     </row>
@@ -719,51 +670,41 @@
           <t>No</t>
         </is>
       </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>Infectious Disease</t>
-        </is>
-      </c>
+      <c r="C5" s="2" t="inlineStr"/>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>Plasmodium Falciparum Malaria</t>
+          <t>Adverse Pregnancy Outcomes</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>| Dimension | Summary |
-|-----------|---------|
-| **Treatment** | ACTs = global standard, high certainty |
-| **Resistance** | Partial, spreading — SE Asia origin, now Africa |
-| **Mechanism** | Kelch13 double mutants + Coronin pathway |
-| **Risk** | Next-gen artemisinins also affected (2025 data) |</t>
+          <t>"Adverse pregnancy outcomes" is an outcome cluster (stillbirth, low birth weight, preterm delivery, miscarriage), not a medication. Current claim corpus describes causes (malaria infection, poor gestational weight gain) and preventive pharmacotherapies (IPTp regimens) targeting this outcome in endemic Africa. Note structured per medication template but content reflects entity's true nature.</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr"/>
       <c r="G5" s="2" t="inlineStr"/>
-      <c r="H5" s="2" t="inlineStr"/>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>_Not applicable to entity._ Upstream causal pathways from claim set:
+```mermaid
+graph LR
+  A[Plasmodium infection, 1st trimester] --&gt;|placental sequestration| O[Adverse pregnancy outcomes]
+  B[First-trimester malaria infection] --&gt; O
+  C[Poor gestational weight gain + macronutrient undernutrition] --&gt; O
+  O --&gt; S[Stillbirth / LBW / preterm / miscarriage]
+```
+- [[plasmodium]] infection in first trimester → adverse outcomes; pregnant, endemic setting [c:959870d1].
+- First-trimester [[malaria]] infection → adverse outcomes; endemic setting [c:6cab89a1].
+- Poor gestational weight gain with [[macronutrient-undernutrition]] in 2nd/3rd trimester → adverse outcomes [c:b7940b67].</t>
+        </is>
+      </c>
       <c r="I5" s="2" t="inlineStr"/>
       <c r="J5" s="2" t="inlineStr"/>
       <c r="K5" s="2" t="inlineStr"/>
       <c r="L5" s="2" t="inlineStr"/>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>**Entity:** Plasmodium falciparum malaria
-**Claims synthesized:** 4 | **Date:** 2026-05-09
----</t>
-        </is>
-      </c>
+      <c r="M5" s="2" t="inlineStr"/>
       <c r="N5" s="2" t="inlineStr"/>
-      <c r="O5" s="2" t="inlineStr">
-        <is>
-          <t>| Dimension | Summary |
-|-----------|---------|
-| **Treatment** | ACTs = global standard, high certainty |
-| **Resistance** | Partial, spreading — SE Asia origin, now Africa |
-| **Mechanism** | Kelch13 double mutants + Coronin pathway |
-| **Risk** | Next-gen artemisinins also affected (2025 data) |</t>
-        </is>
-      </c>
+      <c r="O5" s="2" t="inlineStr"/>
       <c r="P5" s="2" t="inlineStr"/>
       <c r="Q5" s="2" t="inlineStr"/>
     </row>
@@ -785,45 +726,31 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>Plasmodium Falciparum</t>
+          <t>Airport Malaria</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>```
-P. falciparum resistance network
-│
-├── Artemisinin partial resistance
-│   ├── PRIMARY: k13 mutations (C580Y dominant in SEA)
-│   │   └── AMPLIFIED BY: fd-D193Y + arps10-V127M co-mutations
-│   └── SPREADING: SEA → East Africa
-│
-├── Piperaquine resistance (Cambodia)
-│   ├── Plasmepsin II/III copy number ↑
-│   └── CRT mutations
-│       → Combined: DHA-PPQ ACT failure
-│
-└── Legacy resistance
-    ├── Chloroquine (PNG, widespread globally)
-    └── Azithromycin (intrinsically low activity)
-```
----</t>
+          <t>Airport malaria = locally-acquired malaria in [[non-endemic-region|non-endemic regions]] caused by infected mosquitoes transported via aircraft from endemic zones. France reported ~30 cases since 1969, predominantly [[plasmodium-falciparum|*Plasmodium falciparum*]] in immune-[[naive-host|naive]] hosts [c:0837df50] (pending review). Disease requires compulsory notification in France [c:0f1e0407] (pending review).</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr"/>
       <c r="G6" s="2" t="inlineStr"/>
-      <c r="H6" s="2" t="inlineStr"/>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>_Not pharmacological._ Transmission mechanism:
+```mermaid
+flowchart LR
+  A[Infected Anopheles transported in aircraft] --&gt; B[Mosquito escapes near airport]
+  B --&gt; C[Bites naive local host within flight range]
+  C --&gt; D[P. falciparum sporozoite inoculation]
+  D --&gt; E[Clinical malaria in non-endemic region]
+```
+*P. falciparum* identified as causative species in French reported cases, immune-naive population [c:0837df50] (pending review).</t>
+        </is>
+      </c>
       <c r="I6" s="2" t="inlineStr"/>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>1. **Southeast Asia:** DHA-PPQ is compromised by dual k13 + plasmepsin/CRT resistance. Triple ACTs or alternative partners needed.
-2. **Africa:** Artemisinin partial resistance spreading. AL still functional but margin narrowing in Uganda hotspots.
-3. **PNG:** CQ-resistant baseline; azithromycin not viable. ACT selection critical.
-4. **Molecular surveillance priority:** k13, plasmepsin II/III copy number, CRT genotyping must expand beyond SEA sentinel sites into high-burden Africa.
----
-*Sources: 10 unique PMIDs. All claims status: pending\_review.*</t>
-        </is>
-      </c>
+      <c r="J6" s="2" t="inlineStr"/>
       <c r="K6" s="2" t="inlineStr"/>
       <c r="L6" s="2" t="inlineStr"/>
       <c r="M6" s="2" t="inlineStr"/>
@@ -843,45 +770,39 @@
           <t>No</t>
         </is>
       </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>Infectious Disease</t>
-        </is>
-      </c>
+      <c r="C7" s="2" t="inlineStr"/>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>Severe Plasmodium Falciparum Malaria</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr"/>
+          <t>Anaemia</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>Entity classifier flagged `anaemia` as medication, but anaemia is a haematologic condition (reduced haemoglobin / red-cell mass), commonly secondary to malaria in endemic sub-Saharan Africa. Current corpus contains no pharmacologic claims for anaemia itself — all 4 claims describe [[indoor-residual-spraying]] (vector control) as upstream prevention of anaemia in [[itn]]-using communities. Note retained as stub pending re-classification.</t>
+        </is>
+      </c>
       <c r="F7" s="2" t="inlineStr"/>
       <c r="G7" s="2" t="inlineStr"/>
-      <c r="H7" s="2" t="inlineStr"/>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>_No mechanism-of-action claims in current corpus._ Anaemia is a downstream outcome, not an agent. Vector-control claims act upstream by reducing [[plasmodium-falciparum]] transmission → fewer infections → less haemolysis and dyserythropoiesis → lower anaemia prevalence.
+```mermaid
+flowchart LR
+  A[IRS insecticide] --&gt; B[Vector mortality]
+  B --&gt; C[Reduced P. falciparum transmission]
+  C --&gt; D[Fewer malaria infections]
+  D --&gt; E[Less haemolysis/dyserythropoiesis]
+  E --&gt; F[Lower anaemia prevalence]
+```
+Cascade supported by meta-analytic risk ratios on anaemia endpoint [c:c0de6166] [c:d61b7e6d].</t>
+        </is>
+      </c>
       <c r="I7" s="2" t="inlineStr"/>
       <c r="J7" s="2" t="inlineStr"/>
       <c r="K7" s="2" t="inlineStr"/>
       <c r="L7" s="2" t="inlineStr"/>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>**Core finding:** IV artesunate and artemisinin-based combination regimens are first-line inpatient treatment for severe *P. falciparum* malaria.
-| Agent | Setting | Population | Certainty | Evidence grade |
-|---|---|---|---|---|
-| IV artesunate | Inpatient | General | High | Expert opinion |
-| Artemisinin-based regimens | Inpatient, endemic | Sub-Saharan Africa | High | Expert opinion |
-Both claims share high certainty but rest on expert opinion — no RCT-level quantitative effect sizes captured yet.
----</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>Both claims `pending_review`. Recommend:
-1. Add resistance-context qualifier (partial artemisinin resistance) to both
-2. Link claims via shared `supersedes` chain if resistance data changes efficacy assertion
-3. Upgrade evidence grade if WHO treatment guideline sources available
----
-**Sources:** [PMID:38321292](https://pubmed.ncbi.nlm.nih.gov/38321292/) · [PMID:38552654](https://pubmed.ncbi.nlm.nih.gov/38552654/)</t>
-        </is>
-      </c>
+      <c r="M7" s="2" t="inlineStr"/>
+      <c r="N7" s="2" t="inlineStr"/>
       <c r="O7" s="2" t="inlineStr"/>
       <c r="P7" s="2" t="inlineStr"/>
       <c r="Q7" s="2" t="inlineStr"/>
@@ -897,37 +818,39 @@
           <t>No</t>
         </is>
       </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>Infectious Disease</t>
-        </is>
-      </c>
+      <c r="C8" s="2" t="inlineStr"/>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>Uncomplicated Falciparum Malaria</t>
+          <t>Anemia</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>**Artemisinin-based combination therapies (ACTs) treat uncomplicated falciparum malaria.**
-Both claims converge on this single assertion with **high certainty**, sourced from two independent PubMed publications (PMID:34452235, PMID:34267045).
----</t>
+          <t>Entity classified as `medication` but corpus claims describe anemia as **clinical condition** caused by malaria infection [c:db0a2531] (pending review). No pharmacologic claims present. Note retained in medication template per schema; therapeutic fields marked N/A.</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr"/>
       <c r="G8" s="2" t="inlineStr"/>
-      <c r="H8" s="2" t="inlineStr"/>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>_Not applicable to a condition._ Pathogenesis of malarial anemia per corpus:
+```mermaid
+flowchart TD
+  A[Plasmodium infection] --&gt; B[RBC destruction + splenic clearance]
+  C[Splenic accumulation of uninfected RBCs] --&gt; D[Anemia in vivax malaria]
+  A --&gt; C
+  E[Recurrent/chronic P. vivax] --&gt; D
+```
+Splenic accumulation of uninfected red cells drives anemia in [[vivax-malaria]] [c:b421f4fd][c:d359e581] (pending review). Recurrence/chronicity amplifies effect in endemic settings [c:12988f90] (pending review).</t>
+        </is>
+      </c>
       <c r="I8" s="2" t="inlineStr"/>
       <c r="J8" s="2" t="inlineStr"/>
       <c r="K8" s="2" t="inlineStr"/>
       <c r="L8" s="2" t="inlineStr"/>
       <c r="M8" s="2" t="inlineStr"/>
       <c r="N8" s="2" t="inlineStr"/>
-      <c r="O8" s="2" t="inlineStr">
-        <is>
-          <t>Two claims are **redundant** — same subject/predicate/object, minor qualifier differences (one adds `endemic` setting, other adds `outpatient` + `global`). Merge candidate. Neither supersedes the other (`supersedes_id: null`). Recommend deduplication after review.</t>
-        </is>
-      </c>
+      <c r="O8" s="2" t="inlineStr"/>
       <c r="P8" s="2" t="inlineStr"/>
       <c r="Q8" s="2" t="inlineStr"/>
     </row>
@@ -949,32 +872,5671 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>Uncomplicated Plasmodium Falciparum Malaria</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr"/>
+          <t>Anopheles Mosquito</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>*Anopheles* mosquito = arthropod vector of [[plasmodium]] parasites. Female bite transmits [[malaria]] in endemic settings [c:7fc0d7ef]. Field populations show rising insecticide resistance, eroding vector-control programs [c:13a80bce]. Entity misclassified as medication in source corpus — no pharmacologic profile exists. Note retained for schema continuity; clinical actions belong to antimalarials ([[artemether-lumefantrine]], [[primaquine]]) and vector-control tools (ITNs, IRS).</t>
+        </is>
+      </c>
       <c r="F9" s="2" t="inlineStr"/>
       <c r="G9" s="2" t="inlineStr"/>
-      <c r="H9" s="2" t="inlineStr"/>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>Not a drug. Vector mechanism: female *Anopheles* takes blood meal → inoculates *Plasmodium* sporozoites → hepatic then erythrocytic infection → clinical malaria, with mortality burden in endemic settings (pending review) [c:7fc0d7ef].
+```mermaid
+flowchart LR
+  A[Female Anopheles bite] --&gt; B[Sporozoite inoculation]
+  B --&gt; C[Hepatic schizogony]
+  C --&gt; D[Erythrocytic cycle]
+  D --&gt; E[Clinical malaria / death]
+```
+Cascade load-bearing on [c:7fc0d7ef].</t>
+        </is>
+      </c>
       <c r="I9" s="2" t="inlineStr"/>
       <c r="J9" s="2" t="inlineStr"/>
       <c r="K9" s="2" t="inlineStr"/>
       <c r="L9" s="2" t="inlineStr"/>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>**Entity:** Uncomplicated *Plasmodium falciparum* malaria
-**Claims synthesized:** 4 | **Sources:** 3 PMIDs | **Date:** 2026-05-09
----</t>
-        </is>
-      </c>
-      <c r="N9" s="2" t="inlineStr">
-        <is>
-          <t>All 4 claims: `pending_review` — confirm before pipeline promotion.</t>
-        </is>
-      </c>
+      <c r="M9" s="2" t="inlineStr"/>
+      <c r="N9" s="2" t="inlineStr"/>
       <c r="O9" s="2" t="inlineStr"/>
       <c r="P9" s="2" t="inlineStr"/>
       <c r="Q9" s="2" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>Infectious Disease</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>Anopheles Mosquitoes</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>Anopheles mosquitoes are the dipteran vectors of human malaria, not a medication. 465 recognised Anopheles species exist, of which ~41 are dominant vectors transmitting *Plasmodium spp.* across 87 endemic countries [c:72fb278e] [c:bbf3cd0d] [c:ac4b29da]. Entry listed under "medication" only because vector-control targets (insecticides) and resistance patterns intersect drug/chemical-class records.</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr"/>
+      <c r="G10" s="2" t="inlineStr"/>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>Vector biology, not pharmacology. Female Anopheles takes blood meal, ingests gametocytes, sporogony in mosquito, sporozoites injected at next bite — transmits [[plasmodium-spp]] to humans [c:bbf3cd0d] [c:8715ee0c].
+```mermaid
+graph LR
+  A[Anopheles bite] --&gt; B[Sporozoite inoculation]
+  B --&gt; C[Plasmodium spp. infection]
+  C --&gt; D[Human malaria]
+```
+[c:8715ee0c] [c:bbf3cd0d]</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr"/>
+      <c r="J10" s="2" t="inlineStr"/>
+      <c r="K10" s="2" t="inlineStr"/>
+      <c r="L10" s="2" t="inlineStr"/>
+      <c r="M10" s="2" t="inlineStr"/>
+      <c r="N10" s="2" t="inlineStr"/>
+      <c r="O10" s="2" t="inlineStr"/>
+      <c r="P10" s="2" t="inlineStr"/>
+      <c r="Q10" s="2" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>Infectious Disease</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>Antimalarial Drugs</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>Antimalarial drugs treat and prevent infection by *Plasmodium* parasites. Class-level note — individual agents (artemether-lumefantrine, chloroquine, primaquine, atovaquone-proguanil, etc.) carry their own dose, contraindication, and interaction profiles. Use this note as index; defer to agent-specific notes for prescribing.</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr"/>
+      <c r="G11" s="2" t="inlineStr"/>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>Mechanism varies by member agent. No class-level mechanism claim in current corpus. See agent-specific notes ([[artemisinin]], [[chloroquine]], [[primaquine]], [[lumefantrine]]) for target-level detail.</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr"/>
+      <c r="J11" s="2" t="inlineStr"/>
+      <c r="K11" s="2" t="inlineStr"/>
+      <c r="L11" s="2" t="inlineStr"/>
+      <c r="M11" s="2" t="inlineStr"/>
+      <c r="N11" s="2" t="inlineStr"/>
+      <c r="O11" s="2" t="inlineStr"/>
+      <c r="P11" s="2" t="inlineStr"/>
+      <c r="Q11" s="2" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr"/>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>As01 Adjuvanted Vaccine</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>AS01 is liposome-based vaccine adjuvant system combining monophosphoryl lipid A (MPL) and saponin QS-21. Boosts antigen-specific humoral and cellular immune response. Used in licensed vaccines targeting [[herpes-zoster]], [[malaria]], and [[respiratory-syncytial-virus-disease]] (pending review) [c:e87f17fe][c:b826a637][c:bbd5f17e].</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr"/>
+      <c r="G12" s="2" t="inlineStr"/>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>AS01 combines MPL (TLR4 agonist) and QS-21 (saponin) in liposomes. Triggers innate immune activation at injection site, drives antigen-specific CD4+ T cell and antibody response against co-administered antigen. Source claims state preventive effect but do not detail mechanistic cascade — only high-level prevention endpoint documented (expert_opinion grade) [c:e87f17fe][c:b826a637][c:bbd5f17e].</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr"/>
+      <c r="J12" s="2" t="inlineStr"/>
+      <c r="K12" s="2" t="inlineStr"/>
+      <c r="L12" s="2" t="inlineStr"/>
+      <c r="M12" s="2" t="inlineStr"/>
+      <c r="N12" s="2" t="inlineStr"/>
+      <c r="O12" s="2" t="inlineStr"/>
+      <c r="P12" s="2" t="inlineStr"/>
+      <c r="Q12" s="2" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>Infectious Disease</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>Asymptomatic Malaria Infection At Household Survey</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>Entity misclassified as medication. Actually condition: asymptomatic *Plasmodium* infection detected via household survey in [[democratic-republic-of-congo|DRC]], Kinshasa Province. Three species contribute to community prevalence: [[plasmodium-falciparum]] dominant, [[plasmodium-malariae]] and [[plasmodium-ovale]] minor. No therapeutic agent in claim corpus.</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr"/>
+      <c r="G13" s="2" t="inlineStr"/>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>_Not applicable._ No mechanism claims. Entity is infection state, not pharmacologic agent.</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr"/>
+      <c r="J13" s="2" t="inlineStr"/>
+      <c r="K13" s="2" t="inlineStr"/>
+      <c r="L13" s="2" t="inlineStr"/>
+      <c r="M13" s="2" t="inlineStr"/>
+      <c r="N13" s="2" t="inlineStr"/>
+      <c r="O13" s="2" t="inlineStr"/>
+      <c r="P13" s="2" t="inlineStr"/>
+      <c r="Q13" s="2" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr"/>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>Atovaquone Proguanil</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>Atovaquone-proguanil is a fixed-dose oral antimalarial combination (brand [[malarone]]) used for prevention and treatment of [[plasmodium-falciparum]] malaria, including [[chloroquine-resistant-malaria|chloroquine-resistant]] strains. Marketed mainly for travelers from non-endemic regions [c:433f6ee2] [c:f3a7e86f].</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr"/>
+      <c r="G14" s="2" t="inlineStr"/>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>_No mechanism claims in current corpus._ Pharmacology (atovaquone → cytochrome bc1 inhibition; proguanil → dihydrofolate reductase inhibition via cycloguanil metabolite) not surfaced by current claim set.</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr"/>
+      <c r="J14" s="2" t="inlineStr"/>
+      <c r="K14" s="2" t="inlineStr"/>
+      <c r="L14" s="2" t="inlineStr"/>
+      <c r="M14" s="2" t="inlineStr"/>
+      <c r="N14" s="2" t="inlineStr"/>
+      <c r="O14" s="2" t="inlineStr"/>
+      <c r="P14" s="2" t="inlineStr"/>
+      <c r="Q14" s="2" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr"/>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>Azadirachta Indica</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>Azadirachta indica (neem) is a Meliaceae tree whose leaf, bark, and seed extracts are used in traditional medicine across [[sub-saharan-africa]] as an alternative malaria therapy. Current corpus evidence is limited to expert-opinion claims of activity against [[plasmodium-falciparum]] in endemic settings (pending review). No pharmaceutical-grade preparation, standardised active fraction, or validated dose exists in the present claim set.</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr"/>
+      <c r="G15" s="2" t="inlineStr"/>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>Corpus lacks mechanistic claims. Transmission-blocking [c:d7aa14e4] and schizonticidal [c:e3dd6f37] effects asserted at clinical level only; molecular target, gametocytocidal pathway, and active phytochemical (e.g. azadirachtin, nimbolide, gedunin) not characterised in current claim set.
+_No mechanism claims in current corpus beyond clinical-effect assertion._</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr"/>
+      <c r="J15" s="2" t="inlineStr"/>
+      <c r="K15" s="2" t="inlineStr"/>
+      <c r="L15" s="2" t="inlineStr"/>
+      <c r="M15" s="2" t="inlineStr"/>
+      <c r="N15" s="2" t="inlineStr"/>
+      <c r="O15" s="2" t="inlineStr"/>
+      <c r="P15" s="2" t="inlineStr"/>
+      <c r="Q15" s="2" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr"/>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>Bacterial Infection</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>"Bacterial infection" is a disease category, not a therapeutic agent. Current claim corpus describes epidemiologic causation in Chinese children/adolescents aged 6–22, not pharmacology. Scarlet fever case load doubled 2008→2017 [c:6571fe8e]; [[tuberculosis]] remains endemic driver [c:148ebe7c]. No medication claims in corpus — note cannot be populated per medication schema.</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr"/>
+      <c r="G16" s="2" t="inlineStr"/>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>_No mechanism-of-action claims in current corpus._</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr"/>
+      <c r="J16" s="2" t="inlineStr"/>
+      <c r="K16" s="2" t="inlineStr"/>
+      <c r="L16" s="2" t="inlineStr"/>
+      <c r="M16" s="2" t="inlineStr"/>
+      <c r="N16" s="2" t="inlineStr"/>
+      <c r="O16" s="2" t="inlineStr"/>
+      <c r="P16" s="2" t="inlineStr"/>
+      <c r="Q16" s="2" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr"/>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>Blood Group B</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>Blood group B is an ABO red-cell phenotype, not a therapeutic agent. Classifier flagged it as `medication`; corpus contains zero pharmacologic claims. Available claims describe epidemiologic association with *Plasmodium falciparum* infection burden in Kenyan outpatients. Note retained in medication schema for traceability; recommend reclassification to `biomarker` or `host-factor`.</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr"/>
+      <c r="G17" s="2" t="inlineStr"/>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>_No mechanistic claims in current corpus._ Association with parasitaemia reported but molecular pathway (e.g. rosetting, ABO antigen–PfEMP1 binding) not asserted by any claim.</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr"/>
+      <c r="J17" s="2" t="inlineStr"/>
+      <c r="K17" s="2" t="inlineStr"/>
+      <c r="L17" s="2" t="inlineStr"/>
+      <c r="M17" s="2" t="inlineStr"/>
+      <c r="N17" s="2" t="inlineStr"/>
+      <c r="O17" s="2" t="inlineStr"/>
+      <c r="P17" s="2" t="inlineStr"/>
+      <c r="Q17" s="2" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>Infectious Disease</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>Cerebral Malaria</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>Cerebral malaria = severe non-traumatic encephalopathy complicating [[falciparum-malaria]], defined by coma with [[plasmodium-falciparum]] parasitemia [c:2e32305f][c:88ea4b08][c:51829c73]. High case-fatality (~16.7% in children) and major driver of malaria mortality [c:def21fb4][c:89a27be9]. Survivors risk persistent neurologic, cognitive, behavioral sequelae and [[epilepsy]] [c:57a63a35][c:32918ad2][c:9b9670a1][c:55dc59e2].</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr"/>
+      <c r="G18" s="2" t="inlineStr"/>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>_Mechanism = pathogenesis of the syndrome, not drug MoA._ [[plasmodium-falciparum]] infection drives sequestration of parasitized RBCs in cerebral microvasculature, leukocyte sequestration, endothelial activation/apoptosis, cytokine imbalance, [[blood-brain-barrier]] disruption, neuroinflammation, reduced [[nitric-oxide]] bioavailability, platelet activation [c:a7ec1ecb][c:a6870dfa][c:768bc4fe][c:e26185c3][c:dd9cf2ce][c:99448174][c:992035a4][c:b3e62607][c:68f3b561][c:704d32a9][c:e402ac3d][c:98e27cc3][c:496787c6].
+```mermaid
+flowchart LR
+  A[P. falciparum infection] --&gt; B[iRBC + leukocyte sequestration&lt;br/&gt;cerebral microvasculature]
+  B --&gt; C[Endothelial activation/apoptosis&lt;br/&gt;cytokine imbalance]
+  C --&gt; D[BBB disruption +&lt;br/&gt;neuroinflammation]
+  D --&gt; E[Coma · seizures · death ·&lt;br/&gt;long-term sequelae]
+```
+Load-bearing: [c:e26185c3][c:dd9cf2ce][c:68f3b561][c:e402ac3d][c:4d836005]</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr"/>
+      <c r="J18" s="2" t="inlineStr"/>
+      <c r="K18" s="2" t="inlineStr"/>
+      <c r="L18" s="2" t="inlineStr"/>
+      <c r="M18" s="2" t="inlineStr"/>
+      <c r="N18" s="2" t="inlineStr"/>
+      <c r="O18" s="2" t="inlineStr"/>
+      <c r="P18" s="2" t="inlineStr"/>
+      <c r="Q18" s="2" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr"/>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>Chemoprophylaxis And Anti Mosquito Precautions</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>Composite preventive strategy for travelers to malaria-endemic regions. Combines antimalarial chemoprophylaxis (drug taken before/during/after travel) with anti-mosquito measures (repellents, bed nets, protective clothing). Not single drug — umbrella entity. Specific agents (e.g. [[atovaquone-proguanil]], [[doxycycline]], [[mefloquine]]) carry own dose/contraindication profiles.</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr"/>
+      <c r="G19" s="2" t="inlineStr"/>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>Two-pronged. Chemoprophylaxis = suppressive/causal antimalarial drug levels block parasite stages (liver or blood) during exposure window. Anti-mosquito precautions = reduce [[anopheles-mosquito]] bite exposure, cutting inoculation probability. Component-drug mechanisms vary — see individual notes.
+_No mechanistic claims in current corpus — synthesis based on indication claims only._</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr"/>
+      <c r="J19" s="2" t="inlineStr"/>
+      <c r="K19" s="2" t="inlineStr">
+        <is>
+          <t>**Therapeutic category:** Antimalarial prevention strategy
+**Drug group:** Composite intervention (pharmacologic + vector-avoidance)
+**Drug class:** N/A — bundled prevention regimen, not single agent
+**Controlled substance:** No (varies by component drug)</t>
+        </is>
+      </c>
+      <c r="L19" s="2" t="inlineStr"/>
+      <c r="M19" s="2" t="inlineStr"/>
+      <c r="N19" s="2" t="inlineStr"/>
+      <c r="O19" s="2" t="inlineStr"/>
+      <c r="P19" s="2" t="inlineStr"/>
+      <c r="Q19" s="2" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr"/>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>Chemoprophylaxis</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>Chemoprophylaxis = scheduled antimalarial dosing before, during, after travel to endemic zone. Prevents [[malaria]] in non-immune travelers. Not single drug — covers atovaquone-proguanil, doxycycline, mefloquine, chloroquine, primaquine, tafenoquine. Specific agent picked by destination resistance pattern, traveler comorbidities, pregnancy status. Note: this corpus describes the strategy generically; agent-specific dosing lives on individual drug notes.</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr"/>
+      <c r="G20" s="2" t="inlineStr"/>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>Agent-dependent. Schizonticidal agents (atovaquone-proguanil, doxycycline, mefloquine, chloroquine) suppress erythrocytic stage of [[plasmodium-falciparum]] and other species. Hypnozoiticidal agents (primaquine, tafenoquine) kill liver-stage hypnozoites of [[plasmodium-vivax]] / [[plasmodium-ovale]] — true causal prophylaxis. _No mechanism claims in current corpus — see individual drug notes._</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr"/>
+      <c r="J20" s="2" t="inlineStr"/>
+      <c r="K20" s="2" t="inlineStr">
+        <is>
+          <t>**Therapeutic category:** Antimalarial prevention strategy
+**Drug group:** Class — not single agent (umbrella term for prophylactic regimens)
+**Drug class:** N/A — strategy, not molecular entity
+**Controlled substance:** N/A — agent-dependent</t>
+        </is>
+      </c>
+      <c r="L20" s="2" t="inlineStr"/>
+      <c r="M20" s="2" t="inlineStr"/>
+      <c r="N20" s="2" t="inlineStr"/>
+      <c r="O20" s="2" t="inlineStr"/>
+      <c r="P20" s="2" t="inlineStr"/>
+      <c r="Q20" s="2" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>Infectious Disease</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>Childhood Malaria Diagnosis</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>"Childhood malaria diagnosis" not a medication. Entity is pediatric diagnostic workflow for [[malaria]]. Source corpus recommends six diagnostic tools versus [[giemsa-stained-microscopy]] reference standard: [[partec-rapid-malaria-test]], [[quantitative-buffy-coat]], [[loop-mediated-isothermal-amplification]], [[qpcr]], [[pcr]], and [[malaria-rapid-diagnostic-test]] [c:f4b624a7] [c:90046a7b] [c:2adbcf68] [c:fa1ecb07] [c:2416a91b] [c:247ce848]. All claims `(pending review)`, evidence grade expert_opinion.</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr"/>
+      <c r="G21" s="2" t="inlineStr"/>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>Not applicable — entity is diagnostic procedure category, no pharmacologic mechanism. Underlying diagnostic principles (antigen capture for RDT/Partec, fluorescence centrifugation for QBC, isothermal nucleic-acid amplification for LAMP, thermocycled amplification for PCR/qPCR) not stated in current claim set.</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr"/>
+      <c r="J21" s="2" t="inlineStr"/>
+      <c r="K21" s="2" t="inlineStr"/>
+      <c r="L21" s="2" t="inlineStr">
+        <is>
+          <t>**Therapeutic category:** Not applicable — diagnostic workflow, not a medication
+**Drug group:** N/A
+**Drug class:** N/A
+**Controlled substance:** N/A</t>
+        </is>
+      </c>
+      <c r="M21" s="2" t="inlineStr"/>
+      <c r="N21" s="2" t="inlineStr"/>
+      <c r="O21" s="2" t="inlineStr"/>
+      <c r="P21" s="2" t="inlineStr"/>
+      <c r="Q21" s="2" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>Infectious Disease</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>Childhood Malaria Mortality</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>[[r21-vaccine]] and [[rts-s-vaccine]] are recombinant CSP-based malaria vaccines targeting [[plasmodium-falciparum]] sporozoite stage. Both prevent [[childhood-malaria-mortality]] in pediatric populations in [[africa]] endemic settings, deployed at community care level [c:73db124f] [c:4a86f48e]. Both claims `(pending review)`, evidence grade expert_opinion.</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr"/>
+      <c r="G22" s="2" t="inlineStr"/>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>_No mechanism claims in current corpus._ Both vaccines target CSP per drug-class knowledge, but no claim_id supports mechanistic statement here.</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr"/>
+      <c r="J22" s="2" t="inlineStr"/>
+      <c r="K22" s="2" t="inlineStr"/>
+      <c r="L22" s="2" t="inlineStr"/>
+      <c r="M22" s="2" t="inlineStr"/>
+      <c r="N22" s="2" t="inlineStr"/>
+      <c r="O22" s="2" t="inlineStr"/>
+      <c r="P22" s="2" t="inlineStr"/>
+      <c r="Q22" s="2" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr"/>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>Children</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>Pediatric malaria pharmacotherapy spans prevention ([[rts-s-as01]] vaccine), radical cure (8-aminoquinolines), and severe-disease empirical cover. Age-based eligibility and contraindications dominate prescribing decisions. Co-infection risk in severe pediatric malaria drives empirical antibacterial use [c:c09b8c11].</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr"/>
+      <c r="G23" s="2" t="inlineStr"/>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>Population note — mechanism varies by agent. [[rts-s-as01]] = circumsporozoite-protein subunit vaccine eliciting anti-sporozoite antibody [c:f1c540dd]. Empirical antibacterials cover concurrent gram-negative bacteremia common in pediatric severe malaria [c:c09b8c11].</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr"/>
+      <c r="J23" s="2" t="inlineStr"/>
+      <c r="K23" s="2" t="inlineStr"/>
+      <c r="L23" s="2" t="inlineStr"/>
+      <c r="M23" s="2" t="inlineStr"/>
+      <c r="N23" s="2" t="inlineStr"/>
+      <c r="O23" s="2" t="inlineStr"/>
+      <c r="P23" s="2" t="inlineStr"/>
+      <c r="Q23" s="2" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr"/>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>Chronic Kidney Disease</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>AAV.k20 and AAV.k13 are engineered AAV capsids from cross-species capsid-library cycling, selected for kidney tropism. Preclinical candidates for gene transfer to renal tissue in [[chronic-kidney-disease]]. Outperform parental AAV9 on kidney-specific transduction metrics. Not approved; no human dosing established. (pending review)</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr"/>
+      <c r="G24" s="2" t="inlineStr"/>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>Engineered capsids bind renal cell surface receptors with higher affinity than [[aav9]], enabling vector entry and transgene delivery to kidney parenchyma. AAV.k20 enriches kidney transduction efficiency vs AAV9 [c:c9222e47]. AAV.k13 drives transgene expression in [[proximal-tubule-epithelial-cells]] vs AAV9 [c:6abbaaf5].
+```mermaid
+flowchart LR
+  A[AAV.k20/k13 capsid] --&gt; B[Renal cell receptor binding]
+  B --&gt; C[Endocytosis + nuclear entry]
+  C --&gt; D[Transgene expression in proximal tubule epithelium]
+  D --&gt; E[Therapeutic effect in CKD - investigational]
+```
+Mechanism load-bearing claims [c:c9222e47] [c:6abbaaf5].</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr"/>
+      <c r="J24" s="2" t="inlineStr"/>
+      <c r="K24" s="2" t="inlineStr"/>
+      <c r="L24" s="2" t="inlineStr"/>
+      <c r="M24" s="2" t="inlineStr"/>
+      <c r="N24" s="2" t="inlineStr"/>
+      <c r="O24" s="2" t="inlineStr"/>
+      <c r="P24" s="2" t="inlineStr"/>
+      <c r="Q24" s="2" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>Infectious Disease</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>Clinical Malaria Cases Globally</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>"Clinical malaria cases globally" is a disease-burden metric, not a drug. Current claim corpus describes causative parasites: [[plasmodium-falciparum]] accounted for ~234.8M clinical cases in 2022 (CI 179.2–299.0) [c:985b0a30] (pending review), and [[plasmodium-vivax]] for ~12.4M (CI 10.7–14.8) [c:9ce5aeea] (pending review). Both expert_opinion grade, sourced PMID:40056919. No medication claims present.</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr"/>
+      <c r="G25" s="2" t="inlineStr"/>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>_No mechanism-of-action claims in current corpus._</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="inlineStr"/>
+      <c r="J25" s="2" t="inlineStr"/>
+      <c r="K25" s="2" t="inlineStr"/>
+      <c r="L25" s="2" t="inlineStr"/>
+      <c r="M25" s="2" t="inlineStr"/>
+      <c r="N25" s="2" t="inlineStr"/>
+      <c r="O25" s="2" t="inlineStr"/>
+      <c r="P25" s="2" t="inlineStr"/>
+      <c r="Q25" s="2" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>Infectious Disease</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>Clinical Malaria Disease</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>Entity mis-routed to medication template. "Clinical malaria disease" denotes symptomatic infection (fever, anemia, coma) caused by Plasmodium spp., not a therapeutic agent. Current claim corpus contains only etiologic relations naming causative parasites. No pharmacologic claims present.</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr"/>
+      <c r="G26" s="2" t="inlineStr"/>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>_No mechanism-of-drug claims._ Disease caused by erythrocytic-stage infection with:
+- [[plasmodium-falciparum]] → fever, anemia, coma [c:b63de3da] (pending review)
+- [[plasmodium-vivax]] → fever, anemia, coma [c:88250477] [c:52321cce] (pending review)
+- [[plasmodium-knowlesi]] [c:f129bcbe] (pending review)
+- [[plasmodium-malariae]] [c:f67b0e2b] (pending review)
+- [[plasmodium-ovale-curtisi]] [c:b264f3cc] (pending review)
+- [[plasmodium-ovale-wallickeri]] [c:16a1b885] (pending review)
+All evidence_grade: expert_opinion (PMID:28533315).
+```mermaid
+graph LR
+  A[Plasmodium spp.] --&gt; B[Erythrocyte invasion]
+  B --&gt; C[Cytokine cascade + hemolysis]
+  C --&gt; D[Fever / Anemia / Coma]
+```
+Cascade inferred from etiologic claims [c:b63de3da] [c:88250477]; downstream steps not directly claim-backed.</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr"/>
+      <c r="J26" s="2" t="inlineStr"/>
+      <c r="K26" s="2" t="inlineStr"/>
+      <c r="L26" s="2" t="inlineStr"/>
+      <c r="M26" s="2" t="inlineStr"/>
+      <c r="N26" s="2" t="inlineStr"/>
+      <c r="O26" s="2" t="inlineStr"/>
+      <c r="P26" s="2" t="inlineStr"/>
+      <c r="Q26" s="2" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>Infectious Disease</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>Clinical Malaria</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>Clinical malaria = symptomatic [[plasmodium]] infection (fever, anemia, coma) caused by [[plasmodium-falciparum]] [c:c349e9ee] and [[plasmodium-vivax]] [c:0a98f134]. Entity classified as medication in source hint but corpus claims describe **preventive interventions against** clinical malaria, not a drug. Note below catalogs intervention claims rather than pharmacology of single agent.</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr"/>
+      <c r="G27" s="2" t="inlineStr"/>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>Disease entity — no MoA. Causal pathway:
+```mermaid
+graph LR
+    A[Anopheles bite] --&gt; B[Plasmodium sporozoite]
+    B --&gt; C[Hepatic + erythrocytic cycle]
+    C --&gt; D[P. falciparum / P. vivax blood stage]
+    D --&gt; E[Clinical malaria: fever, anemia, coma]
+```
+P. falciparum drives severe phenotype [c:c349e9ee]; P. vivax also causes clinical disease [c:0a98f134]. Repeated natural infection in semi-immune adults reduces clinical episodes [c:12134f40] _(pending review)_.</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="inlineStr"/>
+      <c r="J27" s="2" t="inlineStr"/>
+      <c r="K27" s="2" t="inlineStr"/>
+      <c r="L27" s="2" t="inlineStr"/>
+      <c r="M27" s="2" t="inlineStr"/>
+      <c r="N27" s="2" t="inlineStr"/>
+      <c r="O27" s="2" t="inlineStr"/>
+      <c r="P27" s="2" t="inlineStr"/>
+      <c r="Q27" s="2" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>Infectious Disease</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>Clinical Plasmodium Falciparum Malaria</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>Two WHO-track recombinant CSP vaccines for prevention of clinical *[[plasmodium-falciparum-malaria]]* in young children living in endemic [[sub-saharan-africa]]. [[R21-matrix-m]] uses Matrix-M saponin adjuvant; [[rts-s-as01]] uses AS01 liposomal adjuvant. Both target sporozoite stage to block hepatocyte invasion. Indicated for primary prevention in pediatric endemic populations, not for treatment, not for travelers in this claim set.</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr"/>
+      <c r="G28" s="2" t="inlineStr"/>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>Both vaccines present *P. falciparum* circumsporozoite protein (CSP) fused to hepatitis B surface antigen, assembled as virus-like particles, co-administered with a Th1-biasing adjuvant. Anti-CSP antibodies and CD4⁺ T-cell responses neutralise sporozoites in skin and bloodstream before hepatocyte infection, preventing onward blood-stage disease [c:4d79258b][c:ba445aee] (pending review).
+```mermaid
+flowchart LR
+  A[CSP VLP + adjuvant] --&gt; B[Anti-CSP IgG + CD4 T cells]
+  B --&gt; C[Sporozoite neutralisation pre-liver]
+  C --&gt; D[No hepatocyte infection]
+  D --&gt; E[No blood-stage clinical malaria]
+```
+Cascade load-bearing on [c:4d79258b].</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="inlineStr"/>
+      <c r="J28" s="2" t="inlineStr"/>
+      <c r="K28" s="2" t="inlineStr"/>
+      <c r="L28" s="2" t="inlineStr"/>
+      <c r="M28" s="2" t="inlineStr">
+        <is>
+          <t>- **R21/Matrix-M:** 12-month vaccine efficacy **75%** (95% CI 71–79) against time to first clinical malaria at seasonal sites, vs rabies-vaccine comparator (Abhayrab), children 5–36 mo, sub-Saharan Africa [c:4d79258b] (RCT, pending review).
+- **RTS,S/AS01:** prevents clinical *P. falciparum* malaria in 5–17 mo African children; numeric efficacy not in claim [c:ba445aee] (expert_opinion, pending review).</t>
+        </is>
+      </c>
+      <c r="N28" s="2" t="inlineStr"/>
+      <c r="O28" s="2" t="inlineStr"/>
+      <c r="P28" s="2" t="inlineStr"/>
+      <c r="Q28" s="2" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="B29" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="C29" s="2" t="inlineStr"/>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>Coinfections</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>"Coinfections" not drug. Refers to concurrent infections alongside [[malaria]] that modulate clinical disease presentation [c:9a5d8ea5] (pending review) and co-occur with malaria infection [c:5983f065] (pending review). Entity miscategorized as medication — no pharmacologic content extractable from current claim corpus.</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr"/>
+      <c r="G29" s="2" t="inlineStr"/>
+      <c r="H29" s="2" t="inlineStr">
+        <is>
+          <t>_No mechanism claims in current corpus. Entity is not a pharmacologic agent._</t>
+        </is>
+      </c>
+      <c r="I29" s="2" t="inlineStr"/>
+      <c r="J29" s="2" t="inlineStr"/>
+      <c r="K29" s="2" t="inlineStr"/>
+      <c r="L29" s="2" t="inlineStr"/>
+      <c r="M29" s="2" t="inlineStr"/>
+      <c r="N29" s="2" t="inlineStr"/>
+      <c r="O29" s="2" t="inlineStr"/>
+      <c r="P29" s="2" t="inlineStr"/>
+      <c r="Q29" s="2" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="C30" s="2" t="inlineStr"/>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>Coma</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>Coma not drug. Current claim set describes coma as clinical manifestation of [[malaria-infection]], notably [[cerebral-malaria]] in inpatient endemic settings [c:51829c73] [c:7c444a95] (pending review). No pharmacologic data in corpus. Entity likely misclassified as `medication`; should map to symptom/sign or syndrome node.</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr"/>
+      <c r="G30" s="2" t="inlineStr"/>
+      <c r="H30" s="2" t="inlineStr">
+        <is>
+          <t>_Not applicable._ Pathogenesis context only: [[malaria-infection]] causes coma [c:7c444a95] (pending review); coma with parasitemia co-occurs with [[cerebral-malaria]] in inpatient endemic care [c:51829c73] (pending review).</t>
+        </is>
+      </c>
+      <c r="I30" s="2" t="inlineStr"/>
+      <c r="J30" s="2" t="inlineStr"/>
+      <c r="K30" s="2" t="inlineStr"/>
+      <c r="L30" s="2" t="inlineStr"/>
+      <c r="M30" s="2" t="inlineStr"/>
+      <c r="N30" s="2" t="inlineStr"/>
+      <c r="O30" s="2" t="inlineStr"/>
+      <c r="P30" s="2" t="inlineStr"/>
+      <c r="Q30" s="2" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="B31" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="C31" s="2" t="inlineStr"/>
+      <c r="D31" s="2" t="inlineStr">
+        <is>
+          <t>Comorbidities</t>
+        </is>
+      </c>
+      <c r="E31" s="2" t="inlineStr">
+        <is>
+          <t>"Comorbidities" is not a drug. Current claim set links comorbidities to [[malaria]] pathogenesis and infection, not to any therapeutic agent. Note retained for traceability; promote to a condition/modifier note on next regen. (pending review)</t>
+        </is>
+      </c>
+      <c r="F31" s="2" t="inlineStr"/>
+      <c r="G31" s="2" t="inlineStr"/>
+      <c r="H31" s="2" t="inlineStr">
+        <is>
+          <t>_No mechanism claims in current corpus._</t>
+        </is>
+      </c>
+      <c r="I31" s="2" t="inlineStr"/>
+      <c r="J31" s="2" t="inlineStr"/>
+      <c r="K31" s="2" t="inlineStr"/>
+      <c r="L31" s="2" t="inlineStr"/>
+      <c r="M31" s="2" t="inlineStr"/>
+      <c r="N31" s="2" t="inlineStr"/>
+      <c r="O31" s="2" t="inlineStr"/>
+      <c r="P31" s="2" t="inlineStr"/>
+      <c r="Q31" s="2" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="C32" s="2" t="inlineStr"/>
+      <c r="D32" s="2" t="inlineStr">
+        <is>
+          <t>Death</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="inlineStr">
+        <is>
+          <t>Entity "death" routed to medication template by classifier error. Claim corpus describes death as mortality outcome of [[malaria]], [[cerebral-malaria]], [[plasmodium-knowlesi-malaria]], [[plasmodium-vivax-malaria]], and [[hiv-aids]] — not pharmacology of a therapeutic agent. Note preserved for traceability; recommend re-route to disease/outcome template.</t>
+        </is>
+      </c>
+      <c r="F32" s="2" t="inlineStr"/>
+      <c r="G32" s="2" t="inlineStr"/>
+      <c r="H32" s="2" t="inlineStr">
+        <is>
+          <t>_No mechanism-of-action claims. Causal drivers of mortality in corpus:_
+- [[cerebral-malaria]] → pediatric mortality, case-fatality 16.7% inpatient endemic settings [c:def21fb4] (pending review).
+- [[plasmodium-knowlesi-malaria]] with delayed IV antimalarial therapy → 35.5% of fatal adult cases in Southeast Asia tied to treatment delay [c:93d72be2] (pending review, meta_analysis).
+- Recurrent and chronic [[plasmodium-vivax]] infection → mortality in pediatric and &lt;5 yr populations [c:a371cec5][c:ba8a9f67] (pending review).
+- [[hiv-aids]] → 5× rise in mortality incidence Chinese children/adolescents 6–22 yr 2011–2017 [c:e55f7c4b] (pending review).</t>
+        </is>
+      </c>
+      <c r="I32" s="2" t="inlineStr"/>
+      <c r="J32" s="2" t="inlineStr"/>
+      <c r="K32" s="2" t="inlineStr"/>
+      <c r="L32" s="2" t="inlineStr"/>
+      <c r="M32" s="2" t="inlineStr"/>
+      <c r="N32" s="2" t="inlineStr"/>
+      <c r="O32" s="2" t="inlineStr"/>
+      <c r="P32" s="2" t="inlineStr"/>
+      <c r="Q32" s="2" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="B33" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="C33" s="2" t="inlineStr"/>
+      <c r="D33" s="2" t="inlineStr">
+        <is>
+          <t>Deforestation</t>
+        </is>
+      </c>
+      <c r="E33" s="2" t="inlineStr">
+        <is>
+          <t>Deforestation is not a therapeutic agent. Entity classifier flagged it as `medication`, but current claim corpus describes it as an ecological driver of zoonotic malaria emergence in Southeast Asia — increasing human–vector–macaque contact at forest fringes [c:56f9051a] [c:8c95f5ac]. Note retained under medication template for exporter parity; pharmacological sections intentionally empty.</t>
+        </is>
+      </c>
+      <c r="F33" s="2" t="inlineStr"/>
+      <c r="G33" s="2" t="inlineStr"/>
+      <c r="H33" s="2" t="inlineStr">
+        <is>
+          <t>Land-use mechanism, not pharmacological. Forest clearance pushes simian-malaria vectors and macaque reservoirs into farms, plantations, and settlements [c:56f9051a], expanding [[anopheles-leucosphyrus-group]] vector range into human habitation [c:a89c2532] (pending review).
+```mermaid
+flowchart LR
+    A[Deforestation] --&gt;|range shift| B[Leucosphyrus vectors enter settlements]
+    A --&gt;|habitat fragmentation| C[Macaque movement to forest fringe]
+    B --&gt; D[Increased human-vector contact]
+    C --&gt; D
+    D --&gt; E[P. knowlesi zoonotic spillover]
+```
+Cascade load-bearing: [c:56f9051a] [c:a89c2532] [c:8c95f5ac].</t>
+        </is>
+      </c>
+      <c r="I33" s="2" t="inlineStr"/>
+      <c r="J33" s="2" t="inlineStr"/>
+      <c r="K33" s="2" t="inlineStr"/>
+      <c r="L33" s="2" t="inlineStr"/>
+      <c r="M33" s="2" t="inlineStr"/>
+      <c r="N33" s="2" t="inlineStr"/>
+      <c r="O33" s="2" t="inlineStr"/>
+      <c r="P33" s="2" t="inlineStr"/>
+      <c r="Q33" s="2" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="B34" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="C34" s="2" t="inlineStr"/>
+      <c r="D34" s="2" t="inlineStr">
+        <is>
+          <t>Delayed Treatment</t>
+        </is>
+      </c>
+      <c r="E34" s="2" t="inlineStr">
+        <is>
+          <t>"Delayed treatment" not medication. Care-process concept describing late initiation of antimalarial therapy after symptom onset. Misclassified as medication in source corpus. Note retained for graph integrity; clinical content limited to outcome association with [[malaria]] (pending review).</t>
+        </is>
+      </c>
+      <c r="F34" s="2" t="inlineStr"/>
+      <c r="G34" s="2" t="inlineStr"/>
+      <c r="H34" s="2" t="inlineStr">
+        <is>
+          <t>_Not applicable._ Mechanism of harm (not action): late parasite clearance allows progression to severe [[malaria]], organ dysfunction, higher parasitemia [c:30e9d56b] (pending review).</t>
+        </is>
+      </c>
+      <c r="I34" s="2" t="inlineStr"/>
+      <c r="J34" s="2" t="inlineStr"/>
+      <c r="K34" s="2" t="inlineStr"/>
+      <c r="L34" s="2" t="inlineStr"/>
+      <c r="M34" s="2" t="inlineStr">
+        <is>
+          <t>**Therapeutic category:** Not applicable — care-process concept, not pharmacologic agent
+**Drug group:** N/A
+**Drug class:** N/A
+**Controlled substance:** No</t>
+        </is>
+      </c>
+      <c r="N34" s="2" t="inlineStr"/>
+      <c r="O34" s="2" t="inlineStr"/>
+      <c r="P34" s="2" t="inlineStr"/>
+      <c r="Q34" s="2" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="B35" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="C35" s="2" t="inlineStr">
+        <is>
+          <t>Infectious Disease</t>
+        </is>
+      </c>
+      <c r="D35" s="2" t="inlineStr">
+        <is>
+          <t>Diagnosis Of P Falciparum And P Vivax Malaria</t>
+        </is>
+      </c>
+      <c r="E35" s="2" t="inlineStr">
+        <is>
+          <t>Entity not a drug. Diagnostic procedure for confirming [[plasmodium-falciparum]] and [[plasmodium-vivax]] infection in suspected [[malaria]]. Current corpus covers rapid diagnostic testing (RDT) for plasmodial antigens vs. thick/thin blood films in UK imported-malaria setting [c:d220f730] [c:3f3fbc91] (pending review).</t>
+        </is>
+      </c>
+      <c r="F35" s="2" t="inlineStr"/>
+      <c r="G35" s="2" t="inlineStr"/>
+      <c r="H35" s="2" t="inlineStr">
+        <is>
+          <t>N/A — diagnostic procedure, no pharmacologic mechanism. [[rapid-diagnostic-test]] detects plasmodial antigens (e.g., HRP-2, pLDH); compared against thick/thin blood films as reference [c:3f3fbc91] (pending review).</t>
+        </is>
+      </c>
+      <c r="I35" s="2" t="inlineStr"/>
+      <c r="J35" s="2" t="inlineStr"/>
+      <c r="K35" s="2" t="inlineStr"/>
+      <c r="L35" s="2" t="inlineStr">
+        <is>
+          <t>**Therapeutic category:** Not applicable — diagnostic workup, not a medication
+**Drug group:** N/A
+**Drug class:** N/A
+**Controlled substance:** N/A</t>
+        </is>
+      </c>
+      <c r="M35" s="2" t="inlineStr"/>
+      <c r="N35" s="2" t="inlineStr"/>
+      <c r="O35" s="2" t="inlineStr"/>
+      <c r="P35" s="2" t="inlineStr"/>
+      <c r="Q35" s="2" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="B36" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="C36" s="2" t="inlineStr"/>
+      <c r="D36" s="2" t="inlineStr">
+        <is>
+          <t>Disturbed Consciousness</t>
+        </is>
+      </c>
+      <c r="E36" s="2" t="inlineStr">
+        <is>
+          <t>Entity classifier flagged "disturbed consciousness" as medication, but corpus describes clinical sign in [[falciparum-malaria]], notably [[cerebral-malaria]] [c:a08338a4]. No pharmacologic claims present. Note retained as stub; recommend reclassification to `symptom` or `clinical-finding`.</t>
+        </is>
+      </c>
+      <c r="F36" s="2" t="inlineStr"/>
+      <c r="G36" s="2" t="inlineStr"/>
+      <c r="H36" s="2" t="inlineStr">
+        <is>
+          <t>_No mechanism-of-action claims. Entity is symptom, not agent._</t>
+        </is>
+      </c>
+      <c r="I36" s="2" t="inlineStr"/>
+      <c r="J36" s="2" t="inlineStr"/>
+      <c r="K36" s="2" t="inlineStr"/>
+      <c r="L36" s="2" t="inlineStr"/>
+      <c r="M36" s="2" t="inlineStr"/>
+      <c r="N36" s="2" t="inlineStr"/>
+      <c r="O36" s="2" t="inlineStr"/>
+      <c r="P36" s="2" t="inlineStr"/>
+      <c r="Q36" s="2" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="B37" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="C37" s="2" t="inlineStr">
+        <is>
+          <t>Infectious Disease</t>
+        </is>
+      </c>
+      <c r="D37" s="2" t="inlineStr">
+        <is>
+          <t>Early Accurate Malaria Diagnosis</t>
+        </is>
+      </c>
+      <c r="E37" s="2" t="inlineStr">
+        <is>
+          <t>"Early accurate malaria diagnosis" is diagnostic strategy, not drug. Refers to prompt confirmatory testing (RDT, microscopy, PCR) before antimalarial use, vs presumptive treatment. Pediatric claims in current corpus tie strategy to two stewardship outcomes: fewer needless drug exposures and slower resistance emergence in endemic settings [c:efc5aa9a][c:00972ef4]. Note: entity type flagged `medication` upstream but no drug substance — downstream sections largely non-applicable.</t>
+        </is>
+      </c>
+      <c r="F37" s="2" t="inlineStr"/>
+      <c r="G37" s="2" t="inlineStr"/>
+      <c r="H37" s="2" t="inlineStr">
+        <is>
+          <t>Not a pharmacologic agent. Operates upstream of prescribing: confirmatory test result gates antimalarial initiation, vs [[presumptive-diagnosis]] comparator. Two claimed downstream effects:
+```mermaid
+graph LR
+    A[Confirmatory test&lt;br/&gt;RDT/microscopy/PCR] --&gt; B{Result}
+    B --&gt;|Negative| C[No antimalarial&lt;br/&gt;→ fewer adverse reactions]
+    B --&gt;|Positive| D[Targeted antimalarial&lt;br/&gt;→ reduced drug pressure]
+    C --&gt; E[Prevent unnecessary ADRs]
+    D --&gt; F[Slow resistance emergence]
+```
+Evidence grade: expert_opinion for both pathways [c:efc5aa9a][c:00972ef4].</t>
+        </is>
+      </c>
+      <c r="I37" s="2" t="inlineStr"/>
+      <c r="J37" s="2" t="inlineStr"/>
+      <c r="K37" s="2" t="inlineStr"/>
+      <c r="L37" s="2" t="inlineStr">
+        <is>
+          <t>**Therapeutic category:** Diagnostic strategy (not a medication)
+**Drug group:** N/A — entity misclassified as medication
+**Drug class:** N/A
+**Controlled substance:** N/A</t>
+        </is>
+      </c>
+      <c r="M37" s="2" t="inlineStr"/>
+      <c r="N37" s="2" t="inlineStr"/>
+      <c r="O37" s="2" t="inlineStr"/>
+      <c r="P37" s="2" t="inlineStr"/>
+      <c r="Q37" s="2" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="B38" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="C38" s="2" t="inlineStr"/>
+      <c r="D38" s="2" t="inlineStr">
+        <is>
+          <t>Empirical Broad Spectrum Antibiotics</t>
+        </is>
+      </c>
+      <c r="E38" s="2" t="inlineStr">
+        <is>
+          <t>Empirical broad-spectrum antibiotics = adjunct therapy given alongside antimalarials in pediatric severe malaria when bacterial coinfection suspected. Cover likely pathogens (especially Gram-negative bacteraemia) before culture results. Not antimalarial agent itself — risk-mitigation layer for sepsis overlap. Current claim corpus class-level only; no specific agent named.</t>
+        </is>
+      </c>
+      <c r="F38" s="2" t="inlineStr"/>
+      <c r="G38" s="2" t="inlineStr"/>
+      <c r="H38" s="2" t="inlineStr">
+        <is>
+          <t>Class-level mechanism: broad-spectrum coverage of suspected bacterial pathogens (Gram-negative + Gram-positive) co-occurring with [[plasmodium-falciparum]] sepsis-like presentation. Severe malaria mimics + overlaps bacterial sepsis; coinfection rate non-trivial in pediatric cases, especially [[gram-negative-bacteraemia]] [c:9ca47024]. Empirical cover bridges diagnostic gap until cultures return.
+_No specific agent-level mechanism claims in current corpus._</t>
+        </is>
+      </c>
+      <c r="I38" s="2" t="inlineStr"/>
+      <c r="J38" s="2" t="inlineStr"/>
+      <c r="K38" s="2" t="inlineStr"/>
+      <c r="L38" s="2" t="inlineStr"/>
+      <c r="M38" s="2" t="inlineStr"/>
+      <c r="N38" s="2" t="inlineStr"/>
+      <c r="O38" s="2" t="inlineStr"/>
+      <c r="P38" s="2" t="inlineStr"/>
+      <c r="Q38" s="2" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="B39" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="C39" s="2" t="inlineStr">
+        <is>
+          <t>Infectious Disease</t>
+        </is>
+      </c>
+      <c r="D39" s="2" t="inlineStr">
+        <is>
+          <t>Falciparum Malaria</t>
+        </is>
+      </c>
+      <c r="E39" s="2" t="inlineStr">
+        <is>
+          <t>Falciparum malaria is the *Plasmodium falciparum* infection covered by the current claim set as a clinical condition, not a therapeutic agent. The corpus describes complications and pregnancy-related outcomes only; no pharmacologic claims are present. Cross-references: [[plasmodium-falciparum]], [[cerebral-malaria]], [[malaria-in-pregnancy]].</t>
+        </is>
+      </c>
+      <c r="F39" s="2" t="inlineStr"/>
+      <c r="G39" s="2" t="inlineStr"/>
+      <c r="H39" s="2" t="inlineStr">
+        <is>
+          <t>_No mechanism claims in current corpus._</t>
+        </is>
+      </c>
+      <c r="I39" s="2" t="inlineStr"/>
+      <c r="J39" s="2" t="inlineStr"/>
+      <c r="K39" s="2" t="inlineStr"/>
+      <c r="L39" s="2" t="inlineStr"/>
+      <c r="M39" s="2" t="inlineStr"/>
+      <c r="N39" s="2" t="inlineStr"/>
+      <c r="O39" s="2" t="inlineStr"/>
+      <c r="P39" s="2" t="inlineStr"/>
+      <c r="Q39" s="2" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="B40" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="C40" s="2" t="inlineStr">
+        <is>
+          <t>Infectious Disease</t>
+        </is>
+      </c>
+      <c r="D40" s="2" t="inlineStr">
+        <is>
+          <t>Fatal Malaria</t>
+        </is>
+      </c>
+      <c r="E40" s="2" t="inlineStr">
+        <is>
+          <t>"Fatal malaria" denotes death from malaria infection, not a therapeutic agent. Current claim corpus links [[plasmodium-knowlesi]] to fatal outcomes in [[south-east-asia]], with elevated risk in adults ≥45 years and females in [[sabah-malaysia]] [c:94a1e7ae] [c:201b76e2] [c:58b903a5]. Entity surfaced under `medication` type but no pharmacologic claims exist. Note retained as outcome stub pending reclassification.</t>
+        </is>
+      </c>
+      <c r="F40" s="2" t="inlineStr"/>
+      <c r="G40" s="2" t="inlineStr"/>
+      <c r="H40" s="2" t="inlineStr">
+        <is>
+          <t>_Not applicable. Causal driver in corpus: [[plasmodium-knowlesi]] infection progressing to death, inpatient endemic settings [c:94a1e7ae] (pending review, expert_opinion)._</t>
+        </is>
+      </c>
+      <c r="I40" s="2" t="inlineStr"/>
+      <c r="J40" s="2" t="inlineStr"/>
+      <c r="K40" s="2" t="inlineStr"/>
+      <c r="L40" s="2" t="inlineStr"/>
+      <c r="M40" s="2" t="inlineStr"/>
+      <c r="N40" s="2" t="inlineStr"/>
+      <c r="O40" s="2" t="inlineStr"/>
+      <c r="P40" s="2" t="inlineStr"/>
+      <c r="Q40" s="2" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="B41" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="C41" s="2" t="inlineStr">
+        <is>
+          <t>Infectious Disease</t>
+        </is>
+      </c>
+      <c r="D41" s="2" t="inlineStr">
+        <is>
+          <t>Fatal Plasmodium Knowlesi Malaria</t>
+        </is>
+      </c>
+      <c r="E41" s="2" t="inlineStr">
+        <is>
+          <t>Fatal [[plasmodium-knowlesi-malaria]] = death from zoonotic simian malaria, [[southeast-asia]] endemic, especially [[sabah-malaysia]]. Current corpus (4 claims, all meta-analysis grade, all pending review, all from PMID:30624597) characterises risk-factor profile of fatal cases — not a pharmacotherapy.</t>
+        </is>
+      </c>
+      <c r="F41" s="2" t="inlineStr"/>
+      <c r="G41" s="2" t="inlineStr"/>
+      <c r="H41" s="2" t="inlineStr">
+        <is>
+          <t>_No mechanism-of-action claims in current corpus. Mechanism of fatal progression (hyperparasitaemia, multi-organ failure) not represented in supplied claims._</t>
+        </is>
+      </c>
+      <c r="I41" s="2" t="inlineStr"/>
+      <c r="J41" s="2" t="inlineStr"/>
+      <c r="K41" s="2" t="inlineStr"/>
+      <c r="L41" s="2" t="inlineStr"/>
+      <c r="M41" s="2" t="inlineStr"/>
+      <c r="N41" s="2" t="inlineStr"/>
+      <c r="O41" s="2" t="inlineStr"/>
+      <c r="P41" s="2" t="inlineStr"/>
+      <c r="Q41" s="2" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="B42" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="C42" s="2" t="inlineStr"/>
+      <c r="D42" s="2" t="inlineStr">
+        <is>
+          <t>Female Sex</t>
+        </is>
+      </c>
+      <c r="E42" s="2" t="inlineStr">
+        <is>
+          <t>"female sex" = biological/demographic variable, not therapeutic agent. Current claim corpus links it to malaria outcomes as risk modifier vs male sex comparator. No pharmacological content extractable. Note retained for graph linkage to [[plasmodium-knowlesi-malaria]] and [[plasmodium-falciparum-malaria]] risk-stratification.</t>
+        </is>
+      </c>
+      <c r="F42" s="2" t="inlineStr"/>
+      <c r="G42" s="2" t="inlineStr"/>
+      <c r="H42" s="2" t="inlineStr">
+        <is>
+          <t>_No mechanistic claims in corpus._ Sex-linked mortality differential in [[plasmodium-knowlesi-malaria]] reported but biological mediator unspecified [c:c8783906].</t>
+        </is>
+      </c>
+      <c r="I42" s="2" t="inlineStr"/>
+      <c r="J42" s="2" t="inlineStr"/>
+      <c r="K42" s="2" t="inlineStr"/>
+      <c r="L42" s="2" t="inlineStr"/>
+      <c r="M42" s="2" t="inlineStr"/>
+      <c r="N42" s="2" t="inlineStr"/>
+      <c r="O42" s="2" t="inlineStr"/>
+      <c r="P42" s="2" t="inlineStr"/>
+      <c r="Q42" s="2" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="B43" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="C43" s="2" t="inlineStr"/>
+      <c r="D43" s="2" t="inlineStr">
+        <is>
+          <t>Fetal Growth Restriction</t>
+        </is>
+      </c>
+      <c r="E43" s="2" t="inlineStr">
+        <is>
+          <t>Entity "fetal growth restriction" misclassified as medication. FGR is obstetric outcome — impaired fetal growth versus gestational-age norms. Current claim corpus describes upstream causes of FGR ([[macronutrient-undernutrition]], [[malaria-in-pregnancy]], [[folate-deficiency]]) in pregnant adults, not a pharmacologic agent. No drug claims present.</t>
+        </is>
+      </c>
+      <c r="F43" s="2" t="inlineStr"/>
+      <c r="G43" s="2" t="inlineStr"/>
+      <c r="H43" s="2" t="inlineStr">
+        <is>
+          <t>_No mechanism-of-action claims for a drug in current corpus._ Claim set describes pathogenic cascades into FGR, not pharmacology.</t>
+        </is>
+      </c>
+      <c r="I43" s="2" t="inlineStr"/>
+      <c r="J43" s="2" t="inlineStr"/>
+      <c r="K43" s="2" t="inlineStr"/>
+      <c r="L43" s="2" t="inlineStr"/>
+      <c r="M43" s="2" t="inlineStr"/>
+      <c r="N43" s="2" t="inlineStr"/>
+      <c r="O43" s="2" t="inlineStr"/>
+      <c r="P43" s="2" t="inlineStr"/>
+      <c r="Q43" s="2" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="B44" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="C44" s="2" t="inlineStr"/>
+      <c r="D44" s="2" t="inlineStr">
+        <is>
+          <t>Fever</t>
+        </is>
+      </c>
+      <c r="E44" s="2" t="inlineStr">
+        <is>
+          <t>Fever is a symptom, not a therapeutic agent. Current claim corpus describes fever as a clinical manifestation of [[malaria]] infection [c:a5fe6db3] [c:984cfa60] (pending review) and as a reactogenicity event after [[r21-matrix-m]] malaria vaccination in young children [c:ea78f724] (pending review). No claims position fever as a drug; this note preserves the master-sheet shape but flags the type mismatch.</t>
+        </is>
+      </c>
+      <c r="F44" s="2" t="inlineStr"/>
+      <c r="G44" s="2" t="inlineStr"/>
+      <c r="H44" s="2" t="inlineStr">
+        <is>
+          <t>_No mechanism-of-action claims for fever as an agent._ Mechanistically, claims describe fever as a downstream effect:
+```mermaid
+flowchart LR
+  A[Malaria infection] --&gt;|causes| B[Fever]
+  C[R21/Matrix-M vaccination] --&gt;|reactogenicity| B
+```
+- [[malaria]] infection → fever [c:a5fe6db3] (expert_opinion, pending review)
+- [[malaria]] in endemic setting → fever [c:984cfa60] (expert_opinion, pending review)
+- [[r21-matrix-m]] vaccination → fever in children 5–36 months, sub-Saharan Africa [c:ea78f724] (RCT, pending review)</t>
+        </is>
+      </c>
+      <c r="I44" s="2" t="inlineStr"/>
+      <c r="J44" s="2" t="inlineStr"/>
+      <c r="K44" s="2" t="inlineStr"/>
+      <c r="L44" s="2" t="inlineStr"/>
+      <c r="M44" s="2" t="inlineStr"/>
+      <c r="N44" s="2" t="inlineStr"/>
+      <c r="O44" s="2" t="inlineStr"/>
+      <c r="P44" s="2" t="inlineStr"/>
+      <c r="Q44" s="2" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="B45" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="C45" s="2" t="inlineStr">
+        <is>
+          <t>Infectious Disease</t>
+        </is>
+      </c>
+      <c r="D45" s="2" t="inlineStr">
+        <is>
+          <t>First Trimester Malaria Infection</t>
+        </is>
+      </c>
+      <c r="E45" s="2" t="inlineStr">
+        <is>
+          <t>First-trimester malaria infection refers to *Plasmodium* infection during weeks 1–13 of pregnancy in endemic settings. Current claim corpus frames it as a risk exposure linked to adverse pregnancy outcomes [c:6cab89a1] [c:c9adccaf] (pending review). Entity classified upstream as `medication` but corpus content is condition-level — no pharmacologic data present.</t>
+        </is>
+      </c>
+      <c r="F45" s="2" t="inlineStr"/>
+      <c r="G45" s="2" t="inlineStr"/>
+      <c r="H45" s="2" t="inlineStr">
+        <is>
+          <t>_No mechanism-of-action claims in current corpus._ Pathophysiology (placental sequestration, [[var2csa]]-mediated cytoadherence, maternal anemia) not represented in present claim set.</t>
+        </is>
+      </c>
+      <c r="I45" s="2" t="inlineStr"/>
+      <c r="J45" s="2" t="inlineStr"/>
+      <c r="K45" s="2" t="inlineStr"/>
+      <c r="L45" s="2" t="inlineStr"/>
+      <c r="M45" s="2" t="inlineStr"/>
+      <c r="N45" s="2" t="inlineStr"/>
+      <c r="O45" s="2" t="inlineStr"/>
+      <c r="P45" s="2" t="inlineStr"/>
+      <c r="Q45" s="2" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="B46" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="C46" s="2" t="inlineStr">
+        <is>
+          <t>Infectious Disease</t>
+        </is>
+      </c>
+      <c r="D46" s="2" t="inlineStr">
+        <is>
+          <t>First Trimester Malaria Treatment</t>
+        </is>
+      </c>
+      <c r="E46" s="2" t="inlineStr">
+        <is>
+          <t>Note covers ACT use for malaria during first trimester of pregnancy. Current corpus flags ACT as contraindicated in this window per expert-opinion sources (pending review). Substance is the therapeutic decision, not a distinct molecule.</t>
+        </is>
+      </c>
+      <c r="F46" s="2" t="inlineStr"/>
+      <c r="G46" s="2" t="inlineStr"/>
+      <c r="H46" s="2" t="inlineStr">
+        <is>
+          <t>[[artemisinin-based-combination-therapy]] acts via endoperoxide bridge cleavage generating reactive radicals against *Plasmodium* — but mechanistic claims not present in current corpus. _No mechanism claims in current corpus._</t>
+        </is>
+      </c>
+      <c r="I46" s="2" t="inlineStr"/>
+      <c r="J46" s="2" t="inlineStr"/>
+      <c r="K46" s="2" t="inlineStr"/>
+      <c r="L46" s="2" t="inlineStr"/>
+      <c r="M46" s="2" t="inlineStr">
+        <is>
+          <t>**Therapeutic category:** Antimalarial (pregnancy-restricted context)
+**Drug group:** Artemisinin combination therapy (ACT) — first-trimester use
+**Drug class:** Sesquiterpene endoperoxide + partner drug
+**Controlled substance:** No</t>
+        </is>
+      </c>
+      <c r="N46" s="2" t="inlineStr"/>
+      <c r="O46" s="2" t="inlineStr"/>
+      <c r="P46" s="2" t="inlineStr"/>
+      <c r="Q46" s="2" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="B47" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="C47" s="2" t="inlineStr"/>
+      <c r="D47" s="2" t="inlineStr">
+        <is>
+          <t>G6Pd Deficiency</t>
+        </is>
+      </c>
+      <c r="E47" s="2" t="inlineStr">
+        <is>
+          <t>[[g6pd-deficiency]] not medication. X-linked red-cell enzyme defect predisposing to oxidative haemolysis. Listed here because corpus claims frame it as contraindication target for 8-aminoquinoline antimalarials [[primaquine]] [c:d8708538] and [[tafenoquine]] [c:e03ebba8]. Classifier mismatch — true medication note unavailable. Content below summarises drug-safety relationship only.</t>
+        </is>
+      </c>
+      <c r="F47" s="2" t="inlineStr"/>
+      <c r="G47" s="2" t="inlineStr"/>
+      <c r="H47" s="2" t="inlineStr">
+        <is>
+          <t>_Not applicable as drug._ Relevance: deficient erythrocyte G6PD → reduced NADPH → impaired glutathione regeneration → oxidative haemolysis when exposed to 8-aminoquinolines [c:71068e68].</t>
+        </is>
+      </c>
+      <c r="I47" s="2" t="inlineStr"/>
+      <c r="J47" s="2" t="inlineStr"/>
+      <c r="K47" s="2" t="inlineStr"/>
+      <c r="L47" s="2" t="inlineStr"/>
+      <c r="M47" s="2" t="inlineStr"/>
+      <c r="N47" s="2" t="inlineStr"/>
+      <c r="O47" s="2" t="inlineStr"/>
+      <c r="P47" s="2" t="inlineStr"/>
+      <c r="Q47" s="2" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="B48" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="C48" s="2" t="inlineStr"/>
+      <c r="D48" s="2" t="inlineStr">
+        <is>
+          <t>Gametocyte</t>
+        </is>
+      </c>
+      <c r="E48" s="2" t="inlineStr">
+        <is>
+          <t>Gametocyte is the sexual-stage form of Plasmodium parasites, not a therapeutic agent. Current claim set classifies it as a lifecycle stage of [[plasmodium]] [c:22b09015] and specifically [[plasmodium-vivax]] [c:8ea029a7]. Entity has been routed to the medication template in error; downstream exporter should reclassify as `lifecycle_stage` or `parasitology_concept`. No pharmacological properties apply.</t>
+        </is>
+      </c>
+      <c r="F48" s="2" t="inlineStr"/>
+      <c r="G48" s="2" t="inlineStr"/>
+      <c r="H48" s="2" t="inlineStr">
+        <is>
+          <t>_Not a drug — no mechanism of action._ Biological role per current claims: sexual lifecycle stage of [[plasmodium]] (pending review) [c:22b09015] and [[plasmodium-vivax]] (pending review) [c:8ea029a7]. Egress site evidence noted in source [c:22b09015] but no mechanistic cascade in claim set.</t>
+        </is>
+      </c>
+      <c r="I48" s="2" t="inlineStr"/>
+      <c r="J48" s="2" t="inlineStr"/>
+      <c r="K48" s="2" t="inlineStr"/>
+      <c r="L48" s="2" t="inlineStr"/>
+      <c r="M48" s="2" t="inlineStr"/>
+      <c r="N48" s="2" t="inlineStr"/>
+      <c r="O48" s="2" t="inlineStr"/>
+      <c r="P48" s="2" t="inlineStr"/>
+      <c r="Q48" s="2" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="B49" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="C49" s="2" t="inlineStr"/>
+      <c r="D49" s="2" t="inlineStr">
+        <is>
+          <t>Global Warming</t>
+        </is>
+      </c>
+      <c r="E49" s="2" t="inlineStr">
+        <is>
+          <t>Global warming is long-term rise in Earth surface temperature driven by anthropogenic greenhouse gas emissions. Not a drug, biologic, or therapeutic agent. Entity miscategorised as `medication`; current claim corpus links it to malaria transmission risk in [[endemic-malaria-settings]] [c:7dffbd16] [c:644076a8]. Reclassify as `environmental-factor` or `risk-factor` upstream. Note retained only as placeholder pending reclassification.</t>
+        </is>
+      </c>
+      <c r="F49" s="2" t="inlineStr"/>
+      <c r="G49" s="2" t="inlineStr"/>
+      <c r="H49" s="2" t="inlineStr">
+        <is>
+          <t>_Not a pharmacologic mechanism._ Current claims describe ecological pathway: rising temperatures expand [[anopheles-vector]] range and shorten parasite extrinsic incubation period, raising [[malaria]] transmission risk (pending review) [c:7dffbd16] (evidence_grade: expert_opinion) [c:644076a8] (pending review).</t>
+        </is>
+      </c>
+      <c r="I49" s="2" t="inlineStr"/>
+      <c r="J49" s="2" t="inlineStr"/>
+      <c r="K49" s="2" t="inlineStr"/>
+      <c r="L49" s="2" t="inlineStr"/>
+      <c r="M49" s="2" t="inlineStr"/>
+      <c r="N49" s="2" t="inlineStr"/>
+      <c r="O49" s="2" t="inlineStr"/>
+      <c r="P49" s="2" t="inlineStr"/>
+      <c r="Q49" s="2" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="B50" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="C50" s="2" t="inlineStr"/>
+      <c r="D50" s="2" t="inlineStr">
+        <is>
+          <t>Hrp2 Based Rapid Diagnostic Tests</t>
+        </is>
+      </c>
+      <c r="E50" s="2" t="inlineStr">
+        <is>
+          <t>HRP2-based rapid diagnostic tests detect histidine-rich protein 2 secreted by [[plasmodium-falciparum]]. Lateral-flow immunoassay, finger-prick blood, ~15 min result. Mainstay of point-of-care falciparum diagnosis in [[endemic-malaria-settings]]. Performance now threatened by parasite strains evading HRP2 detection [c:7381fab5] [c:39b493f0] *(pending review)*.</t>
+        </is>
+      </c>
+      <c r="F50" s="2" t="inlineStr"/>
+      <c r="G50" s="2" t="inlineStr"/>
+      <c r="H50" s="2" t="inlineStr">
+        <is>
+          <t>Capture antibodies on nitrocellulose strip bind HRP2 antigen from lysed parasitized erythrocytes; gold-conjugated detection antibody yields visible test line.
+```mermaid
+flowchart LR
+    A[Blood + lysis buffer] --&gt; B[HRP2 antigen released]
+    B --&gt; C[Capture mAb binds HRP2]
+    C --&gt; D[Gold-conjugate detector binds]
+    D --&gt; E[Visible test line = P. falciparum positive]
+    F[pfhrp2/3 gene deletion or variant epitope] -.evades.-&gt; C
+```
+Resistance mechanism: [[plasmodium-falciparum]] strains with *pfhrp2*/*pfhrp3* gene deletions or epitope variation evade antigen capture, producing false negatives [c:7381fab5] (meta-analysis, endemic setting) [c:39b493f0] *(pending review)*.</t>
+        </is>
+      </c>
+      <c r="I50" s="2" t="inlineStr"/>
+      <c r="J50" s="2" t="inlineStr"/>
+      <c r="K50" s="2" t="inlineStr"/>
+      <c r="L50" s="2" t="inlineStr"/>
+      <c r="M50" s="2" t="inlineStr"/>
+      <c r="N50" s="2" t="inlineStr"/>
+      <c r="O50" s="2" t="inlineStr"/>
+      <c r="P50" s="2" t="inlineStr"/>
+      <c r="Q50" s="2" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="B51" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="C51" s="2" t="inlineStr">
+        <is>
+          <t>Infectious Disease</t>
+        </is>
+      </c>
+      <c r="D51" s="2" t="inlineStr">
+        <is>
+          <t>Human Malaria Infection</t>
+        </is>
+      </c>
+      <c r="E51" s="2" t="inlineStr">
+        <is>
+          <t>Human malaria infection is parasitic disease caused by *Plasmodium* protozoa. Current claim set names four causative species: [[plasmodium-knowlesi]] [c:b9b93eaf], [[plasmodium-malariae]] [c:f20e4cdb], [[plasmodium-ovale-curtisi]] [c:daed487c], and [[plasmodium-ovale-wallickeri]] [c:2d0c2e94]. *P. knowlesi* endemic across [[southeast-asia]] [c:dda6609e], notably [[malaysia]] [c:85d4c5cf]. Note: entity classified as "medication" in input, but claim corpus describes disease etiology only — no pharmacologic claims present.</t>
+        </is>
+      </c>
+      <c r="F51" s="2" t="inlineStr"/>
+      <c r="G51" s="2" t="inlineStr"/>
+      <c r="H51" s="2" t="inlineStr">
+        <is>
+          <t>_No drug mechanism claims in current corpus._ Causative-organism claims only:
+- [[plasmodium-knowlesi]] causes human malaria infection [c:b9b93eaf] (pending review)
+- [[plasmodium-malariae]] causes human malaria infection [c:f20e4cdb] (pending review)
+- [[plasmodium-ovale-curtisi]] causes human malaria infection [c:daed487c] (pending review)
+- [[plasmodium-ovale-wallickeri]] causes human malaria infection [c:2d0c2e94] (pending review)
+Regional etiology:
+- *P. knowlesi* endemic in [[malaysia]] [c:85d4c5cf] (pending review)
+- *P. knowlesi* endemic across [[southeast-asia]] [c:dda6609e] (pending review)</t>
+        </is>
+      </c>
+      <c r="I51" s="2" t="inlineStr"/>
+      <c r="J51" s="2" t="inlineStr"/>
+      <c r="K51" s="2" t="inlineStr"/>
+      <c r="L51" s="2" t="inlineStr"/>
+      <c r="M51" s="2" t="inlineStr"/>
+      <c r="N51" s="2" t="inlineStr"/>
+      <c r="O51" s="2" t="inlineStr"/>
+      <c r="P51" s="2" t="inlineStr"/>
+      <c r="Q51" s="2" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="B52" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="C52" s="2" t="inlineStr">
+        <is>
+          <t>Infectious Disease</t>
+        </is>
+      </c>
+      <c r="D52" s="2" t="inlineStr">
+        <is>
+          <t>Human Malaria</t>
+        </is>
+      </c>
+      <c r="E52" s="2" t="inlineStr">
+        <is>
+          <t>Human malaria is a protozoal infection caused by [[plasmodium]] parasites transmitted in endemic settings (pending review) [c:c42ef453]. Six species in the current corpus are implicated: [[plasmodium-falciparum]] [c:e5b88491], [[plasmodium-vivax]] [c:86bb8b28], [[plasmodium-malariae]] [c:91506620], [[plasmodium-ovale]] [c:a80fd411], and the zoonotic [[plasmodium-knowlesi]] in Southeast Asia [c:1663c012] [c:4b60c205]. Entity classified as "medication" by upstream hint, but claim set describes etiology only — no pharmacologic claims present.</t>
+        </is>
+      </c>
+      <c r="F52" s="2" t="inlineStr"/>
+      <c r="G52" s="2" t="inlineStr"/>
+      <c r="H52" s="2" t="inlineStr">
+        <is>
+          <t>_Not applicable — no pharmacologic mechanism. Etiologic mechanism (parasite → disease) summarized below from current claims._
+```mermaid
+flowchart LR
+  A[Plasmodium spp.] --&gt;|infects| B[Human host]
+  B --&gt; C[Human malaria]
+  A1[P. falciparum] --&gt; A
+  A2[P. vivax ~8% global cases] --&gt; A
+  A3[P. malariae] --&gt; A
+  A4[P. ovale] --&gt; A
+  A5[P. knowlesi - SE Asia] --&gt; A
+```
+Species contributions per current corpus (all pending review, expert_opinion grade):
+- [[plasmodium-falciparum]] — dominant share of global cases, exact value not stated [c:e5b88491]
+- [[plasmodium-vivax]] — ~8% of estimated global malaria cases [c:86bb8b28]
+- [[plasmodium-malariae]] [c:91506620], [[plasmodium-ovale]] [c:a80fd411] — endemic contributors, share unspecified
+- [[plasmodium-knowlesi]] — zoonotic, leading cause of human malaria in [[malaysia]] vs other Plasmodium spp. (moderate certainty) [c:9a4500e3]; endemic across Southeast Asia [c:1663c012] [c:1ffa0467] [c:4b60c205]</t>
+        </is>
+      </c>
+      <c r="I52" s="2" t="inlineStr"/>
+      <c r="J52" s="2" t="inlineStr"/>
+      <c r="K52" s="2" t="inlineStr"/>
+      <c r="L52" s="2" t="inlineStr"/>
+      <c r="M52" s="2" t="inlineStr"/>
+      <c r="N52" s="2" t="inlineStr"/>
+      <c r="O52" s="2" t="inlineStr"/>
+      <c r="P52" s="2" t="inlineStr"/>
+      <c r="Q52" s="2" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="B53" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="C53" s="2" t="inlineStr">
+        <is>
+          <t>Infectious Disease</t>
+        </is>
+      </c>
+      <c r="D53" s="2" t="inlineStr">
+        <is>
+          <t>Human Simian Malaria Infection</t>
+        </is>
+      </c>
+      <c r="E53" s="2" t="inlineStr">
+        <is>
+          <t>Entity mis-classified as medication. "Human simian malaria infection" = zoonotic malaria in humans caused by non-human-primate *Plasmodium* species. Current claims name [[plasmodium-inui]] [c:9b4f8255] (pending review) and [[plasmodium-cynomolgi]] [c:1bd8d4d2] (pending review) as causative agents in [[southeast-asia]] endemic settings. No therapeutic agent claims in corpus.</t>
+        </is>
+      </c>
+      <c r="F53" s="2" t="inlineStr"/>
+      <c r="G53" s="2" t="inlineStr"/>
+      <c r="H53" s="2" t="inlineStr">
+        <is>
+          <t>_No mechanism-of-action claims. Causative organisms only:_
+- [[plasmodium-inui]] causes human simian malaria infection in Southeast Asia, endemic setting [c:9b4f8255] (expert_opinion, pending review)
+- [[plasmodium-cynomolgi]] causes human simian malaria infection in Southeast Asia, endemic setting [c:1bd8d4d2] (expert_opinion, pending review)</t>
+        </is>
+      </c>
+      <c r="I53" s="2" t="inlineStr"/>
+      <c r="J53" s="2" t="inlineStr"/>
+      <c r="K53" s="2" t="inlineStr"/>
+      <c r="L53" s="2" t="inlineStr"/>
+      <c r="M53" s="2" t="inlineStr"/>
+      <c r="N53" s="2" t="inlineStr"/>
+      <c r="O53" s="2" t="inlineStr"/>
+      <c r="P53" s="2" t="inlineStr"/>
+      <c r="Q53" s="2" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="B54" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="C54" s="2" t="inlineStr">
+        <is>
+          <t>Infectious Disease</t>
+        </is>
+      </c>
+      <c r="D54" s="2" t="inlineStr">
+        <is>
+          <t>Human Zoonotic Malaria Infection</t>
+        </is>
+      </c>
+      <c r="E54" s="2" t="inlineStr">
+        <is>
+          <t>Human zoonotic malaria = malaria infection in humans caused by *Plasmodium* species whose natural reservoir is non-human primates. In Southeast Asia, simian species cross species barrier into humans in endemic settings [c:a04673e7] (pending review) [c:4a688a6e] (pending review). Entity classified as "medication" in source schema but corpus describes disease etiology, not therapeutic agent.</t>
+        </is>
+      </c>
+      <c r="F54" s="2" t="inlineStr"/>
+      <c r="G54" s="2" t="inlineStr"/>
+      <c r="H54" s="2" t="inlineStr">
+        <is>
+          <t>_Not applicable to medication framing._ Etiologic mechanism per current claims:
+- [[plasmodium-inui]] causes human zoonotic malaria in Southeast Asia, endemic setting; certainty very_low, expert opinion [c:a04673e7] (pending review).
+- [[plasmodium-cynomolgi]] causes human zoonotic malaria in Southeast Asia, endemic setting; certainty low, expert opinion [c:4a688a6e] (pending review).
+```mermaid
+flowchart LR
+  A[Macaque reservoir] --&gt; B[Anopheles vector bite]
+  B --&gt; C[Human host]
+  C --&gt; D[Zoonotic malaria infection]
+```
+Diagram inferred from disease ecology context of cited source; load-bearing etiologic links cited [c:a04673e7] [c:4a688a6e].</t>
+        </is>
+      </c>
+      <c r="I54" s="2" t="inlineStr"/>
+      <c r="J54" s="2" t="inlineStr"/>
+      <c r="K54" s="2" t="inlineStr"/>
+      <c r="L54" s="2" t="inlineStr"/>
+      <c r="M54" s="2" t="inlineStr"/>
+      <c r="N54" s="2" t="inlineStr"/>
+      <c r="O54" s="2" t="inlineStr"/>
+      <c r="P54" s="2" t="inlineStr"/>
+      <c r="Q54" s="2" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="B55" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="C55" s="2" t="inlineStr"/>
+      <c r="D55" s="2" t="inlineStr">
+        <is>
+          <t>Humans</t>
+        </is>
+      </c>
+      <c r="E55" s="2" t="inlineStr">
+        <is>
+          <t>Entity "humans" mis-classified as medication. Current claim set describes zoonotic *Plasmodium* species affecting human hosts in Southeast Asia and Malaysia — host exposure claims, not pharmacologic claims. No medication facts derivable. Recommend reclassify to host/population entity or condition entity. Claims below preserved for traceability.</t>
+        </is>
+      </c>
+      <c r="F55" s="2" t="inlineStr"/>
+      <c r="G55" s="2" t="inlineStr"/>
+      <c r="H55" s="2" t="inlineStr">
+        <is>
+          <t>_No mechanism claims in current corpus._</t>
+        </is>
+      </c>
+      <c r="I55" s="2" t="inlineStr"/>
+      <c r="J55" s="2" t="inlineStr"/>
+      <c r="K55" s="2" t="inlineStr"/>
+      <c r="L55" s="2" t="inlineStr"/>
+      <c r="M55" s="2" t="inlineStr"/>
+      <c r="N55" s="2" t="inlineStr"/>
+      <c r="O55" s="2" t="inlineStr"/>
+      <c r="P55" s="2" t="inlineStr"/>
+      <c r="Q55" s="2" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="B56" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="C56" s="2" t="inlineStr"/>
+      <c r="D56" s="2" t="inlineStr">
+        <is>
+          <t>Hypoglycemia</t>
+        </is>
+      </c>
+      <c r="E56" s="2" t="inlineStr">
+        <is>
+          <t>Entity misclassified as medication. Hypoglycemia = low blood glucose state, not therapeutic agent. Current corpus describes it as (a) co-occurring feature of severe falciparum malaria and (b) adverse effect of intravenous quinine. No medication note possible. Sections below preserve schema; substance limited to what claims support.</t>
+        </is>
+      </c>
+      <c r="F56" s="2" t="inlineStr"/>
+      <c r="G56" s="2" t="inlineStr"/>
+      <c r="H56" s="2" t="inlineStr">
+        <is>
+          <t>_Not applicable — entity is not a drug._ Causal upstream in current corpus: [[intravenous-quinine]] induces hypoglycemia in inpatient setting (pending review) [c:f20e32c8]. Co-occurs with disturbed consciousness in [[falciparum-malaria]] (pending review) [c:2fb8ba7a].</t>
+        </is>
+      </c>
+      <c r="I56" s="2" t="inlineStr"/>
+      <c r="J56" s="2" t="inlineStr"/>
+      <c r="K56" s="2" t="inlineStr"/>
+      <c r="L56" s="2" t="inlineStr"/>
+      <c r="M56" s="2" t="inlineStr"/>
+      <c r="N56" s="2" t="inlineStr"/>
+      <c r="O56" s="2" t="inlineStr"/>
+      <c r="P56" s="2" t="inlineStr"/>
+      <c r="Q56" s="2" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="B57" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="C57" s="2" t="inlineStr"/>
+      <c r="D57" s="2" t="inlineStr">
+        <is>
+          <t>Impaired Infant Neurocognitive Development</t>
+        </is>
+      </c>
+      <c r="E57" s="2" t="inlineStr">
+        <is>
+          <t>Impaired infant neurocognitive development is a developmental sequela observed in infants of mothers exposed to [[plasmodium-falciparum]] during pregnancy in endemic settings. Current corpus links the outcome to maternal infection rather than to any therapeutic agent [c:c75fe6bf] [c:c260dcf0] _(pending review)_.</t>
+        </is>
+      </c>
+      <c r="F57" s="2" t="inlineStr"/>
+      <c r="G57" s="2" t="inlineStr"/>
+      <c r="H57" s="2" t="inlineStr">
+        <is>
+          <t>_No pharmacological mechanism — outcome, not drug._ Causal pathway in corpus:
+```mermaid
+flowchart LR
+    A[Maternal P. falciparum infection] --&gt; B[Placental sequestration / inflammation]
+    B --&gt; C[Adverse intrauterine environment]
+    C --&gt; D[Impaired infant neurocognitive development]
+```
+Corpus supports endpoint A → D only [c:c75fe6bf] [c:c260dcf0]; intermediate steps B and C are template scaffolding, not claim-backed.</t>
+        </is>
+      </c>
+      <c r="I57" s="2" t="inlineStr"/>
+      <c r="J57" s="2" t="inlineStr"/>
+      <c r="K57" s="2" t="inlineStr"/>
+      <c r="L57" s="2" t="inlineStr"/>
+      <c r="M57" s="2" t="inlineStr"/>
+      <c r="N57" s="2" t="inlineStr"/>
+      <c r="O57" s="2" t="inlineStr"/>
+      <c r="P57" s="2" t="inlineStr"/>
+      <c r="Q57" s="2" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="B58" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="C58" s="2" t="inlineStr">
+        <is>
+          <t>Infectious Disease</t>
+        </is>
+      </c>
+      <c r="D58" s="2" t="inlineStr">
+        <is>
+          <t>Imported Malaria</t>
+        </is>
+      </c>
+      <c r="E58" s="2" t="inlineStr">
+        <is>
+          <t>Imported malaria = [[malaria]] diagnosed in travelers returning from endemic regions to non-endemic countries. UK and Netherlands data dominate current claim set. Predominantly [[plasmodium-falciparum]] in UK returnees [c:4c726444]. Netherlands sees ~250 cases/year (CI 200–300) in immune-naive population [c:2bdb5b2c] (pending review). UK reports 2–11 deaths annually among travelers [c:57848b90] (pending review).</t>
+        </is>
+      </c>
+      <c r="F58" s="2" t="inlineStr"/>
+      <c r="G58" s="2" t="inlineStr"/>
+      <c r="H58" s="2" t="inlineStr">
+        <is>
+          <t>_Not applicable. Pathogen mechanism belongs in [[plasmodium-falciparum]] note._</t>
+        </is>
+      </c>
+      <c r="I58" s="2" t="inlineStr"/>
+      <c r="J58" s="2" t="inlineStr"/>
+      <c r="K58" s="2" t="inlineStr"/>
+      <c r="L58" s="2" t="inlineStr"/>
+      <c r="M58" s="2" t="inlineStr"/>
+      <c r="N58" s="2" t="inlineStr"/>
+      <c r="O58" s="2" t="inlineStr"/>
+      <c r="P58" s="2" t="inlineStr"/>
+      <c r="Q58" s="2" t="inlineStr"/>
+    </row>
+    <row r="59">
+      <c r="A59" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="B59" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="C59" s="2" t="inlineStr">
+        <is>
+          <t>Infectious Disease</t>
+        </is>
+      </c>
+      <c r="D59" s="2" t="inlineStr">
+        <is>
+          <t>Increased Malaria Transmission Risk</t>
+        </is>
+      </c>
+      <c r="E59" s="2" t="inlineStr">
+        <is>
+          <t>"Increased malaria transmission risk" is not a drug. It is a population-level outcome in [[endemic-malaria]] settings, driven by ecosystem change, political instability, and reduced vector-control funding [c:5a248841] (pending review). Current claim set contains no pharmacological agent — medication template fields below are intentionally empty.</t>
+        </is>
+      </c>
+      <c r="F59" s="2" t="inlineStr"/>
+      <c r="G59" s="2" t="inlineStr"/>
+      <c r="H59" s="2" t="inlineStr">
+        <is>
+          <t>_Not applicable._ No pharmacological mechanism. Driver cascade from claim corpus:
+```mermaid
+graph LR
+  A[ecosystem change] --&gt; D[increased transmission risk]
+  B[political instability] --&gt; D
+  C[reduced vector-control funding] --&gt; D
+  D --&gt; E[higher case incidence in endemic regions]
+```
+Multifactorial driver model exceeds temperature-only explanation [c:5a248841].</t>
+        </is>
+      </c>
+      <c r="I59" s="2" t="inlineStr">
+        <is>
+          <t>**Therapeutic category:** Not applicable — entity is an epidemiological outcome, not a medication
+**Drug group:** _Not applicable._
+**Drug class:** _Not applicable._
+**Controlled substance:** _Not applicable._</t>
+        </is>
+      </c>
+      <c r="J59" s="2" t="inlineStr"/>
+      <c r="K59" s="2" t="inlineStr"/>
+      <c r="L59" s="2" t="inlineStr"/>
+      <c r="M59" s="2" t="inlineStr"/>
+      <c r="N59" s="2" t="inlineStr"/>
+      <c r="O59" s="2" t="inlineStr"/>
+      <c r="P59" s="2" t="inlineStr"/>
+      <c r="Q59" s="2" t="inlineStr"/>
+    </row>
+    <row r="60">
+      <c r="A60" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="B60" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="C60" s="2" t="inlineStr">
+        <is>
+          <t>Infectious Disease</t>
+        </is>
+      </c>
+      <c r="D60" s="2" t="inlineStr">
+        <is>
+          <t>Increased Risk Of Malaria Transmission</t>
+        </is>
+      </c>
+      <c r="E60" s="2" t="inlineStr">
+        <is>
+          <t>"Increased risk of [[malaria-transmission]]" is not a medication. It is an epidemiological outcome linked to [[anthropogenic-global-warming]] in [[malaria-endemic-regions]] [c:7dffbd16] [c:15f0d886]. Current claim corpus contains no pharmacological data for this entity — only causal climate-health claims. Note rendered under medication template per request, but pharmacology sections cannot be populated from present claims (pending review).</t>
+        </is>
+      </c>
+      <c r="F60" s="2" t="inlineStr"/>
+      <c r="G60" s="2" t="inlineStr"/>
+      <c r="H60" s="2" t="inlineStr">
+        <is>
+          <t>Entity is a risk state, not an agent. Driver claims:
+```mermaid
+graph TD
+  A[Global warming / anthropogenic] --&gt;|expert_opinion| B[Vector range + season expansion]
+  B --&gt; C[Endemic transmission increase]
+  C --&gt; D[Increased risk of malaria transmission]
+```
+Climate–transmission linkage supported [c:7dffbd16] [c:644076a8] [c:15f0d886] (all evidence_grade=expert_opinion, certainty=moderate, pending review). Vector and parasite biology steps inferred from claim context, not directly asserted.</t>
+        </is>
+      </c>
+      <c r="I60" s="2" t="inlineStr">
+        <is>
+          <t>**Therapeutic category:** Not applicable — entity is an epidemiological risk outcome, not a pharmacological agent
+**Drug group:** Not applicable
+**Drug class:** Not applicable
+**Controlled substance:** Not applicable</t>
+        </is>
+      </c>
+      <c r="J60" s="2" t="inlineStr"/>
+      <c r="K60" s="2" t="inlineStr"/>
+      <c r="L60" s="2" t="inlineStr"/>
+      <c r="M60" s="2" t="inlineStr"/>
+      <c r="N60" s="2" t="inlineStr"/>
+      <c r="O60" s="2" t="inlineStr"/>
+      <c r="P60" s="2" t="inlineStr"/>
+      <c r="Q60" s="2" t="inlineStr"/>
+    </row>
+    <row r="61">
+      <c r="A61" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="B61" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="C61" s="2" t="inlineStr"/>
+      <c r="D61" s="2" t="inlineStr">
+        <is>
+          <t>India Population</t>
+        </is>
+      </c>
+      <c r="E61" s="2" t="inlineStr">
+        <is>
+          <t>"India population" is not a therapeutic agent. Current corpus contains only epidemiological claims where India population serves as the affected denominator for [[malaria]] burden estimates [c:3e18b4e4] [c:46afc788] (pending review). No pharmacological data exists for this entity. Note retained as placeholder; reclassify entity_type from `medication` to `population` or `epidemiology` upstream.</t>
+        </is>
+      </c>
+      <c r="F61" s="2" t="inlineStr"/>
+      <c r="G61" s="2" t="inlineStr"/>
+      <c r="H61" s="2" t="inlineStr">
+        <is>
+          <t>_No mechanism claims in current corpus._</t>
+        </is>
+      </c>
+      <c r="I61" s="2" t="inlineStr"/>
+      <c r="J61" s="2" t="inlineStr"/>
+      <c r="K61" s="2" t="inlineStr"/>
+      <c r="L61" s="2" t="inlineStr"/>
+      <c r="M61" s="2" t="inlineStr"/>
+      <c r="N61" s="2" t="inlineStr"/>
+      <c r="O61" s="2" t="inlineStr"/>
+      <c r="P61" s="2" t="inlineStr"/>
+      <c r="Q61" s="2" t="inlineStr"/>
+    </row>
+    <row r="62">
+      <c r="A62" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="B62" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="C62" s="2" t="inlineStr"/>
+      <c r="D62" s="2" t="inlineStr">
+        <is>
+          <t>Indoor Residual Spraying</t>
+        </is>
+      </c>
+      <c r="E62" s="2" t="inlineStr">
+        <is>
+          <t>IRS is application of long-acting insecticide to interior walls and ceilings of dwellings to kill resting endophilic *Anopheles* vectors. Deployed at community scale in [[malaria]]-endemic settings, alone or layered with [[insecticide-treated-nets]]. Effect depends on chemical class, vector resistance, and net coverage [c:0496d512] [c:016dcd00].</t>
+        </is>
+      </c>
+      <c r="F62" s="2" t="inlineStr"/>
+      <c r="G62" s="2" t="inlineStr"/>
+      <c r="H62" s="2" t="inlineStr">
+        <is>
+          <t>Residual insecticide deposited on wall surfaces contacts endophilic [[anopheles]] mosquitoes resting indoors after blood-feeding. Contact toxicity kills vector before sporogonic cycle completes, breaking human-mosquito-human transmission chain.
+```mermaid
+flowchart LR
+    A[IRS deposit on wall] --&gt; B[Resting Anopheles tarsal contact]
+    B --&gt; C[Insecticide uptake]
+    C --&gt; D[Vector mortality pre-sporogony]
+    D --&gt; E[Reduced entomological inoculation rate]
+    E --&gt; F[Lower parasite prevalence / incidence]
+```
+Mechanism inferred from population-level effect on parasite prevalence [c:b8dc9e27] and falciparum infection [c:016dcd00].</t>
+        </is>
+      </c>
+      <c r="I62" s="2" t="inlineStr"/>
+      <c r="J62" s="2" t="inlineStr"/>
+      <c r="K62" s="2" t="inlineStr"/>
+      <c r="L62" s="2" t="inlineStr"/>
+      <c r="M62" s="2" t="inlineStr"/>
+      <c r="N62" s="2" t="inlineStr"/>
+      <c r="O62" s="2" t="inlineStr"/>
+      <c r="P62" s="2" t="inlineStr"/>
+      <c r="Q62" s="2" t="inlineStr"/>
+    </row>
+    <row r="63">
+      <c r="A63" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="B63" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="C63" s="2" t="inlineStr"/>
+      <c r="D63" s="2" t="inlineStr">
+        <is>
+          <t>Inflammatory Mediators</t>
+        </is>
+      </c>
+      <c r="E63" s="2" t="inlineStr">
+        <is>
+          <t>Inflammatory mediators (cytokines, chemokines) are endogenous signaling molecules, not administered drugs. In current corpus, implicated in [[cerebral-malaria]] pathogenesis: drive [[neuroinflammation]] [c:327c6bed] and increase [[blood-brain-barrier]] permeability [c:8928d809] in inpatient endemic settings. Listed here only because upstream classifier tagged entity as `medication`; reclassification to `pathophysiological-mediator` recommended.</t>
+        </is>
+      </c>
+      <c r="F63" s="2" t="inlineStr"/>
+      <c r="G63" s="2" t="inlineStr"/>
+      <c r="H63" s="2" t="inlineStr">
+        <is>
+          <t>In severe/cerebral malaria (inpatient, endemic), inflammatory mediators drive two load-bearing downstream effects (pending review):
+```mermaid
+flowchart LR
+    A[inflammatory mediators] --&gt; B[neuroinflammation]
+    A --&gt; C[BBB permeability ↑]
+    B --&gt; D[cerebral malaria pathology]
+    C --&gt; D
+```
+- Cause [[neuroinflammation]] [c:327c6bed] (expert_opinion, moderate certainty, pending review).
+- Cause increased [[blood-brain-barrier]] permeability [c:8928d809] (expert_opinion, moderate certainty, pending review).</t>
+        </is>
+      </c>
+      <c r="I63" s="2" t="inlineStr"/>
+      <c r="J63" s="2" t="inlineStr"/>
+      <c r="K63" s="2" t="inlineStr"/>
+      <c r="L63" s="2" t="inlineStr"/>
+      <c r="M63" s="2" t="inlineStr"/>
+      <c r="N63" s="2" t="inlineStr"/>
+      <c r="O63" s="2" t="inlineStr"/>
+      <c r="P63" s="2" t="inlineStr"/>
+      <c r="Q63" s="2" t="inlineStr"/>
+    </row>
+    <row r="64">
+      <c r="A64" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="B64" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="C64" s="2" t="inlineStr"/>
+      <c r="D64" s="2" t="inlineStr">
+        <is>
+          <t>Insecticide Treated Bed Nets</t>
+        </is>
+      </c>
+      <c r="E64" s="2" t="inlineStr">
+        <is>
+          <t>Insecticide-treated bed nets (ITNs) are mesh nets impregnated with pyrethroid insecticide, hung over sleeping spaces in malaria-endemic areas. Dual action: physical barrier against night-biting *Anopheles* mosquitoes plus insecticidal kill on contact. Frontline community-level prevention tool for [[malaria]] in endemic regions, including pregnant women.</t>
+        </is>
+      </c>
+      <c r="F64" s="2" t="inlineStr"/>
+      <c r="G64" s="2" t="inlineStr"/>
+      <c r="H64" s="2" t="inlineStr">
+        <is>
+          <t>Physical mesh barrier blocks mosquito access to sleeping host. Pyrethroid coating delivers contact toxicity to *Anopheles* vectors that land on net, reducing vector density and personal biting rate. Net effect: lower [[plasmodium-falciparum]] inoculation rate at household and community level [c:7c8c484b] (pending review).</t>
+        </is>
+      </c>
+      <c r="I64" s="2" t="inlineStr"/>
+      <c r="J64" s="2" t="inlineStr"/>
+      <c r="K64" s="2" t="inlineStr"/>
+      <c r="L64" s="2" t="inlineStr"/>
+      <c r="M64" s="2" t="inlineStr"/>
+      <c r="N64" s="2" t="inlineStr"/>
+      <c r="O64" s="2" t="inlineStr"/>
+      <c r="P64" s="2" t="inlineStr"/>
+      <c r="Q64" s="2" t="inlineStr"/>
+    </row>
+    <row r="65">
+      <c r="A65" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="B65" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="C65" s="2" t="inlineStr"/>
+      <c r="D65" s="2" t="inlineStr">
+        <is>
+          <t>Insecticide Treated Bednets</t>
+        </is>
+      </c>
+      <c r="E65" s="2" t="inlineStr">
+        <is>
+          <t>Insecticide-treated bednets (ITNs) are mesh sleeping nets impregnated with pyrethroid insecticide. Deployed over sleeping spaces in malaria-endemic settings to block and kill anopheline mosquito vectors during peak nocturnal biting. Core community-level prevention tool against [[plasmodium-falciparum-malaria]].</t>
+        </is>
+      </c>
+      <c r="F65" s="2" t="inlineStr"/>
+      <c r="G65" s="2" t="inlineStr"/>
+      <c r="H65" s="2" t="inlineStr">
+        <is>
+          <t>Physical barrier + contact insecticide. Net mesh blocks mosquito access to sleeper. Pyrethroid coating kills or repels [[anopheles-mosquito]] on contact, reducing vector lifespan and community-level transmission of [[plasmodium-falciparum]] [c:f8d17229] (pending review).
+```mermaid
+graph LR
+  A[ITN deployment over sleeping space] --&gt; B[Physical barrier blocks bite]
+  A --&gt; C[Pyrethroid contact kills vector]
+  B --&gt; D[Reduced individual exposure]
+  C --&gt; E[Reduced vector density]
+  D --&gt; F[Lower malaria incidence]
+  E --&gt; F
+```</t>
+        </is>
+      </c>
+      <c r="I65" s="2" t="inlineStr"/>
+      <c r="J65" s="2" t="inlineStr"/>
+      <c r="K65" s="2" t="inlineStr"/>
+      <c r="L65" s="2" t="inlineStr"/>
+      <c r="M65" s="2" t="inlineStr"/>
+      <c r="N65" s="2" t="inlineStr"/>
+      <c r="O65" s="2" t="inlineStr"/>
+      <c r="P65" s="2" t="inlineStr"/>
+      <c r="Q65" s="2" t="inlineStr"/>
+    </row>
+    <row r="66">
+      <c r="A66" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="B66" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="C66" s="2" t="inlineStr"/>
+      <c r="D66" s="2" t="inlineStr">
+        <is>
+          <t>Insecticide Treated Nets</t>
+        </is>
+      </c>
+      <c r="E66" s="2" t="inlineStr">
+        <is>
+          <t>ITN = bed net treated with pyrethroid insecticide. Physical barrier blocks mosquito contact during sleep; insecticide kills/repels vectors landing on net. Core WHO malaria-prevention tool in endemic settings, including pregnancy. Distributed at community level [c:fca1155d].</t>
+        </is>
+      </c>
+      <c r="F66" s="2" t="inlineStr"/>
+      <c r="G66" s="2" t="inlineStr"/>
+      <c r="H66" s="2" t="inlineStr">
+        <is>
+          <t>Pyrethroid insecticide ([[pyrethroid]]) bound to net fibers; mosquito contact triggers neurotoxicity via voltage-gated sodium-channel disruption → vector knockdown/death. Physical mesh blocks host-seeking *Anopheles* during peak biting (night). Combined effect reduces human-vector contact and vector population density [c:fca1155d].
+```mermaid
+graph LR
+  A[Pyrethroid-treated mesh] --&gt; B[Physical barrier blocks bite]
+  A --&gt; C[Contact insecticide kills Anopheles]
+  C --&gt; D[Reduced vector density]
+  B --&gt; E[Reduced human-vector contact]
+  D --&gt; F[Lower malaria transmission]
+  E --&gt; F
+  F --&gt; G[Prevented malaria, placental malaria, low birth weight]
+```
+[c:fca1155d]</t>
+        </is>
+      </c>
+      <c r="I66" s="2" t="inlineStr"/>
+      <c r="J66" s="2" t="inlineStr"/>
+      <c r="K66" s="2" t="inlineStr"/>
+      <c r="L66" s="2" t="inlineStr"/>
+      <c r="M66" s="2" t="inlineStr"/>
+      <c r="N66" s="2" t="inlineStr"/>
+      <c r="O66" s="2" t="inlineStr"/>
+      <c r="P66" s="2" t="inlineStr"/>
+      <c r="Q66" s="2" t="inlineStr"/>
+    </row>
+    <row r="67">
+      <c r="A67" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="B67" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="C67" s="2" t="inlineStr"/>
+      <c r="D67" s="2" t="inlineStr">
+        <is>
+          <t>Insecticides</t>
+        </is>
+      </c>
+      <c r="E67" s="2" t="inlineStr">
+        <is>
+          <t>Insecticides target [[anopheles-mosquito]] vectors of [[malaria]], deployed via indoor residual spraying (IRS) and insecticide-treated nets (ITNs). Not a patient-administered medication — class entry retained for vector-control linkage. Resistance in *Anopheles* populations now widespread in endemic settings, threatening control programs (pending review) [c:13a80bce][c:5270b8a2].</t>
+        </is>
+      </c>
+      <c r="F67" s="2" t="inlineStr"/>
+      <c r="G67" s="2" t="inlineStr"/>
+      <c r="H67" s="2" t="inlineStr">
+        <is>
+          <t>Class-dependent neurotoxicity on arthropod targets — pyrethroids/DDT on voltage-gated sodium channels, carbamates/organophosphates on acetylcholinesterase. Resistance arises via target-site mutations and metabolic detoxification in [[anopheles-mosquito]] populations (pending review, expert_opinion) [c:13a80bce].
+```mermaid
+flowchart LR
+  A[Insecticide contact] --&gt; B[Neural target binding]
+  B --&gt; C[Vector mortality]
+  C --&gt; D[Reduced transmission]
+  E[Resistance alleles] -.blocks.-&gt; B
+```
+Resistance cascade load-bearing [c:13a80bce][c:02d86a46][c:5270b8a2].</t>
+        </is>
+      </c>
+      <c r="I67" s="2" t="inlineStr"/>
+      <c r="J67" s="2" t="inlineStr"/>
+      <c r="K67" s="2" t="inlineStr"/>
+      <c r="L67" s="2" t="inlineStr"/>
+      <c r="M67" s="2" t="inlineStr"/>
+      <c r="N67" s="2" t="inlineStr"/>
+      <c r="O67" s="2" t="inlineStr"/>
+      <c r="P67" s="2" t="inlineStr"/>
+      <c r="Q67" s="2" t="inlineStr"/>
+    </row>
+    <row r="68">
+      <c r="A68" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="B68" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="C68" s="2" t="inlineStr">
+        <is>
+          <t>Infectious Disease</t>
+        </is>
+      </c>
+      <c r="D68" s="2" t="inlineStr">
+        <is>
+          <t>Interaction Between Human Host Anopheles Vector And Plasmodium Parasite</t>
+        </is>
+      </c>
+      <c r="E68" s="2" t="inlineStr">
+        <is>
+          <t>Not a pharmacological agent. Refers to tripartite biological interaction among [[human-host]], [[anopheles-vector]], [[plasmodium-parasite]] required for [[malaria]] transmission in endemic settings [c:3e9f52d3] [c:0494067c] (pending review).</t>
+        </is>
+      </c>
+      <c r="F68" s="2" t="inlineStr"/>
+      <c r="G68" s="2" t="inlineStr"/>
+      <c r="H68" s="2" t="inlineStr">
+        <is>
+          <t>Transmission cycle, not drug mechanism. Efficient malaria transmission requires concurrent interaction of human host, Anopheles vector, Plasmodium parasite [c:3e9f52d3] (expert_opinion, pending review). General malaria transmission carries same tripartite requirement [c:0494067c] (expert_opinion, pending review).
+```mermaid
+flowchart LR
+  P[Plasmodium parasite] --&gt;|sporozoites via bite| H[Human host]
+  H --&gt;|gametocytes in blood meal| V[Anopheles vector]
+  V --&gt;|sporogony| P
+```
+[c:3e9f52d3]</t>
+        </is>
+      </c>
+      <c r="I68" s="2" t="inlineStr"/>
+      <c r="J68" s="2" t="inlineStr"/>
+      <c r="K68" s="2" t="inlineStr"/>
+      <c r="L68" s="2" t="inlineStr"/>
+      <c r="M68" s="2" t="inlineStr"/>
+      <c r="N68" s="2" t="inlineStr"/>
+      <c r="O68" s="2" t="inlineStr"/>
+      <c r="P68" s="2" t="inlineStr"/>
+      <c r="Q68" s="2" t="inlineStr"/>
+    </row>
+    <row r="69">
+      <c r="A69" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="B69" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="C69" s="2" t="inlineStr"/>
+      <c r="D69" s="2" t="inlineStr">
+        <is>
+          <t>Intermittent Preventive Treatment</t>
+        </is>
+      </c>
+      <c r="E69" s="2" t="inlineStr">
+        <is>
+          <t>Intermittent preventive treatment (IPT) = scheduled full therapeutic doses of antimalarial given at fixed intervals to at-risk groups regardless of infection status. Two main programs: IPT in pregnancy (IPTp) for [[uncomplicated-falciparum-malaria]] prevention in 2nd/3rd trimester [c:0190c9cf], and IPT in infants (IPTi) for pediatric malaria prevention in endemic zones [c:a31655bc]. Strategy, not single drug — partner agents (e.g. [[sulfadoxine-pyrimethamine]]) listed separately.</t>
+        </is>
+      </c>
+      <c r="F69" s="2" t="inlineStr"/>
+      <c r="G69" s="2" t="inlineStr"/>
+      <c r="H69" s="2" t="inlineStr">
+        <is>
+          <t>IPT delivers full curative dose of antimalarial at scheduled antenatal/immunization contacts. Clears existing sub-clinical [[plasmodium-falciparum]] parasitemia + provides post-treatment prophylactic window via residual drug levels. Pregnancy benefit tied to reducing placental sequestration in 2nd/3rd trimester when risk peaks [c:0190c9cf]. Infant benefit tied to coverage during peak transmission exposure age [c:a31655bc]. Drug-specific mechanism depends on partner agent — not specified in current claim set.</t>
+        </is>
+      </c>
+      <c r="I69" s="2" t="inlineStr"/>
+      <c r="J69" s="2" t="inlineStr"/>
+      <c r="K69" s="2" t="inlineStr"/>
+      <c r="L69" s="2" t="inlineStr"/>
+      <c r="M69" s="2" t="inlineStr">
+        <is>
+          <t>**Therapeutic category:** Antimalarial chemoprevention
+**Drug group:** Public-health chemoprevention strategy (not single agent)
+**Drug class:** Scheduled full-dose antimalarial regimen (drug varies by program)
+**Controlled substance:** No</t>
+        </is>
+      </c>
+      <c r="N69" s="2" t="inlineStr"/>
+      <c r="O69" s="2" t="inlineStr"/>
+      <c r="P69" s="2" t="inlineStr"/>
+      <c r="Q69" s="2" t="inlineStr"/>
+    </row>
+    <row r="70">
+      <c r="A70" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="B70" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="C70" s="2" t="inlineStr"/>
+      <c r="D70" s="2" t="inlineStr">
+        <is>
+          <t>Iron Folic Acid Supplementation</t>
+        </is>
+      </c>
+      <c r="E70" s="2" t="inlineStr">
+        <is>
+          <t>Fixed-dose oral combination of elemental iron and folic acid used routinely in antenatal care. Daily supplementation in the second and third trimesters reduces [[maternal-anaemia]], [[low-birthweight]], and [[preterm-birth]] [c:39bdfd76][c:77b59495][c:6c0c06b1]. Standard component of WHO antenatal micronutrient regimens.</t>
+        </is>
+      </c>
+      <c r="F70" s="2" t="inlineStr"/>
+      <c r="G70" s="2" t="inlineStr"/>
+      <c r="H70" s="2" t="inlineStr">
+        <is>
+          <t>Elemental iron replenishes erythropoietic iron stores → supports haemoglobin synthesis → corrects/prevents iron-deficiency anaemia. [[folic-acid]] supplies one-carbon units for purine/thymidylate synthesis → supports erythropoiesis and fetal tissue growth. Combined effect on maternal haematology plausibly mediates downstream reductions in low birthweight and preterm birth [c:77b59495][c:6c0c06b1].
+```mermaid
+flowchart LR
+  A[Oral Fe + folate] --&gt; B[Restore Fe stores + 1-C units]
+  B --&gt; C[Haemoglobin synthesis ↑]
+  C --&gt; D[Maternal anaemia ↓]
+  D --&gt; E[Low birthweight ↓ / Preterm birth ↓]
+```</t>
+        </is>
+      </c>
+      <c r="I70" s="2" t="inlineStr"/>
+      <c r="J70" s="2" t="inlineStr"/>
+      <c r="K70" s="2" t="inlineStr"/>
+      <c r="L70" s="2" t="inlineStr"/>
+      <c r="M70" s="2" t="inlineStr"/>
+      <c r="N70" s="2" t="inlineStr"/>
+      <c r="O70" s="2" t="inlineStr"/>
+      <c r="P70" s="2" t="inlineStr"/>
+      <c r="Q70" s="2" t="inlineStr"/>
+    </row>
+    <row r="71">
+      <c r="A71" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="B71" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="C71" s="2" t="inlineStr"/>
+      <c r="D71" s="2" t="inlineStr">
+        <is>
+          <t>Itn Ownership</t>
+        </is>
+      </c>
+      <c r="E71" s="2" t="inlineStr">
+        <is>
+          <t>ITN ownership denotes household possession of an insecticide-treated net for [[malaria-prevention]]. Note: classifier tagged this entity as "medication" but it is a vector-control commodity, not a drug. Current claim set covers sociodemographic correlates of ownership in [[ghana]], not pharmacology. Dose, mechanism, contraindication, and interaction fields are not applicable to a bed net and no such claims exist in the corpus.</t>
+        </is>
+      </c>
+      <c r="F71" s="2" t="inlineStr"/>
+      <c r="G71" s="2" t="inlineStr"/>
+      <c r="H71" s="2" t="inlineStr">
+        <is>
+          <t>_No mechanism claims in current corpus._ (Out-of-corpus context: pyrethroid contact insecticide on netting kills/repels *Anopheles* vectors; physical barrier blocks bites during sleep — not cited because unsupported by claim set.)</t>
+        </is>
+      </c>
+      <c r="I71" s="2" t="inlineStr"/>
+      <c r="J71" s="2" t="inlineStr"/>
+      <c r="K71" s="2" t="inlineStr"/>
+      <c r="L71" s="2" t="inlineStr"/>
+      <c r="M71" s="2" t="inlineStr"/>
+      <c r="N71" s="2" t="inlineStr"/>
+      <c r="O71" s="2" t="inlineStr"/>
+      <c r="P71" s="2" t="inlineStr"/>
+      <c r="Q71" s="2" t="inlineStr"/>
+    </row>
+    <row r="72">
+      <c r="A72" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="B72" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="C72" s="2" t="inlineStr"/>
+      <c r="D72" s="2" t="inlineStr">
+        <is>
+          <t>Itn Usage</t>
+        </is>
+      </c>
+      <c r="E72" s="2" t="inlineStr">
+        <is>
+          <t>ITN usage = behavioral act of sleeping under [[insecticide-treated-net]] to prevent [[malaria]] transmission via [[anopheles-mosquito]] bite reduction. Not a pharmacologic agent — listed here as preventive intervention. Current claim corpus addresses correlates of usage in [[ghana]], not device pharmacology or efficacy.</t>
+        </is>
+      </c>
+      <c r="F72" s="2" t="inlineStr"/>
+      <c r="G72" s="2" t="inlineStr"/>
+      <c r="H72" s="2" t="inlineStr">
+        <is>
+          <t>_No mechanistic claims in current corpus._ ITN listed as exposure/behavior, not pharmacologic agent.</t>
+        </is>
+      </c>
+      <c r="I72" s="2" t="inlineStr"/>
+      <c r="J72" s="2" t="inlineStr"/>
+      <c r="K72" s="2" t="inlineStr"/>
+      <c r="L72" s="2" t="inlineStr"/>
+      <c r="M72" s="2" t="inlineStr"/>
+      <c r="N72" s="2" t="inlineStr"/>
+      <c r="O72" s="2" t="inlineStr"/>
+      <c r="P72" s="2" t="inlineStr"/>
+      <c r="Q72" s="2" t="inlineStr"/>
+    </row>
+    <row r="73">
+      <c r="A73" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="B73" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="C73" s="2" t="inlineStr"/>
+      <c r="D73" s="2" t="inlineStr">
+        <is>
+          <t>Long Lasting Insecticidal Nets</t>
+        </is>
+      </c>
+      <c r="E73" s="2" t="inlineStr">
+        <is>
+          <t>Long-lasting insecticidal nets (LLINs) are bed nets factory-treated with pyrethroid insecticide bonded to fibers, retaining bioactivity across multiple washes. Deployed at community level in malaria-endemic regions, LLINs combine physical barrier and contact insecticide action against [[anopheles-mosquito]] vectors. Core tool in [[malaria]] prevention programs.</t>
+        </is>
+      </c>
+      <c r="F73" s="2" t="inlineStr"/>
+      <c r="G73" s="2" t="inlineStr"/>
+      <c r="H73" s="2" t="inlineStr">
+        <is>
+          <t>Physical barrier blocks mosquito-host contact during sleep. Pyrethroid coating delivers contact toxicity to *Anopheles* vectors landing on net surface, reducing vector survival and transmission intensity at community scale when coverage is high [c:a5f00c46] (pending review).
+```mermaid
+flowchart LR
+    A[LLIN deployed] --&gt; B[Physical barrier]
+    A --&gt; C[Pyrethroid contact kill]
+    B --&gt; D[Reduced bites]
+    C --&gt; E[Reduced vector population]
+    D --&gt; F[Reduced malaria transmission]
+    E --&gt; F
+```
+Cascade load-bearing on [c:a5f00c46].</t>
+        </is>
+      </c>
+      <c r="I73" s="2" t="inlineStr"/>
+      <c r="J73" s="2" t="inlineStr"/>
+      <c r="K73" s="2" t="inlineStr"/>
+      <c r="L73" s="2" t="inlineStr"/>
+      <c r="M73" s="2" t="inlineStr"/>
+      <c r="N73" s="2" t="inlineStr"/>
+      <c r="O73" s="2" t="inlineStr"/>
+      <c r="P73" s="2" t="inlineStr"/>
+      <c r="Q73" s="2" t="inlineStr"/>
+    </row>
+    <row r="74">
+      <c r="A74" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="B74" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="C74" s="2" t="inlineStr"/>
+      <c r="D74" s="2" t="inlineStr">
+        <is>
+          <t>Low Birth Weight</t>
+        </is>
+      </c>
+      <c r="E74" s="2" t="inlineStr">
+        <is>
+          <t>Low birth weight (LBW) = clinical outcome, not drug. Corpus links it to [[malaria-in-pregnancy]] as cause and to [[piperaquine]] exposure plus [[insecticide-treated-nets]] as preventive interventions during second/third trimester [c:33934556] [c:7eeeb08b] [c:8cc2f0b6] [c:7611788b]. Note re-classified for downstream graph; medication-template fields below left empty per dose-safety rule.</t>
+        </is>
+      </c>
+      <c r="F74" s="2" t="inlineStr"/>
+      <c r="G74" s="2" t="inlineStr"/>
+      <c r="H74" s="2" t="inlineStr">
+        <is>
+          <t>_No mechanism applies — LBW is outcome._ Causal driver in corpus: [[malaria-in-pregnancy]] causes LBW in second/third trimester, endemic settings [c:33934556] [c:7eeeb08b] _(pending review)_. Likely path: placental sequestration → fetal growth restriction (not directly claimed; not asserted).
+```mermaid
+flowchart LR
+  A[malaria-in-pregnancy] --&gt;|causes| B[low birth weight]
+  C[piperaquine exposure &gt;target] --&gt;|prevents per 10-day ↑| B
+  D[insecticide-treated nets] --&gt;|prevents| B
+```
+Citations: [c:33934556] [c:8cc2f0b6] [c:7611788b].</t>
+        </is>
+      </c>
+      <c r="I74" s="2" t="inlineStr"/>
+      <c r="J74" s="2" t="inlineStr"/>
+      <c r="K74" s="2" t="inlineStr"/>
+      <c r="L74" s="2" t="inlineStr"/>
+      <c r="M74" s="2" t="inlineStr"/>
+      <c r="N74" s="2" t="inlineStr"/>
+      <c r="O74" s="2" t="inlineStr"/>
+      <c r="P74" s="2" t="inlineStr"/>
+      <c r="Q74" s="2" t="inlineStr"/>
+    </row>
+    <row r="75">
+      <c r="A75" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="B75" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="C75" s="2" t="inlineStr"/>
+      <c r="D75" s="2" t="inlineStr">
+        <is>
+          <t>Low Birthweight</t>
+        </is>
+      </c>
+      <c r="E75" s="2" t="inlineStr">
+        <is>
+          <t>Low birthweight (&lt;2500 g at delivery) = neonatal outcome, not drug. Entity mis-classified as medication. Current claim set links it to malaria-in-pregnancy interventions and folate status. Note retained as outcome reference; cross-link from causative/preventive medications.</t>
+        </is>
+      </c>
+      <c r="F75" s="2" t="inlineStr"/>
+      <c r="G75" s="2" t="inlineStr"/>
+      <c r="H75" s="2" t="inlineStr">
+        <is>
+          <t>_Not applicable — outcome._ Mechanistic links from claims:
+```mermaid
+graph TD
+  A[Placental P. falciparum infection] --&gt;|IPTp-SP suppresses| B[Reduced placental parasitaemia]
+  B --&gt; C[Preserved fetal growth]
+  D[Folate deficiency 1st trimester] --&gt;|impairs DNA synthesis| E[Restricted fetal growth]
+  E --&gt; F[Low birthweight]
+  C --&gt; F
+```
+[[folate-deficiency]] in first trimester causes low birthweight [c:6f7139ab] (meta_analysis, pending review).</t>
+        </is>
+      </c>
+      <c r="I75" s="2" t="inlineStr"/>
+      <c r="J75" s="2" t="inlineStr"/>
+      <c r="K75" s="2" t="inlineStr"/>
+      <c r="L75" s="2" t="inlineStr"/>
+      <c r="M75" s="2" t="inlineStr"/>
+      <c r="N75" s="2" t="inlineStr"/>
+      <c r="O75" s="2" t="inlineStr"/>
+      <c r="P75" s="2" t="inlineStr"/>
+      <c r="Q75" s="2" t="inlineStr"/>
+    </row>
+    <row r="76">
+      <c r="A76" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="B76" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="C76" s="2" t="inlineStr"/>
+      <c r="D76" s="2" t="inlineStr">
+        <is>
+          <t>Macronutrient Undernutrition</t>
+        </is>
+      </c>
+      <c r="E76" s="2" t="inlineStr">
+        <is>
+          <t>Macronutrient undernutrition = deficient intake of protein, carbohydrate, fat. Not a drug. Classifier mislabeled this entity as medication. Note re-framed as condition profile pending entity-type correction. In pregnancy, undernutrition drives immune dysregulation, raises malaria susceptibility, harms fetus [c:ebd53703] [c:a34b6674] [c:f854a17f].</t>
+        </is>
+      </c>
+      <c r="F76" s="2" t="inlineStr"/>
+      <c r="G76" s="2" t="inlineStr"/>
+      <c r="H76" s="2" t="inlineStr">
+        <is>
+          <t>Pathophysiology, not pharmacology. Undernutrition → immune dysregulation [c:a34b6674] → increased malaria susceptibility in pregnancy [c:ebd53703]. Independent of malaria, undernutrition restricts fetal growth and triggers preterm birth [c:f854a17f] [c:a9ceeb01].
+```mermaid
+flowchart TD
+    A[Macronutrient undernutrition] --&gt;|c:a34b6674| B[Immune dysregulation]
+    B --&gt;|c:ebd53703| C[Malaria susceptibility ↑ in pregnancy]
+    A --&gt;|c:f854a17f| D[Fetal growth restriction]
+    A --&gt;|c:a9ceeb01| E[Preterm birth]
+    C -.co-occurs c:fb7a3787.- F[[malaria-in-pregnancy]]
+```
+All mechanistic links graded `expert_opinion`, status `pending_review`.</t>
+        </is>
+      </c>
+      <c r="I76" s="2" t="inlineStr"/>
+      <c r="J76" s="2" t="inlineStr"/>
+      <c r="K76" s="2" t="inlineStr"/>
+      <c r="L76" s="2" t="inlineStr"/>
+      <c r="M76" s="2" t="inlineStr"/>
+      <c r="N76" s="2" t="inlineStr"/>
+      <c r="O76" s="2" t="inlineStr"/>
+      <c r="P76" s="2" t="inlineStr"/>
+      <c r="Q76" s="2" t="inlineStr"/>
+    </row>
+    <row r="77">
+      <c r="A77" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="B77" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="C77" s="2" t="inlineStr">
+        <is>
+          <t>Infectious Disease</t>
+        </is>
+      </c>
+      <c r="D77" s="2" t="inlineStr">
+        <is>
+          <t>Malaria Cases And Deaths</t>
+        </is>
+      </c>
+      <c r="E77" s="2" t="inlineStr">
+        <is>
+          <t>"Malaria cases and deaths" not drug. Outcome variable in spatiotemporal epidemiology. Current claim corpus link three ecological/demographic correlates in [[india]] endemic [[community-setting]]: [[scheduled-tribe-population]] proportion, annual rainfall, forest cover. Note misclassified as medication — flag for retype to `epidemiologic_outcome` or `condition`.</t>
+        </is>
+      </c>
+      <c r="F77" s="2" t="inlineStr"/>
+      <c r="G77" s="2" t="inlineStr"/>
+      <c r="H77" s="2" t="inlineStr">
+        <is>
+          <t>_Not applicable._ Ecological correlates only (pending review):
+- [[scheduled-tribe-population]] proportion co-occurs spatially with malaria cases and deaths in India endemic community settings, with socioeconomic-disadvantage comorbidity qualifier [c:3910f2bc] (pending review).
+- Annual rainfall co-occurs spatially with malaria cases and deaths in India endemic community settings [c:e8c175ab] (pending review).
+- [[forest-cover]] co-occurs spatially with malaria cases and deaths in India endemic community settings [c:5682d19a] (pending review).</t>
+        </is>
+      </c>
+      <c r="I77" s="2" t="inlineStr"/>
+      <c r="J77" s="2" t="inlineStr"/>
+      <c r="K77" s="2" t="inlineStr"/>
+      <c r="L77" s="2" t="inlineStr"/>
+      <c r="M77" s="2" t="inlineStr"/>
+      <c r="N77" s="2" t="inlineStr"/>
+      <c r="O77" s="2" t="inlineStr"/>
+      <c r="P77" s="2" t="inlineStr"/>
+      <c r="Q77" s="2" t="inlineStr"/>
+    </row>
+    <row r="78">
+      <c r="A78" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="B78" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="C78" s="2" t="inlineStr">
+        <is>
+          <t>Infectious Disease</t>
+        </is>
+      </c>
+      <c r="D78" s="2" t="inlineStr">
+        <is>
+          <t>Malaria Clinical Disease Variation</t>
+        </is>
+      </c>
+      <c r="E78" s="2" t="inlineStr">
+        <is>
+          <t>"Malaria clinical disease variation" not medication. Phenotypic concept describe heterogeneity in [[malaria]] presentation across hosts. Current claim set describe co-occurrence factors (comorbidities, coinfections) that modulate clinical course, not pharmacologic agent. Note retained as stub; recommend reclassify entity_type to `concept` or `phenotype`.</t>
+        </is>
+      </c>
+      <c r="F78" s="2" t="inlineStr"/>
+      <c r="G78" s="2" t="inlineStr"/>
+      <c r="H78" s="2" t="inlineStr">
+        <is>
+          <t>_No mechanism claims in current corpus._ Co-occurrence claims only:
+- [[comorbidities]] co-occur with malaria clinical disease variation (pending review) [c:44191cc3]
+- [[coinfections]] co-occur with malaria clinical disease variation (pending review) [c:9a5d8ea5]
+Both expert_opinion grade, moderate certainty, sourced PMID:28533315.</t>
+        </is>
+      </c>
+      <c r="I78" s="2" t="inlineStr"/>
+      <c r="J78" s="2" t="inlineStr"/>
+      <c r="K78" s="2" t="inlineStr"/>
+      <c r="L78" s="2" t="inlineStr"/>
+      <c r="M78" s="2" t="inlineStr"/>
+      <c r="N78" s="2" t="inlineStr"/>
+      <c r="O78" s="2" t="inlineStr"/>
+      <c r="P78" s="2" t="inlineStr"/>
+      <c r="Q78" s="2" t="inlineStr"/>
+    </row>
+    <row r="79">
+      <c r="A79" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="B79" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="C79" s="2" t="inlineStr">
+        <is>
+          <t>Infectious Disease</t>
+        </is>
+      </c>
+      <c r="D79" s="2" t="inlineStr">
+        <is>
+          <t>Malaria Diagnosis When Microscopy Unavailable Within 24H</t>
+        </is>
+      </c>
+      <c r="E79" s="2" t="inlineStr">
+        <is>
+          <t>Malaria RDT is a point-of-care lateral-flow immunoassay detecting *Plasmodium* antigens from a fingerprick blood sample. Used to confirm malaria when [[microscopy]] unavailable within 24 hours in endemic settings. Result in 15–20 minutes. Note: this concept note covers a **diagnostic recommendation**, not a therapeutic drug — dosing/pharmacology sections not applicable.</t>
+        </is>
+      </c>
+      <c r="F79" s="2" t="inlineStr"/>
+      <c r="G79" s="2" t="inlineStr"/>
+      <c r="H79" s="2" t="inlineStr">
+        <is>
+          <t>Antibody-coated nitrocellulose strip captures circulating *Plasmodium* antigens (HRP-2 for *P. falciparum*, pLDH for pan-species) from whole blood. Antigen–antibody complex migrates via capillary action, binds labeled conjugate, produces visible band. Not a pharmacologic agent — no MoA in drug sense. Diagnostic role specified by claim set [c:cdca1173].</t>
+        </is>
+      </c>
+      <c r="I79" s="2" t="inlineStr"/>
+      <c r="J79" s="2" t="inlineStr"/>
+      <c r="K79" s="2" t="inlineStr"/>
+      <c r="L79" s="2" t="inlineStr"/>
+      <c r="M79" s="2" t="inlineStr"/>
+      <c r="N79" s="2" t="inlineStr"/>
+      <c r="O79" s="2" t="inlineStr"/>
+      <c r="P79" s="2" t="inlineStr"/>
+      <c r="Q79" s="2" t="inlineStr"/>
+    </row>
+    <row r="80">
+      <c r="A80" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="B80" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="C80" s="2" t="inlineStr">
+        <is>
+          <t>Infectious Disease</t>
+        </is>
+      </c>
+      <c r="D80" s="2" t="inlineStr">
+        <is>
+          <t>Malaria Diagnosis</t>
+        </is>
+      </c>
+      <c r="E80" s="2" t="inlineStr">
+        <is>
+          <t>Entity classified as "medication" but corpus claims describe diagnostic modalities for [[malaria]], not a drug. Current claims compare [[rapid-diagnostic-tests]] vs [[thick-and-thin-blood-film-microscopy]] for confirming malaria in [[febrile-illness-returning-traveler]] and military personnel. No pharmacologic content available.</t>
+        </is>
+      </c>
+      <c r="F80" s="2" t="inlineStr"/>
+      <c r="G80" s="2" t="inlineStr"/>
+      <c r="H80" s="2" t="inlineStr">
+        <is>
+          <t>Not pharmacologic. Diagnostic mechanism only:
+```mermaid
+flowchart LR
+  A[Febrile traveler] --&gt; B{Suspect malaria}
+  B --&gt; C[Thick + thin blood film microscopy]
+  B --&gt; D[Rapid diagnostic test antigen detection]
+  C --&gt; E[Species ID + parasitemia %]
+  D --&gt; F[HRP2/pLDH antigen positive]
+  E --&gt; G[Treatment decision]
+  F --&gt; G
+```
+UK inpatient pathway favors thick + thin film microscopy as reference modality [c:5f151210]. Field/military pathway favors RDT vs microscopy [c:d324ea3a].</t>
+        </is>
+      </c>
+      <c r="I80" s="2" t="inlineStr"/>
+      <c r="J80" s="2" t="inlineStr"/>
+      <c r="K80" s="2" t="inlineStr"/>
+      <c r="L80" s="2" t="inlineStr">
+        <is>
+          <t>**Therapeutic category:** Diagnostic workflow (not a pharmacologic agent)
+**Drug group:** _Not applicable — entity is diagnostic, not medication._
+**Drug class:** _Not applicable._
+**Controlled substance:** No</t>
+        </is>
+      </c>
+      <c r="M80" s="2" t="inlineStr"/>
+      <c r="N80" s="2" t="inlineStr"/>
+      <c r="O80" s="2" t="inlineStr"/>
+      <c r="P80" s="2" t="inlineStr"/>
+      <c r="Q80" s="2" t="inlineStr"/>
+    </row>
+    <row r="81">
+      <c r="A81" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="B81" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="C81" s="2" t="inlineStr">
+        <is>
+          <t>Infectious Disease</t>
+        </is>
+      </c>
+      <c r="D81" s="2" t="inlineStr">
+        <is>
+          <t>Malaria Importation Risk</t>
+        </is>
+      </c>
+      <c r="E81" s="2" t="inlineStr">
+        <is>
+          <t>Malaria importation risk = probability that [[plasmodium]] parasites enter [[non-endemic-areas]] via infected travelers or migrants. Migratory flows from endemic countries drive this risk [c:e5269e68] (pending review) [c:32a9b12e] (pending review). Entity not a drug; no pharmacological content applies.</t>
+        </is>
+      </c>
+      <c r="F81" s="2" t="inlineStr"/>
+      <c r="G81" s="2" t="inlineStr"/>
+      <c r="H81" s="2" t="inlineStr">
+        <is>
+          <t>Risk pathway, not pharmacological MoA:
+```mermaid
+flowchart LR
+  A[Endemic source country] --&gt; B[Migratory flow]
+  B --&gt; C[Infected traveler arrival]
+  C --&gt; D[Non-endemic setting]
+  D --&gt; E[Importation risk]
+```
+Migratory flows from endemic countries causally linked to importation risk in non-endemic settings [c:32a9b12e] (pending review, moderate certainty, expert_opinion). Underlying climate/environment context noted in source [c:e5269e68] (pending review, low certainty).</t>
+        </is>
+      </c>
+      <c r="I81" s="2" t="inlineStr">
+        <is>
+          <t>**Therapeutic category:** _Not a medication — epidemiological phenomenon mis-classified as drug entity._
+**Drug group:** _N/A_
+**Drug class:** _N/A_
+**Controlled substance:** _N/A_</t>
+        </is>
+      </c>
+      <c r="J81" s="2" t="inlineStr"/>
+      <c r="K81" s="2" t="inlineStr"/>
+      <c r="L81" s="2" t="inlineStr"/>
+      <c r="M81" s="2" t="inlineStr"/>
+      <c r="N81" s="2" t="inlineStr"/>
+      <c r="O81" s="2" t="inlineStr"/>
+      <c r="P81" s="2" t="inlineStr"/>
+      <c r="Q81" s="2" t="inlineStr"/>
+    </row>
+    <row r="82">
+      <c r="A82" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="B82" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="C82" s="2" t="inlineStr">
+        <is>
+          <t>Infectious Disease</t>
+        </is>
+      </c>
+      <c r="D82" s="2" t="inlineStr">
+        <is>
+          <t>Malaria Incidence</t>
+        </is>
+      </c>
+      <c r="E82" s="2" t="inlineStr">
+        <is>
+          <t>Indoor residual spraying (IRS) coats interior walls with long-acting insecticide to kill resting [[anopheles-mosquito]] vectors. Deployed alongside [[insecticide-treated-nets]] (ITNs) in endemic [[sub-saharan-africa]] and elimination settings (Namibia). Reactive focal IRS plus [[artemether-lumefantrine]] tested for spillover prevention around index cases.</t>
+        </is>
+      </c>
+      <c r="F82" s="2" t="inlineStr"/>
+      <c r="G82" s="2" t="inlineStr"/>
+      <c r="H82" s="2" t="inlineStr">
+        <is>
+          <t>Pyrethroids (DDT, deltamethrin) hyperactivate insect voltage-gated sodium channels → vector paralysis [c:bc57bd82]. Non-pyrethroids: carbamates and organophosphates (bendiocarb, pirimiphos-methyl, propoxur) inhibit acetylcholinesterase → cholinergic crisis in resting mosquitoes [c:037f304e] [c:f6af45c4]. Vector mortality on treated walls breaks transmission. Co-administered [[artemether-lumefantrine]] clears parasitaemia in humans → reduces infectious reservoir → spillover protection ≤1 km from index case [c:0670e3b6].
+```mermaid
+flowchart LR
+  A[IRS insecticide on wall] --&gt; B[Resting Anopheles contact]
+  B --&gt; C[Na-channel or AChE disruption]
+  C --&gt; D[Vector kill]
+  E[AL to index case] --&gt; F[Parasite clearance]
+  F --&gt; G[Reservoir shrink]
+  D --&gt; H[Malaria incidence drop]
+  G --&gt; H
+```</t>
+        </is>
+      </c>
+      <c r="I82" s="2" t="inlineStr"/>
+      <c r="J82" s="2" t="inlineStr"/>
+      <c r="K82" s="2" t="inlineStr"/>
+      <c r="L82" s="2" t="inlineStr"/>
+      <c r="M82" s="2" t="inlineStr"/>
+      <c r="N82" s="2" t="inlineStr"/>
+      <c r="O82" s="2" t="inlineStr"/>
+      <c r="P82" s="2" t="inlineStr"/>
+      <c r="Q82" s="2" t="inlineStr"/>
+    </row>
+    <row r="83">
+      <c r="A83" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="B83" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="C83" s="2" t="inlineStr">
+        <is>
+          <t>Infectious Disease</t>
+        </is>
+      </c>
+      <c r="D83" s="2" t="inlineStr">
+        <is>
+          <t>Malaria Parasitaemia</t>
+        </is>
+      </c>
+      <c r="E83" s="2" t="inlineStr">
+        <is>
+          <t>Malaria parasitaemia = presence of *Plasmodium* parasites in peripheral blood. Not a drug. Current claim corpus describes vector-control interventions (indoor residual spraying, IRS) aimed at preventing parasitaemia in [[sub-saharan-africa]] communities already using [[insecticide-treated-nets]]. No pharmacologic agent claims present for this entity.</t>
+        </is>
+      </c>
+      <c r="F83" s="2" t="inlineStr"/>
+      <c r="G83" s="2" t="inlineStr"/>
+      <c r="H83" s="2" t="inlineStr">
+        <is>
+          <t>_No drug mechanism applies._ Vector-control logic in claims: insecticide on indoor surfaces → kills/repels resting *Anopheles* mosquitoes → cuts human-vector contact → reduces parasite transmission. Not pharmacologic.</t>
+        </is>
+      </c>
+      <c r="I83" s="2" t="inlineStr"/>
+      <c r="J83" s="2" t="inlineStr"/>
+      <c r="K83" s="2" t="inlineStr"/>
+      <c r="L83" s="2" t="inlineStr"/>
+      <c r="M83" s="2" t="inlineStr">
+        <is>
+          <t>| Intervention | Comparator | RR parasite prevalence | 95% CI | Grade | Status |
+|---|---|---|---|---|---|
+| IRS pyrethroid-like + ITN | ITN alone | 1.11 | 0.86–1.44 | meta-analysis | auto-promoted [c:2bb1e5de] |
+| IRS non-pyrethroid-like + ITN | ITN alone | 0.67 | 0.35–1.28 | meta-analysis | pending review [c:1f74c617] |
+Both CIs cross 1.0 → no statistically significant benefit over ITN alone in cited Cochrane review (PMID:31120132). Pyrethroid-like point estimate suggests possible harm direction; non-pyrethroid-like trends toward benefit but low certainty.</t>
+        </is>
+      </c>
+      <c r="N83" s="2" t="inlineStr"/>
+      <c r="O83" s="2" t="inlineStr"/>
+      <c r="P83" s="2" t="inlineStr"/>
+      <c r="Q83" s="2" t="inlineStr"/>
+    </row>
+    <row r="84">
+      <c r="A84" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="B84" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="C84" s="2" t="inlineStr">
+        <is>
+          <t>Infectious Disease</t>
+        </is>
+      </c>
+      <c r="D84" s="2" t="inlineStr">
+        <is>
+          <t>Malaria Related Mortality And Readmission Post Discharge</t>
+        </is>
+      </c>
+      <c r="E84" s="2" t="inlineStr">
+        <is>
+          <t>PDMC = scheduled antimalarial courses given to children recently discharged after [[severe-anaemia]] in malaria-endemic settings. Post-discharge window high-risk for recurrent [[malaria]], readmission, death. Three agents in current corpus: [[dihydroartemisinin-piperaquine]], [[artemether-lumefantrine]], [[sulfadoxine-pyrimethamine]] — all [c:41c754ae][c:15a79d74][c:c6990d28].</t>
+        </is>
+      </c>
+      <c r="F84" s="2" t="inlineStr"/>
+      <c r="G84" s="2" t="inlineStr"/>
+      <c r="H84" s="2" t="inlineStr">
+        <is>
+          <t>Scheduled monthly courses suppress recrudescent + new [[plasmodium-falciparum]] infection during high-risk post-discharge period [c:41c754ae][c:15a79d74]. Per-agent MoA not in current claim set.</t>
+        </is>
+      </c>
+      <c r="I84" s="2" t="inlineStr"/>
+      <c r="J84" s="2" t="inlineStr"/>
+      <c r="K84" s="2" t="inlineStr">
+        <is>
+          <t>**Therapeutic category:** Antimalarial chemoprevention
+**Drug group:** Post-discharge malaria chemoprevention (PDMC) regimens
+**Drug class:** Mixed — artemisinin combinations + antifolate
+**Controlled substance:** No
+&gt; _Note: source entity is an outcome (`malaria-related mortality and readmission post-discharge`), not single drug. Claim corpus covers 3 PDMC agents. Note synthesizes class-level._</t>
+        </is>
+      </c>
+      <c r="L84" s="2" t="inlineStr"/>
+      <c r="M84" s="2" t="inlineStr"/>
+      <c r="N84" s="2" t="inlineStr"/>
+      <c r="O84" s="2" t="inlineStr"/>
+      <c r="P84" s="2" t="inlineStr"/>
+      <c r="Q84" s="2" t="inlineStr"/>
+    </row>
+    <row r="85">
+      <c r="A85" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="B85" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="C85" s="2" t="inlineStr">
+        <is>
+          <t>Infectious Disease</t>
+        </is>
+      </c>
+      <c r="D85" s="2" t="inlineStr">
+        <is>
+          <t>Malaria Transmission</t>
+        </is>
+      </c>
+      <c r="E85" s="2" t="inlineStr">
+        <is>
+          <t>Dihydroartemisinin–piperaquine (DHA-PPQ) is deployed beyond curative use as a **focal mass treatment** agent to interrupt [[malaria-transmission]] in elimination programmes, notably across the [[greater-mekong-subregion]] (pending review) [c:aecdb983]. Transmission itself requires the triad of human host, [[anopheles-mosquito]] vector, and [[plasmodium]] parasite, so chemotherapeutic mass treatment is one arm of a multi-modal strategy that also includes vector control [c:0494067c].</t>
+        </is>
+      </c>
+      <c r="F85" s="2" t="inlineStr"/>
+      <c r="G85" s="2" t="inlineStr"/>
+      <c r="H85" s="2" t="inlineStr">
+        <is>
+          <t>DHA clears asexual blood-stage parasites and reduces gametocyte carriage; piperaquine provides a long post-treatment prophylactic tail that suppresses re-emergence. By depleting the human infectious reservoir across a focal population simultaneously, mass treatment lowers the probability that an [[anopheles-mosquito]] blood-meal yields onward infection [c:aecdb983][c:20465445]. Transmission depends on the host–vector–parasite interaction, so reservoir depletion targets the host arm of that triad [c:0494067c].
+```mermaid
+flowchart LR
+    A[DHA-PPQ mass dose] --&gt; B[Asexual parasite clearance]
+    A --&gt; C[Gametocyte reservoir reduction]
+    B --&gt; D[Lower human infectivity]
+    C --&gt; D
+    D --&gt; E[Fewer infectious blood meals in Anopheles]
+    E --&gt; F[Interrupted transmission]
+```
+Mechanistic cascade load-bearing claim [c:aecdb983].</t>
+        </is>
+      </c>
+      <c r="I85" s="2" t="inlineStr"/>
+      <c r="J85" s="2" t="inlineStr"/>
+      <c r="K85" s="2" t="inlineStr"/>
+      <c r="L85" s="2" t="inlineStr"/>
+      <c r="M85" s="2" t="inlineStr">
+        <is>
+          <t>**Therapeutic category:** Antimalarial
+**Drug group:** Artemisinin-based combination therapy (ACT)
+**Drug class:** Sesquiterpene endoperoxide (dihydroartemisinin) + bisquinoline (piperaquine)
+**Controlled substance:** No</t>
+        </is>
+      </c>
+      <c r="N85" s="2" t="inlineStr"/>
+      <c r="O85" s="2" t="inlineStr"/>
+      <c r="P85" s="2" t="inlineStr"/>
+      <c r="Q85" s="2" t="inlineStr"/>
+    </row>
+    <row r="86">
+      <c r="A86" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="B86" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="C86" s="2" t="inlineStr"/>
+      <c r="D86" s="2" t="inlineStr">
+        <is>
+          <t>Malnutrition</t>
+        </is>
+      </c>
+      <c r="E86" s="2" t="inlineStr">
+        <is>
+          <t>Malnutrition is not a medication. Classifier flagged it as `medication` but current claim corpus describes it as a host comorbidity that (a) reduces [[piperaquine]] exposure in young children [c:8f2818f4] and (b) results from recurrent [[plasmodium-vivax]] infection in pediatric populations [c:07f24140] [c:ae24c94e]. Note retained for pharmacokinetic dosing context; not a prescribable agent. _(pending review — reclassification recommended)_</t>
+        </is>
+      </c>
+      <c r="F86" s="2" t="inlineStr"/>
+      <c r="G86" s="2" t="inlineStr"/>
+      <c r="H86" s="2" t="inlineStr">
+        <is>
+          <t>_Not applicable._ Mechanistic relevance limited to pharmacokinetic modulation: malnutrition reduces [[piperaquine]] systemic exposure in children aged 2–24 months in endemic Uganda outpatient setting [c:8f2818f4] (RCT, moderate certainty). Underlying mechanism (altered absorption, distribution, protein binding) not specified in current claims.</t>
+        </is>
+      </c>
+      <c r="I86" s="2" t="inlineStr"/>
+      <c r="J86" s="2" t="inlineStr"/>
+      <c r="K86" s="2" t="inlineStr"/>
+      <c r="L86" s="2" t="inlineStr"/>
+      <c r="M86" s="2" t="inlineStr"/>
+      <c r="N86" s="2" t="inlineStr"/>
+      <c r="O86" s="2" t="inlineStr"/>
+      <c r="P86" s="2" t="inlineStr"/>
+      <c r="Q86" s="2" t="inlineStr"/>
+    </row>
+    <row r="87">
+      <c r="A87" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="B87" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="C87" s="2" t="inlineStr"/>
+      <c r="D87" s="2" t="inlineStr">
+        <is>
+          <t>Mass Drug Administration</t>
+        </is>
+      </c>
+      <c r="E87" s="2" t="inlineStr">
+        <is>
+          <t>Mass drug administration (MDA) = community-wide delivery of antimalarial treatment to entire target population regardless of infection status. Goal: shrink parasite reservoir, cut transmission in [[malaria-endemic-settings]]. Partner regimen typically schizonticidal. Distinct from targeted chemoprevention — covers all eligible residents.</t>
+        </is>
+      </c>
+      <c r="F87" s="2" t="inlineStr"/>
+      <c r="G87" s="2" t="inlineStr"/>
+      <c r="H87" s="2" t="inlineStr">
+        <is>
+          <t>Population-level parasite clearance. Schizonticidal partner kills asexual blood-stage [[plasmodium-falciparum]] parasites across treated cohort simultaneously [c:c8413a02]. Synchronous clearance shrinks infectious reservoir → fewer onward [[anopheles]] infections → reduced community transmission and disease burden [c:8a872785] (pending review).
+```mermaid
+flowchart LR
+  A[MDA round in endemic community] --&gt; B[Schizonticide kills blood-stage P. falciparum]
+  B --&gt; C[Parasite reservoir shrinks]
+  C --&gt; D[Reduced mosquito infection]
+  D --&gt; E[Lower community malaria burden]
+```
+Cascade load-bearing on [c:c8413a02] and [c:8a872785].</t>
+        </is>
+      </c>
+      <c r="I87" s="2" t="inlineStr"/>
+      <c r="J87" s="2" t="inlineStr"/>
+      <c r="K87" s="2" t="inlineStr"/>
+      <c r="L87" s="2" t="inlineStr"/>
+      <c r="M87" s="2" t="inlineStr"/>
+      <c r="N87" s="2" t="inlineStr"/>
+      <c r="O87" s="2" t="inlineStr"/>
+      <c r="P87" s="2" t="inlineStr"/>
+      <c r="Q87" s="2" t="inlineStr"/>
+    </row>
+    <row r="88">
+      <c r="A88" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="B88" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="C88" s="2" t="inlineStr"/>
+      <c r="D88" s="2" t="inlineStr">
+        <is>
+          <t>Microscopic Misdiagnosis</t>
+        </is>
+      </c>
+      <c r="E88" s="2" t="inlineStr">
+        <is>
+          <t>"Microscopic misdiagnosis" not a medication — diagnostic failure where light-microscopy of blood film mis-identifies [[plasmodium-knowlesi]] as other Plasmodium species. Surfaced here because entity classifier tagged as medication; corpus claims describe epidemiologic association with fatal [[knowlesi-malaria]] in [[southeast-asia]] inpatients (pending review) [c:8b531772][c:bd5a6115].</t>
+        </is>
+      </c>
+      <c r="F88" s="2" t="inlineStr"/>
+      <c r="G88" s="2" t="inlineStr"/>
+      <c r="H88" s="2" t="inlineStr">
+        <is>
+          <t>_Not applicable as drug mechanism._ Epidemiologic mechanism per claims:
+```mermaid
+flowchart LR
+    A[Blood film microscopy] --&gt; B[Morphologic overlap with P. malariae / P. falciparum]
+    B --&gt; C[Species misidentification]
+    C --&gt; D[Delayed/incorrect antimalarial regimen]
+    D --&gt; E[Fatal P. knowlesi outcome]
+```
+Misdiagnosis co-occurs with ~90% of fatal knowlesi cases in endemic SE Asia inpatient series [c:bd5a6115] (pending review); causal link reported for 89.7% of fatal cases [c:8b531772] (pending review, meta_analysis, moderate certainty).</t>
+        </is>
+      </c>
+      <c r="I88" s="2" t="inlineStr"/>
+      <c r="J88" s="2" t="inlineStr"/>
+      <c r="K88" s="2" t="inlineStr"/>
+      <c r="L88" s="2" t="inlineStr">
+        <is>
+          <t>**Therapeutic category:** _Not applicable — entity is a diagnostic error, not a medication._
+**Drug group:** _N/A_
+**Drug class:** _N/A_
+**Controlled substance:** _N/A_</t>
+        </is>
+      </c>
+      <c r="M88" s="2" t="inlineStr"/>
+      <c r="N88" s="2" t="inlineStr"/>
+      <c r="O88" s="2" t="inlineStr"/>
+      <c r="P88" s="2" t="inlineStr"/>
+      <c r="Q88" s="2" t="inlineStr"/>
+    </row>
+    <row r="89">
+      <c r="A89" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="B89" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="C89" s="2" t="inlineStr"/>
+      <c r="D89" s="2" t="inlineStr">
+        <is>
+          <t>Migratory Flows</t>
+        </is>
+      </c>
+      <c r="E89" s="2" t="inlineStr">
+        <is>
+          <t>Migratory flows from malaria-endemic to non-endemic regions act as an importation vector for [[malaria]] transmission risk, not as a pharmacological agent [c:e5269e68] [c:32a9b12e] (pending review). Entity mis-routed to medication template; substance retained for completeness, but dose/mechanism/interaction sections inapplicable.</t>
+        </is>
+      </c>
+      <c r="F89" s="2" t="inlineStr"/>
+      <c r="G89" s="2" t="inlineStr"/>
+      <c r="H89" s="2" t="inlineStr">
+        <is>
+          <t>Not a pharmacological mechanism. Epidemiological pathway: infected travelers from endemic regions carry [[plasmodium]] parasites into non-endemic areas, seeding imported cases [c:e5269e68] [c:32a9b12e]. No mechanistic cascade claims in corpus — Mermaid diagram omitted.</t>
+        </is>
+      </c>
+      <c r="I89" s="2" t="inlineStr"/>
+      <c r="J89" s="2" t="inlineStr"/>
+      <c r="K89" s="2" t="inlineStr"/>
+      <c r="L89" s="2" t="inlineStr"/>
+      <c r="M89" s="2" t="inlineStr"/>
+      <c r="N89" s="2" t="inlineStr"/>
+      <c r="O89" s="2" t="inlineStr"/>
+      <c r="P89" s="2" t="inlineStr"/>
+      <c r="Q89" s="2" t="inlineStr"/>
+    </row>
+    <row r="90">
+      <c r="A90" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="B90" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="C90" s="2" t="inlineStr"/>
+      <c r="D90" s="2" t="inlineStr">
+        <is>
+          <t>Mk 7602</t>
+        </is>
+      </c>
+      <c r="E90" s="2" t="inlineStr">
+        <is>
+          <t>MK-7602 is an investigational antimalarial under development for [[plasmodium-falciparum-malaria]]. Acts across multiple parasite life-cycle stages — liver, blood, and transmission — via dual-targeting mechanism [c:71bcbe6f] [c:abe83a25] (pending review). All current claims are `expert_opinion` grade from a single PubMed source.</t>
+        </is>
+      </c>
+      <c r="F90" s="2" t="inlineStr"/>
+      <c r="G90" s="2" t="inlineStr"/>
+      <c r="H90" s="2" t="inlineStr">
+        <is>
+          <t>MK-7602 inhibits [[plasmepsin-ix]] and [[plasmepsin-x]] — aspartic proteases essential to parasite egress and invasion [c:f9ebfb67] (pending review). Dual-targeting profile yields multi-stage activity across liver, blood, and gametocyte stages [c:de777b8b] [c:145ad339] [c:abe83a25] (pending review).
+```mermaid
+graph LR
+  A[MK-7602] --&gt;|inhibits| B[Plasmepsin IX/X]
+  B --&gt; C[Block merozoite egress/invasion]
+  C --&gt; D[Blood-stage clearance]
+  B --&gt; E[Block sporozoite development]
+  E --&gt; F[Liver-stage clearance]
+  C --&gt; G[Gametocyte disruption]
+  G --&gt; H[Transmission blocked]
+```
+Cascade load-bearing: [c:f9ebfb67] (pending review).</t>
+        </is>
+      </c>
+      <c r="I90" s="2" t="inlineStr"/>
+      <c r="J90" s="2" t="inlineStr"/>
+      <c r="K90" s="2" t="inlineStr"/>
+      <c r="L90" s="2" t="inlineStr"/>
+      <c r="M90" s="2" t="inlineStr"/>
+      <c r="N90" s="2" t="inlineStr"/>
+      <c r="O90" s="2" t="inlineStr"/>
+      <c r="P90" s="2" t="inlineStr"/>
+      <c r="Q90" s="2" t="inlineStr"/>
+    </row>
+    <row r="91">
+      <c r="A91" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="B91" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="C91" s="2" t="inlineStr"/>
+      <c r="D91" s="2" t="inlineStr">
+        <is>
+          <t>Mortality</t>
+        </is>
+      </c>
+      <c r="E91" s="2" t="inlineStr">
+        <is>
+          <t>Mortality is the death endpoint used across infectious-disease claims in this corpus, not a medication. Current claims attach it to [[plasmodium-falciparum-malaria]] globally [c:e61096eb] [c:ad387568], [[malaria]] in children under five [c:e313b62a], and notifiable infectious diseases in Chinese pediatric populations [c:74b06ea0]. Additional claims link clinical features of severe malaria to mortality co-occurrence [c:546fce01] [c:d70f94c8] [c:f4b05e2f] [c:d878c565] [c:7529d81e]. _No medication-specific claims present._</t>
+        </is>
+      </c>
+      <c r="F91" s="2" t="inlineStr"/>
+      <c r="G91" s="2" t="inlineStr"/>
+      <c r="H91" s="2" t="inlineStr">
+        <is>
+          <t>_Not applicable — mortality is endpoint, not pharmacologic agent._ Claim set describes pathophysiologic correlates in severe malaria rather than mechanism of a drug:
+```mermaid
+flowchart LR
+  A[severe falciparum malaria] --&gt; B[hyperlactataemia]
+  A --&gt; C[metabolic acidosis]
+  A --&gt; D[respiratory distress]
+  A --&gt; E[circulatory shock]
+  A --&gt; F[neurological involvement]
+  B --&gt; Z[mortality]
+  C --&gt; Z
+  D --&gt; Z
+  E --&gt; Z
+  F --&gt; Z
+```
+Co-occurrence claims (inpatient, moderate certainty, pending review): [[hyperlactataemia]] [c:546fce01], [[metabolic-acidosis]] [c:d70f94c8], [[respiratory-distress]] [c:f4b05e2f], [[circulatory-shock]] [c:d878c565], [[neurological-involvement]] [c:7529d81e].</t>
+        </is>
+      </c>
+      <c r="I91" s="2" t="inlineStr"/>
+      <c r="J91" s="2" t="inlineStr"/>
+      <c r="K91" s="2" t="inlineStr"/>
+      <c r="L91" s="2" t="inlineStr"/>
+      <c r="M91" s="2" t="inlineStr"/>
+      <c r="N91" s="2" t="inlineStr"/>
+      <c r="O91" s="2" t="inlineStr"/>
+      <c r="P91" s="2" t="inlineStr"/>
+      <c r="Q91" s="2" t="inlineStr"/>
+    </row>
+    <row r="92">
+      <c r="A92" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="B92" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="C92" s="2" t="inlineStr">
+        <is>
+          <t>Infectious Disease</t>
+        </is>
+      </c>
+      <c r="D92" s="2" t="inlineStr">
+        <is>
+          <t>Most Antimalarial Drugs</t>
+        </is>
+      </c>
+      <c r="E92" s="2" t="inlineStr">
+        <is>
+          <t>"Most antimalarial drugs" not single drug. Umbrella term in [[plasmodium-vivax]] literature for blood-stage antimalarials lacking hypnozoiticidal action. Current corpus describe one shared limitation: failure against dormant liver-stage hypnozoites of [[plasmodium-vivax]] (pending review) [c:c1317ee2][c:10af1c9b].</t>
+        </is>
+      </c>
+      <c r="F92" s="2" t="inlineStr"/>
+      <c r="G92" s="2" t="inlineStr"/>
+      <c r="H92" s="2" t="inlineStr">
+        <is>
+          <t>_No mechanism claims in current corpus for class as whole._ Shared negative property: most agents target erythrocytic stages, miss [[hypnozoite]] dormant liver form of [[plasmodium-vivax]] (pending review) [c:c1317ee2][c:10af1c9b].
+```mermaid
+flowchart LR
+    A[Most antimalarials] --&gt;|active| B[Blood-stage parasites]
+    A --&gt;|inactive| C[P. vivax hypnozoite]
+    C --&gt;|persists| D[Relapse]
+```
+Diagram supported by [c:c1317ee2][c:10af1c9b] (pending review).</t>
+        </is>
+      </c>
+      <c r="I92" s="2" t="inlineStr"/>
+      <c r="J92" s="2" t="inlineStr"/>
+      <c r="K92" s="2" t="inlineStr"/>
+      <c r="L92" s="2" t="inlineStr"/>
+      <c r="M92" s="2" t="inlineStr"/>
+      <c r="N92" s="2" t="inlineStr"/>
+      <c r="O92" s="2" t="inlineStr"/>
+      <c r="P92" s="2" t="inlineStr"/>
+      <c r="Q92" s="2" t="inlineStr"/>
+    </row>
+    <row r="93">
+      <c r="A93" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="B93" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="C93" s="2" t="inlineStr"/>
+      <c r="D93" s="2" t="inlineStr">
+        <is>
+          <t>Neuroinflammation</t>
+        </is>
+      </c>
+      <c r="E93" s="2" t="inlineStr">
+        <is>
+          <t>Neuroinflammation is a CNS inflammatory response, not a therapeutic agent. Classifier hint (`medication`) does not match the underlying claim set, which positions neuroinflammation as an *effect* of [[inflammatory-mediators]] [c:327c6bed] and [[cerebral-malaria]] [c:e402ac3d]. Note retained as stub; recommend reclassification to `concept` or `condition`.</t>
+        </is>
+      </c>
+      <c r="F93" s="2" t="inlineStr"/>
+      <c r="G93" s="2" t="inlineStr"/>
+      <c r="H93" s="2" t="inlineStr">
+        <is>
+          <t>_Not applicable as a drug._ Upstream drivers in current corpus: inflammatory mediators (cytokines, chemokines) drive neuroinflammation in inpatient endemic settings [c:327c6bed] (pending review); cerebral malaria causes neuroinflammation [c:e402ac3d] (pending review). Both `expert_opinion` grade.
+```mermaid
+flowchart LR
+  A[Cerebral malaria] --&gt;|releases| B[Inflammatory mediators]
+  B --&gt;|drive| C[Neuroinflammation]
+```
+Cascade per [c:e402ac3d] and [c:327c6bed].</t>
+        </is>
+      </c>
+      <c r="I93" s="2" t="inlineStr"/>
+      <c r="J93" s="2" t="inlineStr"/>
+      <c r="K93" s="2" t="inlineStr"/>
+      <c r="L93" s="2" t="inlineStr"/>
+      <c r="M93" s="2" t="inlineStr"/>
+      <c r="N93" s="2" t="inlineStr"/>
+      <c r="O93" s="2" t="inlineStr"/>
+      <c r="P93" s="2" t="inlineStr"/>
+      <c r="Q93" s="2" t="inlineStr"/>
+    </row>
+    <row r="94">
+      <c r="A94" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="B94" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="C94" s="2" t="inlineStr">
+        <is>
+          <t>Infectious Disease</t>
+        </is>
+      </c>
+      <c r="D94" s="2" t="inlineStr">
+        <is>
+          <t>Non Falciparum Malaria</t>
+        </is>
+      </c>
+      <c r="E94" s="2" t="inlineStr">
+        <is>
+          <t>Imported [[non-falciparum-malaria]] in UK travelers treated with either oral [[artemisinin-combination-therapy]] or [[chloroquine]]. UK 2016 guidelines favor oral ACT over chloroquine across outpatient, inpatient, and traveler settings, with stronger preference where mixed infection or [[chloroquine-resistant-p-vivax]] exposure suspected [c:540756c3] [c:10717bce] [c:47c3afc3] [c:ef1f9fb3] [c:cc23c153]. (pending review)</t>
+        </is>
+      </c>
+      <c r="F94" s="2" t="inlineStr"/>
+      <c r="G94" s="2" t="inlineStr"/>
+      <c r="H94" s="2" t="inlineStr">
+        <is>
+          <t>_No mechanism claims in current corpus._ See [[artemisinin-combination-therapy]] and [[chloroquine]] notes for MOA.</t>
+        </is>
+      </c>
+      <c r="I94" s="2" t="inlineStr"/>
+      <c r="J94" s="2" t="inlineStr"/>
+      <c r="K94" s="2" t="inlineStr"/>
+      <c r="L94" s="2" t="inlineStr"/>
+      <c r="M94" s="2" t="inlineStr">
+        <is>
+          <t>**Therapeutic category:** Antimalarial
+**Drug group:** Oral [[artemisinin-combination-therapy]] (ACT) · 4-aminoquinoline ([[chloroquine]])
+**Drug class:** Sesquiterpene endoperoxide combination · 4-aminoquinoline
+**Controlled substance:** No
+&gt; Note: entity is condition, but claim corpus describes two competing regimens. Note covers both as treatment options for [[non-falciparum-malaria]].</t>
+        </is>
+      </c>
+      <c r="N94" s="2" t="inlineStr"/>
+      <c r="O94" s="2" t="inlineStr"/>
+      <c r="P94" s="2" t="inlineStr"/>
+      <c r="Q94" s="2" t="inlineStr"/>
+    </row>
+    <row r="95">
+      <c r="A95" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="B95" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="C95" s="2" t="inlineStr"/>
+      <c r="D95" s="2" t="inlineStr">
+        <is>
+          <t>Oral Act</t>
+        </is>
+      </c>
+      <c r="E95" s="2" t="inlineStr">
+        <is>
+          <t>Oral artemisinin-combination therapy (ACT) class label covering fixed-dose oral regimens pairing artemisinin derivative with longer-acting partner drug. UK guidance positions oral ACT as treatment option for [[non-falciparum-malaria]] in imported/traveler cases, especially where chloroquine resistance suspected (pending review) [c:10717bce] [c:47c3afc3].</t>
+        </is>
+      </c>
+      <c r="F95" s="2" t="inlineStr"/>
+      <c r="G95" s="2" t="inlineStr"/>
+      <c r="H95" s="2" t="inlineStr">
+        <is>
+          <t>_No mechanism claims in current corpus._ Class-level: artemisinin component generates reactive intermediates against intra-erythrocytic parasite; partner drug clears residual parasitemia. Not citable from current claim set.</t>
+        </is>
+      </c>
+      <c r="I95" s="2" t="inlineStr"/>
+      <c r="J95" s="2" t="inlineStr"/>
+      <c r="K95" s="2" t="inlineStr"/>
+      <c r="L95" s="2" t="inlineStr"/>
+      <c r="M95" s="2" t="inlineStr"/>
+      <c r="N95" s="2" t="inlineStr"/>
+      <c r="O95" s="2" t="inlineStr"/>
+      <c r="P95" s="2" t="inlineStr"/>
+      <c r="Q95" s="2" t="inlineStr"/>
+    </row>
+    <row r="96">
+      <c r="A96" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="B96" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="C96" s="2" t="inlineStr">
+        <is>
+          <t>Infectious Disease</t>
+        </is>
+      </c>
+      <c r="D96" s="2" t="inlineStr">
+        <is>
+          <t>P Falciparum Malaria</t>
+        </is>
+      </c>
+      <c r="E96" s="2" t="inlineStr">
+        <is>
+          <t>Vaccines aimed at preventing [[p-falciparum-malaria]], caused by *Plasmodium falciparum* sporozoite infection. Three agents in current corpus: [[pfspz-vaccine]] (irradiated sporozoite), [[pfspz-cvac]] (chemoattenuated sporozoite under drug cover), and [[r21-vaccine]] (recombinant circumsporozoite subunit). All entries `(pending review)`.</t>
+        </is>
+      </c>
+      <c r="F96" s="2" t="inlineStr"/>
+      <c r="G96" s="2" t="inlineStr"/>
+      <c r="H96" s="2" t="inlineStr">
+        <is>
+          <t>Pre-erythrocytic vaccines induce immunity against sporozoite and liver-stage parasites, blocking infection before blood-stage disease. Whole-sporozoite platforms ([[pfspz-vaccine]], [[pfspz-cvac]]) deliver attenuated parasites; R21 is a recombinant [[circumsporozoite-protein]] virus-like particle [c:3ea70610] [c:0a197d0b] [c:10d60266].
+```mermaid
+flowchart LR
+  A[Vaccine antigen] --&gt; B[Anti-sporozoite Ab + CD8 T-cells]
+  B --&gt; C[Sporozoite neutralization at skin/liver]
+  C --&gt; D[Block hepatocyte infection]
+  D --&gt; E[No blood-stage parasitemia]
+  E --&gt; F[Prevent clinical malaria]
+```
+[c:3ea70610] [c:0a197d0b] [c:10d60266]</t>
+        </is>
+      </c>
+      <c r="I96" s="2" t="inlineStr"/>
+      <c r="J96" s="2" t="inlineStr"/>
+      <c r="K96" s="2" t="inlineStr"/>
+      <c r="L96" s="2" t="inlineStr"/>
+      <c r="M96" s="2" t="inlineStr"/>
+      <c r="N96" s="2" t="inlineStr"/>
+      <c r="O96" s="2" t="inlineStr"/>
+      <c r="P96" s="2" t="inlineStr"/>
+      <c r="Q96" s="2" t="inlineStr"/>
+    </row>
+    <row r="97">
+      <c r="A97" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="B97" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="C97" s="2" t="inlineStr">
+        <is>
+          <t>Infectious Disease</t>
+        </is>
+      </c>
+      <c r="D97" s="2" t="inlineStr">
+        <is>
+          <t>P Falciparum</t>
+        </is>
+      </c>
+      <c r="E97" s="2" t="inlineStr">
+        <is>
+          <t>_No medication claims in current corpus._ Entity `P. falciparum` is a protozoan parasite causing [[falciparum-malaria]], not a therapeutic agent. Available claims describe co-endemicity with [[plasmodium-vivax]] in non-African regions [c:6e858a33] (pending review) and community-level [[mass-drug-administration]] with schizonticidal treatment as an intervention targeting the parasite [c:c8413a02] (pending review).</t>
+        </is>
+      </c>
+      <c r="F97" s="2" t="inlineStr"/>
+      <c r="G97" s="2" t="inlineStr"/>
+      <c r="H97" s="2" t="inlineStr">
+        <is>
+          <t>_No mechanism-of-action claims in current corpus._</t>
+        </is>
+      </c>
+      <c r="I97" s="2" t="inlineStr"/>
+      <c r="J97" s="2" t="inlineStr"/>
+      <c r="K97" s="2" t="inlineStr"/>
+      <c r="L97" s="2" t="inlineStr"/>
+      <c r="M97" s="2" t="inlineStr"/>
+      <c r="N97" s="2" t="inlineStr"/>
+      <c r="O97" s="2" t="inlineStr"/>
+      <c r="P97" s="2" t="inlineStr"/>
+      <c r="Q97" s="2" t="inlineStr"/>
+    </row>
+    <row r="98">
+      <c r="A98" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="B98" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="C98" s="2" t="inlineStr">
+        <is>
+          <t>Infectious Disease</t>
+        </is>
+      </c>
+      <c r="D98" s="2" t="inlineStr">
+        <is>
+          <t>P Vivax And P Ovale Hypnozoites</t>
+        </is>
+      </c>
+      <c r="E98" s="2" t="inlineStr">
+        <is>
+          <t>Primaquine clears dormant liver-stage hypnozoites of [[plasmodium-vivax]] and [[plasmodium-ovale]], preventing relapse after blood-stage cure. Used as radical-cure adjunct alongside schizonticide. G6PD status gate required before dosing — hemolysis risk in G6PD-deficient patients.</t>
+        </is>
+      </c>
+      <c r="F98" s="2" t="inlineStr"/>
+      <c r="G98" s="2" t="inlineStr"/>
+      <c r="H98" s="2" t="inlineStr">
+        <is>
+          <t>Targets liver-stage [[hypnozoite]] forms that blood schizonticides miss. Active metabolites generate reactive oxygen species disrupting parasite mitochondria, eradicating dormant reservoir and breaking relapse cycle [c:d4b0c986].
+```mermaid
+graph LR
+  A[Primaquine] --&gt; B[CYP2D6 metabolites]
+  B --&gt; C[ROS in parasite mitochondria]
+  C --&gt; D[Hypnozoite kill]
+  D --&gt; E[Relapse prevention]
+```</t>
+        </is>
+      </c>
+      <c r="I98" s="2" t="inlineStr"/>
+      <c r="J98" s="2" t="inlineStr"/>
+      <c r="K98" s="2" t="inlineStr"/>
+      <c r="L98" s="2" t="inlineStr"/>
+      <c r="M98" s="2" t="inlineStr"/>
+      <c r="N98" s="2" t="inlineStr"/>
+      <c r="O98" s="2" t="inlineStr"/>
+      <c r="P98" s="2" t="inlineStr"/>
+      <c r="Q98" s="2" t="inlineStr"/>
+    </row>
+    <row r="99">
+      <c r="A99" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="B99" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="C99" s="2" t="inlineStr">
+        <is>
+          <t>Infectious Disease</t>
+        </is>
+      </c>
+      <c r="D99" s="2" t="inlineStr">
+        <is>
+          <t>P Vivax Hypnozoites</t>
+        </is>
+      </c>
+      <c r="E99" s="2" t="inlineStr">
+        <is>
+          <t>P. vivax hypnozoites = dormant liver-stage parasites of [[plasmodium-vivax]]. Cause relapse weeks-months after primary infection. Targeted by radical cure, not a medication themselves. Entity classified as "medication" in source corpus appears mis-tagged — hypnozoites are the **target**, not the agent. Note assembled per template; most drug-specific fields N/A.</t>
+        </is>
+      </c>
+      <c r="F99" s="2" t="inlineStr"/>
+      <c r="G99" s="2" t="inlineStr"/>
+      <c r="H99" s="2" t="inlineStr">
+        <is>
+          <t>Hypnozoites persist as dormant intrahepatic forms. Resist most antimalarial drugs [c:10af1c9b] (pending review, expert_opinion, high certainty) — explains relapse biology and why blood-stage schizonticides alone fail to cure [[p-vivax-malaria]].
+```mermaid
+flowchart LR
+  A[Sporozoite inoculation] --&gt; B[Hepatocyte invasion]
+  B --&gt; C[Dormant hypnozoite]
+  C --&gt;|weeks-months| D[Reactivation]
+  D --&gt; E[Blood-stage relapse]
+  C -.resists.-&gt; F[Most antimalarials c:10af1c9b]
+  C -.cleared by.-&gt; G[Radical cure c:a24f7bef]
+```</t>
+        </is>
+      </c>
+      <c r="I99" s="2" t="inlineStr"/>
+      <c r="J99" s="2" t="inlineStr"/>
+      <c r="K99" s="2" t="inlineStr"/>
+      <c r="L99" s="2" t="inlineStr"/>
+      <c r="M99" s="2" t="inlineStr"/>
+      <c r="N99" s="2" t="inlineStr"/>
+      <c r="O99" s="2" t="inlineStr"/>
+      <c r="P99" s="2" t="inlineStr"/>
+      <c r="Q99" s="2" t="inlineStr"/>
+    </row>
+    <row r="100">
+      <c r="A100" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="B100" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="C100" s="2" t="inlineStr">
+        <is>
+          <t>Infectious Disease</t>
+        </is>
+      </c>
+      <c r="D100" s="2" t="inlineStr">
+        <is>
+          <t>P Vivax Relapse</t>
+        </is>
+      </c>
+      <c r="E100" s="2" t="inlineStr">
+        <is>
+          <t>Co-administration of [[primaquine]] (hypnozoiticide) with [[chloroquine]] (blood schizonticide) for radical cure of [[plasmodium-vivax]] malaria. Chloroquine clears blood-stage parasites; primaquine kills dormant liver-stage hypnozoites that drive [[p-vivax-relapse]]. Schizonticidal therapy alone — chloroquine without primaquine — leaves hypnozoites intact and causes relapse [c:1228e637] _(pending review)_.</t>
+        </is>
+      </c>
+      <c r="F100" s="2" t="inlineStr"/>
+      <c r="G100" s="2" t="inlineStr"/>
+      <c r="H100" s="2" t="inlineStr">
+        <is>
+          <t>Chloroquine kills erythrocytic schizonts → resolves acute parasitemia. Primaquine kills liver hypnozoites → blocks relapse. Schizonticidal-only treatment leaves hypnozoite reservoir intact → relapse [c:1228e637] _(pending review, expert_opinion)_.
+```mermaid
+flowchart LR
+  A[Chloroquine] --&gt; B[Blood schizont kill]
+  C[Primaquine] --&gt; D[Hypnozoite kill in liver]
+  B --&gt; E[Acute symptom resolution]
+  D --&gt; F[Relapse prevented]
+  G[Schizonticidal alone] --&gt; H[Hypnozoites persist] --&gt; I[Relapse]
+```
+Cascade supported by [c:1228e637].</t>
+        </is>
+      </c>
+      <c r="I100" s="2" t="inlineStr"/>
+      <c r="J100" s="2" t="inlineStr"/>
+      <c r="K100" s="2" t="inlineStr"/>
+      <c r="L100" s="2" t="inlineStr"/>
+      <c r="M100" s="2" t="inlineStr"/>
+      <c r="N100" s="2" t="inlineStr"/>
+      <c r="O100" s="2" t="inlineStr"/>
+      <c r="P100" s="2" t="inlineStr"/>
+      <c r="Q100" s="2" t="inlineStr"/>
+    </row>
+    <row r="101">
+      <c r="A101" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="B101" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="C101" s="2" t="inlineStr"/>
+      <c r="D101" s="2" t="inlineStr">
+        <is>
+          <t>Paracetamol</t>
+        </is>
+      </c>
+      <c r="E101" s="2" t="inlineStr">
+        <is>
+          <t>Paracetamol is a widely used analgesic and antipyretic. In severe [[plasmodium-knowlesi-malaria]], expert opinion suggests an adjunctive renoprotective role by attenuating haemolysis-driven lipid peroxidation in the kidney [c:26a3eb90] [c:942e062d]. Current corpus limited to two expert-opinion claims; no dose, contraindication, or interaction claims available.</t>
+        </is>
+      </c>
+      <c r="F101" s="2" t="inlineStr"/>
+      <c r="G101" s="2" t="inlineStr"/>
+      <c r="H101" s="2" t="inlineStr">
+        <is>
+          <t>Proposed mechanism in haemolytic severe knowlesi malaria: paracetamol inhibits cell-free haemoglobin–driven lipid peroxidation, reducing oxidative renal tubular injury (pending review) [c:942e062d].
+```mermaid
+flowchart LR
+  A[Haemolysis] --&gt; B[Cell-free haemoglobin]
+  B --&gt; C[Lipid peroxidation in renal tubules]
+  C --&gt; D[Acute kidney injury]
+  P[Paracetamol] -.inhibits.-&gt; C
+```
+Mechanistic chain supported by [c:942e062d].</t>
+        </is>
+      </c>
+      <c r="I101" s="2" t="inlineStr"/>
+      <c r="J101" s="2" t="inlineStr"/>
+      <c r="K101" s="2" t="inlineStr"/>
+      <c r="L101" s="2" t="inlineStr"/>
+      <c r="M101" s="2" t="inlineStr"/>
+      <c r="N101" s="2" t="inlineStr"/>
+      <c r="O101" s="2" t="inlineStr"/>
+      <c r="P101" s="2" t="inlineStr"/>
+      <c r="Q101" s="2" t="inlineStr"/>
+    </row>
+    <row r="102">
+      <c r="A102" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="B102" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="C102" s="2" t="inlineStr"/>
+      <c r="D102" s="2" t="inlineStr">
+        <is>
+          <t>Parasitemia</t>
+        </is>
+      </c>
+      <c r="E102" s="2" t="inlineStr">
+        <is>
+          <t>Fixed-dose ACT combining dihydroartemisinin (fast-acting blood schizonticide) with piperaquine (long-acting partner drug). Evidence in current corpus covers use as intermittent preventive treatment in pregnancy (IPTp) against [[plasmodium-falciparum]] in endemic settings, where it reduces prevalence of [[parasitemia-in-pregnancy]] versus [[sulfadoxine-pyrimethamine]] [c:da2ba758][c:9eee5181].</t>
+        </is>
+      </c>
+      <c r="F102" s="2" t="inlineStr"/>
+      <c r="G102" s="2" t="inlineStr"/>
+      <c r="H102" s="2" t="inlineStr">
+        <is>
+          <t>_No mechanism-of-action claims in current corpus._ Claims support clinical effect only — reduced prevalence of parasitemia vs SP comparator [c:da2ba758][c:9eee5181].</t>
+        </is>
+      </c>
+      <c r="I102" s="2" t="inlineStr"/>
+      <c r="J102" s="2" t="inlineStr"/>
+      <c r="K102" s="2" t="inlineStr"/>
+      <c r="L102" s="2" t="inlineStr"/>
+      <c r="M102" s="2" t="inlineStr"/>
+      <c r="N102" s="2" t="inlineStr"/>
+      <c r="O102" s="2" t="inlineStr"/>
+      <c r="P102" s="2" t="inlineStr"/>
+      <c r="Q102" s="2" t="inlineStr"/>
+    </row>
+    <row r="103">
+      <c r="A103" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="B103" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="C103" s="2" t="inlineStr"/>
+      <c r="D103" s="2" t="inlineStr">
+        <is>
+          <t>Partner Drug Resistance</t>
+        </is>
+      </c>
+      <c r="E103" s="2" t="inlineStr">
+        <is>
+          <t>"Partner drug resistance" not a medication. Refers to reduced *P. falciparum* susceptibility to non-artemisinin partner in artemisinin-combination therapy (ACT). Driven by parasite transporter mutations. Entry mis-classified as medication; treat as resistance entity. Current corpus only links two transporters as causal drivers.</t>
+        </is>
+      </c>
+      <c r="F103" s="2" t="inlineStr"/>
+      <c r="G103" s="2" t="inlineStr"/>
+      <c r="H103" s="2" t="inlineStr">
+        <is>
+          <t>Two parasite transporters implicated as causal drivers of partner drug resistance:
+- [[p-falciparum-multidrug-resistance-protein-1]] (*pfmdr1*) causes partner drug resistance [c:ddfefdba] *(pending review, expert_opinion)*
+- [[p-falciparum-chloroquine-resistance-transporter]] (*pfcrt*) causes partner drug resistance [c:4e8c61fd] *(pending review, expert_opinion)*
+```mermaid
+flowchart LR
+  A[pfmdr1 variant] --&gt; C[Altered drug efflux/accumulation in digestive vacuole]
+  B[pfcrt variant] --&gt; C
+  C --&gt; D[Reduced partner drug potency]
+  D --&gt; E[ACT treatment failure risk]
+```
+Mechanistic cascade beyond transporter → resistance not supported by current claim set [c:ddfefdba][c:4e8c61fd].</t>
+        </is>
+      </c>
+      <c r="I103" s="2" t="inlineStr"/>
+      <c r="J103" s="2" t="inlineStr"/>
+      <c r="K103" s="2" t="inlineStr"/>
+      <c r="L103" s="2" t="inlineStr"/>
+      <c r="M103" s="2" t="inlineStr"/>
+      <c r="N103" s="2" t="inlineStr"/>
+      <c r="O103" s="2" t="inlineStr"/>
+      <c r="P103" s="2" t="inlineStr"/>
+      <c r="Q103" s="2" t="inlineStr"/>
+    </row>
+    <row r="104">
+      <c r="A104" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="B104" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="C104" s="2" t="inlineStr"/>
+      <c r="D104" s="2" t="inlineStr">
+        <is>
+          <t>Permethrin Treated Baby Wraps</t>
+        </is>
+      </c>
+      <c r="E104" s="2" t="inlineStr">
+        <is>
+          <t>Cloth baby wraps impregnated with permethrin, worn by caregiver carrying infant. Insecticide on fabric repels and kills [[anopheles-mosquitoes]] on contact, reducing bites to infant during high-exposure carrying hours. Tested in [[uganda]] as adjunct to [[long-lasting-insecticidal-net|LLIN]] for infants 6–18 months in endemic setting (pending review).</t>
+        </is>
+      </c>
+      <c r="F104" s="2" t="inlineStr"/>
+      <c r="G104" s="2" t="inlineStr"/>
+      <c r="H104" s="2" t="inlineStr">
+        <is>
+          <t>[[permethrin]] on wrap fabric contacts host-seeking [[anopheles-mosquitoes]] approaching carried infant. Pyrethroid binds voltage-gated sodium channels in mosquito, causing knockdown and mortality before successful blood meal. Net effect: fewer infective bites reaching infant during carrying hours, lowering clinical malaria incidence vs sham wrap + LLIN alone [c:193a60dc].
+```mermaid
+flowchart LR
+  A[Permethrin on wrap] --&gt; B[Mosquito contact]
+  B --&gt; C[Na+ channel block / knockdown]
+  C --&gt; D[Reduced infective bites to infant]
+  D --&gt; E[Lower clinical malaria incidence]
+```
+[c:193a60dc]</t>
+        </is>
+      </c>
+      <c r="I104" s="2" t="inlineStr"/>
+      <c r="J104" s="2" t="inlineStr"/>
+      <c r="K104" s="2" t="inlineStr"/>
+      <c r="L104" s="2" t="inlineStr"/>
+      <c r="M104" s="2" t="inlineStr"/>
+      <c r="N104" s="2" t="inlineStr"/>
+      <c r="O104" s="2" t="inlineStr"/>
+      <c r="P104" s="2" t="inlineStr"/>
+      <c r="Q104" s="2" t="inlineStr"/>
+    </row>
+    <row r="105">
+      <c r="A105" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="B105" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="C105" s="2" t="inlineStr"/>
+      <c r="D105" s="2" t="inlineStr">
+        <is>
+          <t>Pfspz Cvac</t>
+        </is>
+      </c>
+      <c r="E105" s="2" t="inlineStr">
+        <is>
+          <t>PfSPZ-CVac is an investigational whole-sporozoite malaria vaccine using live, fully infectious *P. falciparum* sporozoites administered under antimalarial drug cover. The drug kills emerging blood-stage parasites while the host mounts a protective immune response against pre-erythrocytic stages [c:9939ff9f] (pending review).</t>
+        </is>
+      </c>
+      <c r="F105" s="2" t="inlineStr"/>
+      <c r="G105" s="2" t="inlineStr"/>
+      <c r="H105" s="2" t="inlineStr">
+        <is>
+          <t>Live [[plasmodium-falciparum]] sporozoites delivered under chemoprophylaxis cover; drug clears blood-stage parasites while pre-erythrocytic immunity develops [c:9939ff9f] (pending review; evidence_grade: expert_opinion).</t>
+        </is>
+      </c>
+      <c r="I105" s="2" t="inlineStr"/>
+      <c r="J105" s="2" t="inlineStr"/>
+      <c r="K105" s="2" t="inlineStr"/>
+      <c r="L105" s="2" t="inlineStr"/>
+      <c r="M105" s="2" t="inlineStr"/>
+      <c r="N105" s="2" t="inlineStr"/>
+      <c r="O105" s="2" t="inlineStr"/>
+      <c r="P105" s="2" t="inlineStr"/>
+      <c r="Q105" s="2" t="inlineStr"/>
+    </row>
+    <row r="106">
+      <c r="A106" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="B106" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="C106" s="2" t="inlineStr"/>
+      <c r="D106" s="2" t="inlineStr">
+        <is>
+          <t>Pfspz Vaccine</t>
+        </is>
+      </c>
+      <c r="E106" s="2" t="inlineStr">
+        <is>
+          <t>PfSPZ Vaccine is investigational malaria vaccine made from radiation-attenuated, aseptic, purified, cryopreserved *Plasmodium falciparum* sporozoites. Targets pre-erythrocytic stage to prevent [[plasmodium-falciparum-malaria]] infection [c:1e1263ae] (pending review).</t>
+        </is>
+      </c>
+      <c r="F106" s="2" t="inlineStr"/>
+      <c r="G106" s="2" t="inlineStr"/>
+      <c r="H106" s="2" t="inlineStr">
+        <is>
+          <t>Radiation-attenuated sporozoites enter hepatocytes but cannot complete liver-stage development. Arrested parasites prime sterile pre-erythrocytic immunity (CD8+ T cell + antibody response against sporozoite/liver-stage antigens), blocking subsequent wild-type infection before blood stage [c:1e1263ae] (pending review).
+```mermaid
+flowchart LR
+  A[Irradiated PfSPZ inoculum] --&gt; B[Hepatocyte invasion]
+  B --&gt; C[Arrested liver-stage parasite]
+  C --&gt; D[CD8+ T cell + antibody priming]
+  D --&gt; E[Block wild-type sporozoite → prevent P. falciparum malaria]
+```
+Cascade load-bearing claim [c:1e1263ae].</t>
+        </is>
+      </c>
+      <c r="I106" s="2" t="inlineStr"/>
+      <c r="J106" s="2" t="inlineStr"/>
+      <c r="K106" s="2" t="inlineStr"/>
+      <c r="L106" s="2" t="inlineStr"/>
+      <c r="M106" s="2" t="inlineStr"/>
+      <c r="N106" s="2" t="inlineStr"/>
+      <c r="O106" s="2" t="inlineStr"/>
+      <c r="P106" s="2" t="inlineStr"/>
+      <c r="Q106" s="2" t="inlineStr"/>
+    </row>
+    <row r="107">
+      <c r="A107" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="B107" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="C107" s="2" t="inlineStr">
+        <is>
+          <t>Infectious Disease</t>
+        </is>
+      </c>
+      <c r="D107" s="2" t="inlineStr">
+        <is>
+          <t>Placental Malaria</t>
+        </is>
+      </c>
+      <c r="E107" s="2" t="inlineStr">
+        <is>
+          <t>Fixed-dose ACT used for intermittent preventive treatment in pregnancy (IPTp) against [[placental-malaria]]. Corpus positions DHA-PPQ as alternative to [[sulfadoxine-pyrimethamine]] for [[uncomplicated-falciparum-malaria]] prevention in second/third trimester, including [[hiv-coinfection]] settings.</t>
+        </is>
+      </c>
+      <c r="F107" s="2" t="inlineStr"/>
+      <c r="G107" s="2" t="inlineStr"/>
+      <c r="H107" s="2" t="inlineStr">
+        <is>
+          <t>_No direct MoA claims in current corpus._ Disease-side mechanism: [[chondroitin-sulfate-a]]-binding parasitized erythrocytes sequester in placenta and cause placental malaria in malaria-naive gravidae [c:657176b7]; semi-immune mothers develop anti-CSA-binding antibodies that prevent sequestration [c:ef16afad] (pending review). DHA-PPQ presumed to act by clearing/suppressing parasitemia before placental sequestration occurs — *not directly supported by claim set.*
+```mermaid
+flowchart LR
+  A[CSA-binding iRBC] --&gt;|sequester| B[Placental intervillous space]
+  B --&gt; C[Placental malaria]
+  D[DHA-PPQ IPTp] -.-&gt;|suppress parasitemia| A
+  E[Anti-CSA antibodies] -.-&gt;|block adhesion| A
+```
+Cascade load-bearing: [c:657176b7] [c:ef16afad].</t>
+        </is>
+      </c>
+      <c r="I107" s="2" t="inlineStr"/>
+      <c r="J107" s="2" t="inlineStr"/>
+      <c r="K107" s="2" t="inlineStr">
+        <is>
+          <t>[[insecticide-treated-nets]] prevent placental malaria at community level, endemic settings [c:23fbd0bb] (pending review) — non-pharmacologic complement to IPTp.
+---
+*Last regenerated: 2026-05-13T19:20:10Z. Source claims: 8. Evidence mix: 3 meta-analysis · 2 RCT · 3 expert_opinion.*</t>
+        </is>
+      </c>
+      <c r="L107" s="2" t="inlineStr"/>
+      <c r="M107" s="2" t="inlineStr"/>
+      <c r="N107" s="2" t="inlineStr"/>
+      <c r="O107" s="2" t="inlineStr"/>
+      <c r="P107" s="2" t="inlineStr"/>
+      <c r="Q107" s="2" t="inlineStr"/>
+    </row>
+    <row r="108">
+      <c r="A108" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="B108" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="C108" s="2" t="inlineStr"/>
+      <c r="D108" s="2" t="inlineStr">
+        <is>
+          <t>Placental Parasitemia</t>
+        </is>
+      </c>
+      <c r="E108" s="2" t="inlineStr">
+        <is>
+          <t>Piperaquine is long-acting bisquinoline antimalarial, paired with dihydroartemisinin in ACT regimen. Long terminal half-life drives post-treatment prophylactic window. Studied as intermittent preventive treatment in pregnancy (IPTp) against [[placental-parasitemia]] in [[plasmodium-falciparum]] endemic settings.</t>
+        </is>
+      </c>
+      <c r="F108" s="2" t="inlineStr"/>
+      <c r="G108" s="2" t="inlineStr"/>
+      <c r="H108" s="2" t="inlineStr">
+        <is>
+          <t>_No mechanism claims in current corpus._ Class-level mechanism (heme detoxification inhibition in parasite food vacuole) not supported by present claim set.</t>
+        </is>
+      </c>
+      <c r="I108" s="2" t="inlineStr"/>
+      <c r="J108" s="2" t="inlineStr"/>
+      <c r="K108" s="2" t="inlineStr"/>
+      <c r="L108" s="2" t="inlineStr"/>
+      <c r="M108" s="2" t="inlineStr"/>
+      <c r="N108" s="2" t="inlineStr"/>
+      <c r="O108" s="2" t="inlineStr"/>
+      <c r="P108" s="2" t="inlineStr"/>
+      <c r="Q108" s="2" t="inlineStr"/>
+    </row>
+    <row r="109">
+      <c r="A109" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="B109" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="C109" s="2" t="inlineStr">
+        <is>
+          <t>Infectious Disease</t>
+        </is>
+      </c>
+      <c r="D109" s="2" t="inlineStr">
+        <is>
+          <t>Plasmodium Falciparum Infection</t>
+        </is>
+      </c>
+      <c r="E109" s="2" t="inlineStr">
+        <is>
+          <t>Fixed-dose ACT combining short-acting dihydroartemisinin with long-acting piperaquine. Used as intermittent preventive treatment in pregnancy (IPTp) for [[plasmodium-falciparum-infection]] in endemic regions, where it shows antimalarial efficacy versus standard [[sulfadoxine-pyrimethamine]] IPTp [c:d9fa18f9] (pending review).</t>
+        </is>
+      </c>
+      <c r="F109" s="2" t="inlineStr"/>
+      <c r="G109" s="2" t="inlineStr"/>
+      <c r="H109" s="2" t="inlineStr">
+        <is>
+          <t>Dihydroartemisinin = active artemisinin metabolite; endoperoxide bridge cleaved by parasite heme-iron → reactive radicals → parasite protein/lipid alkylation. Piperaquine = long-acting blood schizonticide accumulating in parasite food vacuole, blocking heme detoxification. Parasite [[proteostasis]] perturbation tied to artemisinin action and resistance [c:b9d44edb] (low certainty, pending review).
+```mermaid
+flowchart LR
+  A[DHA endoperoxide] --&gt;|heme-Fe cleavage| B[Free radicals]
+  B --&gt; C[Parasite protein alkylation]
+  C --&gt; D[Proteostasis collapse]
+  D --&gt; E[Schizont death]
+  F[Piperaquine] --&gt;|food vacuole accumulation| G[Heme detox block]
+  G --&gt; E
+```
+Proteostasis step [c:b9d44edb].</t>
+        </is>
+      </c>
+      <c r="I109" s="2" t="inlineStr"/>
+      <c r="J109" s="2" t="inlineStr"/>
+      <c r="K109" s="2" t="inlineStr"/>
+      <c r="L109" s="2" t="inlineStr"/>
+      <c r="M109" s="2" t="inlineStr"/>
+      <c r="N109" s="2" t="inlineStr"/>
+      <c r="O109" s="2" t="inlineStr"/>
+      <c r="P109" s="2" t="inlineStr"/>
+      <c r="Q109" s="2" t="inlineStr"/>
+    </row>
+    <row r="110">
+      <c r="A110" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="B110" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="C110" s="2" t="inlineStr">
+        <is>
+          <t>Infectious Disease</t>
+        </is>
+      </c>
+      <c r="D110" s="2" t="inlineStr">
+        <is>
+          <t>Plasmodium Falciparum Malaria Infection</t>
+        </is>
+      </c>
+      <c r="E110" s="2" t="inlineStr">
+        <is>
+          <t>Corpus references generic "antimalarial drug treatment" for [[plasmodium-falciparum-malaria]] infection in children 2–10 yr, sub-Saharan Africa, outpatient endemic setting [c:94c70d1b] (pending review). No specific agent, class, or regimen named. Two adjunct vector-control measures (IRS, ITN) cited as prevention, not pharmacotherapy [c:016dcd00][c:98c759c7] (pending review).</t>
+        </is>
+      </c>
+      <c r="F110" s="2" t="inlineStr"/>
+      <c r="G110" s="2" t="inlineStr"/>
+      <c r="H110" s="2" t="inlineStr">
+        <is>
+          <t>_No mechanism claims in current corpus._ Agent unidentified; downstream target unknown.</t>
+        </is>
+      </c>
+      <c r="I110" s="2" t="inlineStr"/>
+      <c r="J110" s="2" t="inlineStr"/>
+      <c r="K110" s="2" t="inlineStr">
+        <is>
+          <t>- [[indoor-residual-spraying]] — prevents falciparum infection, community setting, children 2–10 yr, sub-Saharan Africa [c:016dcd00] (pending review)
+- [[insecticide-treated-bednets]] — prevents falciparum infection, community setting, children 2–10 yr, sub-Saharan Africa [c:98c759c7] (pending review)
+---
+*Last regenerated: 2026-05-13T19:23:48.558815+00:00. Source claims: 3. Evidence mix: 3 expert_opinion (all pending review). Entity mis-typed as medication — underlying claims describe a disease and its treatment/prevention bundle, not a single drug. Recommend reclassify to `condition` or split into specific drug entities.*</t>
+        </is>
+      </c>
+      <c r="L110" s="2" t="inlineStr"/>
+      <c r="M110" s="2" t="inlineStr">
+        <is>
+          <t>**Therapeutic category:** Antimalarial
+**Drug group:** _Not specified in current corpus._
+**Drug class:** _Not specified in current corpus._
+**Controlled substance:** _Not specified in current corpus._</t>
+        </is>
+      </c>
+      <c r="N110" s="2" t="inlineStr"/>
+      <c r="O110" s="2" t="inlineStr"/>
+      <c r="P110" s="2" t="inlineStr"/>
+      <c r="Q110" s="2" t="inlineStr"/>
+    </row>
+    <row r="111">
+      <c r="A111" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="B111" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="C111" s="2" t="inlineStr">
+        <is>
+          <t>Infectious Disease</t>
+        </is>
+      </c>
+      <c r="D111" s="2" t="inlineStr">
+        <is>
+          <t>Plasmodium Falciparum Malaria</t>
+        </is>
+      </c>
+      <c r="E111" s="2" t="inlineStr">
+        <is>
+          <t>[[plasmodium-falciparum-malaria]] caused ~600 000 deaths/yr in 2021 across tropical and subtropical regions [c:ad387568][c:e61096eb]. Effective antimalarial treatment exists in endemic [[sub-saharan-africa]] outpatient settings [c:3d7baa62]. Therapy splits into (a) treatment with [[artemisinin]]-based regimens, (b) chemoprevention for travellers, children, and pregnant women, (c) pre-erythrocytic vaccines.</t>
+        </is>
+      </c>
+      <c r="F111" s="2" t="inlineStr"/>
+      <c r="G111" s="2" t="inlineStr"/>
+      <c r="H111" s="2" t="inlineStr">
+        <is>
+          <t>```mermaid
+graph LR
+  A[Artemisinin endoperoxide] --&gt; B[Fe2+-heme cleavage in parasite digestive vacuole]
+  B --&gt; C[Free radical alkylation of parasite proteins/lipids]
+  C --&gt; D[Asexual blood-stage parasite kill]
+  E[RTS,S/AS01 CSP antigen] --&gt; F[Anti-circumsporozoite antibodies]
+  F --&gt; G[Sporozoite hepatocyte invasion blocked]
+  H[MMV1557817] --&gt; I[PfA-M1/M17 aminopeptidase inhibition]
+  I --&gt; J[Hemoglobin digestion arrested]
+```
+[[artemisinin]] derivatives are first-line schizonticides for blood-stage parasites [c:27565d0d][c:20091eef]. [[rts-s-as01]] and [[r21-matrix-m]] target pre-erythrocytic circumsporozoite protein [c:d0e31868][c:910efe0b]. [[mmv1557817]] inhibits parasite aminopeptidases PfA-M1/M17 [c:1b9f2f02].</t>
+        </is>
+      </c>
+      <c r="I111" s="2" t="inlineStr"/>
+      <c r="J111" s="2" t="inlineStr"/>
+      <c r="K111" s="2" t="inlineStr"/>
+      <c r="L111" s="2" t="inlineStr"/>
+      <c r="M111" s="2" t="inlineStr"/>
+      <c r="N111" s="2" t="inlineStr"/>
+      <c r="O111" s="2" t="inlineStr"/>
+      <c r="P111" s="2" t="inlineStr"/>
+      <c r="Q111" s="2" t="inlineStr"/>
+    </row>
+    <row r="112">
+      <c r="A112" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="B112" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="C112" s="2" t="inlineStr">
+        <is>
+          <t>Infectious Disease</t>
+        </is>
+      </c>
+      <c r="D112" s="2" t="inlineStr">
+        <is>
+          <t>Plasmodium Falciparum Transmission Near Index Cases</t>
+        </is>
+      </c>
+      <c r="E112" s="2" t="inlineStr">
+        <is>
+          <t>Fixed-dose ACT deployed as reactive focal chemoprevention (rfMDA) around [[plasmodium-falciparum]] index cases in elimination settings. Current claim corpus narrowly scopes [[artemether-lumefantrine]] to transmission-prevention role near index households in [[namibia]] alongside [[pirimiphos-methyl]] indoor residual spraying [c:0ca4eaa0] [c:fdda9571].</t>
+        </is>
+      </c>
+      <c r="F112" s="2" t="inlineStr"/>
+      <c r="G112" s="2" t="inlineStr"/>
+      <c r="H112" s="2" t="inlineStr">
+        <is>
+          <t>_No mechanism claims in current corpus._ Transmission-prevention effect inferred at population level only; individual-level parasiticidal pathway not represented in claim set [c:0ca4eaa0].</t>
+        </is>
+      </c>
+      <c r="I112" s="2" t="inlineStr"/>
+      <c r="J112" s="2" t="inlineStr"/>
+      <c r="K112" s="2" t="inlineStr">
+        <is>
+          <t>**Therapeutic category:** Antimalarial
+**Drug group:** Artemisinin combination therapy (ACT)
+**Drug class:** Sesquiterpene endoperoxide + aryl-amino alcohol
+**Controlled substance:** No</t>
+        </is>
+      </c>
+      <c r="L112" s="2" t="inlineStr"/>
+      <c r="M112" s="2" t="inlineStr"/>
+      <c r="N112" s="2" t="inlineStr"/>
+      <c r="O112" s="2" t="inlineStr"/>
+      <c r="P112" s="2" t="inlineStr"/>
+      <c r="Q112" s="2" t="inlineStr"/>
+    </row>
+    <row r="113">
+      <c r="A113" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="B113" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="C113" s="2" t="inlineStr">
+        <is>
+          <t>Infectious Disease</t>
+        </is>
+      </c>
+      <c r="D113" s="2" t="inlineStr">
+        <is>
+          <t>Plasmodium Falciparum Transmission</t>
+        </is>
+      </c>
+      <c r="E113" s="2" t="inlineStr">
+        <is>
+          <t>Not single drug. Composite entry covering interventions targeting [[plasmodium-falciparum]] transmission stage — gametocyte clearance, mosquito-stage blockade, focal mass drug administration. Includes [[dihydroartemisinin-piperaquine]] focal MDA, transmission-blocking vaccine antigens ([[pfs25]], [[pfs230]], [[pfs48-45]], [[pfs47]], [[pfhap2]]), and botanical [[azadirachta-indica]]. All current claims `expert_opinion` grade, pending review.</t>
+        </is>
+      </c>
+      <c r="F113" s="2" t="inlineStr"/>
+      <c r="G113" s="2" t="inlineStr"/>
+      <c r="H113" s="2" t="inlineStr">
+        <is>
+          <t>Mechanisms differ per intervention.
+```mermaid
+graph TD
+    A[Asexual blood-stage parasite] --&gt;|DHA-PPQ MDA clears reservoir| B[Reduced gametocyte carriage]
+    A --&gt;|Gametocytogenesis| C[Mature gametocytes]
+    C --&gt;|Mosquito uptake| D[Gamete + zygote in midgut]
+    D --&gt; E[Ookinete]
+    E --&gt; F[Oocyst → sporozoite]
+    G[Pfs230, Pfs48/45] -.blocks fertilization.-&gt; D
+    H[PfHAP2] -.blocks gamete fusion.-&gt; D
+    I[Pfs25] -.blocks ookinete development.-&gt; E
+    J[Pfs47] -.evades mosquito immunity, vaccine blocks midgut traversal.-&gt; E
+    K[Azadirachta indica] -.gametocytocidal/sporontocidal claim.-&gt; C
+```
+Focal MDA with [[dihydroartemisinin-piperaquine]] clears asexual + gametocyte reservoir community-wide [c:5d886b6d]. Pre-fertilization antigens [[pfs230]] [c:f60b7589] + [[pfs48-45]] [c:5bf4d11e] elicit antibodies blocking gamete fertilization. [[pfhap2]] targets gamete membrane fusion [c:ee0b16d4]. Post-fertilization [[pfs25]] blocks ookinete-to-oocyst transition [c:6655178b]. [[pfs47]] disrupts mosquito midgut immune evasion [c:b793273c]. [[azadirachta-indica]] mechanism not specified in corpus [c:d7aa14e4].</t>
+        </is>
+      </c>
+      <c r="I113" s="2" t="inlineStr"/>
+      <c r="J113" s="2" t="inlineStr"/>
+      <c r="K113" s="2" t="inlineStr"/>
+      <c r="L113" s="2" t="inlineStr"/>
+      <c r="M113" s="2" t="inlineStr"/>
+      <c r="N113" s="2" t="inlineStr"/>
+      <c r="O113" s="2" t="inlineStr"/>
+      <c r="P113" s="2" t="inlineStr"/>
+      <c r="Q113" s="2" t="inlineStr"/>
+    </row>
+    <row r="114">
+      <c r="A114" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="B114" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="C114" s="2" t="inlineStr">
+        <is>
+          <t>Infectious Disease</t>
+        </is>
+      </c>
+      <c r="D114" s="2" t="inlineStr">
+        <is>
+          <t>Plasmodium Inui</t>
+        </is>
+      </c>
+      <c r="E114" s="2" t="inlineStr">
+        <is>
+          <t>Plasmodium inui is a simian malaria parasite, not a therapeutic agent. Classifier hint (`medication`) appears incorrect; entity belongs under pathogens/organisms. Causes zoonotic malaria in humans in [[southeast-asia]], with documented [[simian-malaria]] cases [c:5dbafef4] and zoonotic transmission to humans [c:a04673e7] (pending review). All claims expert-opinion grade.</t>
+        </is>
+      </c>
+      <c r="F114" s="2" t="inlineStr"/>
+      <c r="G114" s="2" t="inlineStr"/>
+      <c r="H114" s="2" t="inlineStr">
+        <is>
+          <t>_Not applicable — pathogen, not drug._ No mechanism-of-action claims in current corpus. For pathogenesis of [[plasmodium-inui-infection]], see organism note (separate entity type).</t>
+        </is>
+      </c>
+      <c r="I114" s="2" t="inlineStr"/>
+      <c r="J114" s="2" t="inlineStr"/>
+      <c r="K114" s="2" t="inlineStr"/>
+      <c r="L114" s="2" t="inlineStr"/>
+      <c r="M114" s="2" t="inlineStr"/>
+      <c r="N114" s="2" t="inlineStr"/>
+      <c r="O114" s="2" t="inlineStr"/>
+      <c r="P114" s="2" t="inlineStr"/>
+      <c r="Q114" s="2" t="inlineStr"/>
+    </row>
+    <row r="115">
+      <c r="A115" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="B115" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="C115" s="2" t="inlineStr">
+        <is>
+          <t>Infectious Disease</t>
+        </is>
+      </c>
+      <c r="D115" s="2" t="inlineStr">
+        <is>
+          <t>Plasmodium Knowlesi Infection</t>
+        </is>
+      </c>
+      <c r="E115" s="2" t="inlineStr">
+        <is>
+          <t>[[plasmodium-knowlesi]] is a simian malaria parasite causing zoonotic human infection across [[southeast-asia]]. Pediatric cases tend toward uncomplicated outpatient course [c:ac218bdf] (pending review). Molecular assays outperform microscopy for species ID [c:059b5ce9] (pending review). No medication claims present — this note cannot describe a drug.</t>
+        </is>
+      </c>
+      <c r="F115" s="2" t="inlineStr"/>
+      <c r="G115" s="2" t="inlineStr"/>
+      <c r="H115" s="2" t="inlineStr">
+        <is>
+          <t>_No mechanism claims in current corpus._ Entity is an infectious agent, not a therapeutic.</t>
+        </is>
+      </c>
+      <c r="I115" s="2" t="inlineStr"/>
+      <c r="J115" s="2" t="inlineStr"/>
+      <c r="K115" s="2" t="inlineStr"/>
+      <c r="L115" s="2" t="inlineStr"/>
+      <c r="M115" s="2" t="inlineStr"/>
+      <c r="N115" s="2" t="inlineStr"/>
+      <c r="O115" s="2" t="inlineStr"/>
+      <c r="P115" s="2" t="inlineStr"/>
+      <c r="Q115" s="2" t="inlineStr"/>
+    </row>
+    <row r="116">
+      <c r="A116" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="B116" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="C116" s="2" t="inlineStr">
+        <is>
+          <t>Infectious Disease</t>
+        </is>
+      </c>
+      <c r="D116" s="2" t="inlineStr">
+        <is>
+          <t>Plasmodium Knowlesi</t>
+        </is>
+      </c>
+      <c r="E116" s="2" t="inlineStr">
+        <is>
+          <t>Zoonotic apicomplexan parasite causing human malaria across Southeast Asia [c:1b738a81] [c:dd18f73c] [c:1ffa0467] [c:dda6609e], predominantly Malaysia where it ranks as leading cause of human malaria [c:04e2112f] [c:9a4500e3]. Transmitted by *Anopheles* Leucosphyrus Group mosquitoes [c:7fa962dd]. Causes clinical disease spanning uncomplicated to fatal severe malaria [c:f129bcbe] [c:3b069426].</t>
+        </is>
+      </c>
+      <c r="F116" s="2" t="inlineStr"/>
+      <c r="G116" s="2" t="inlineStr"/>
+      <c r="H116" s="2" t="inlineStr">
+        <is>
+          <t>_Not a drug — pathogenesis summary._ Sporozoites inoculated by [[anopheles-leucosphyrus-group]] vectors [c:7fa962dd] establish blood-stage infection in humans [c:b9b93eaf]; rapid 24-hour erythrocytic cycle (shortest of human plasmodia) drives clinical disease [c:f129bcbe] and progression to severe/fatal malaria with multiorgan failure [c:6d086826] [c:3b069426].
+```mermaid
+graph LR
+  A[Anopheles Leucosphyrus bite] --&gt;|c:7fa962dd| B[Sporozoite inoculation]
+  B --&gt; C[Hepatic stage]
+  C --&gt; D[24h erythrocytic cycle]
+  D --&gt;|c:f129bcbe| E[Clinical malaria]
+  E --&gt;|c:3b069426| F[Severe malaria]
+  F --&gt;|c:6d086826| G[Multiorgan failure]
+  G --&gt;|c:94a1e7ae| H[Death]
+```</t>
+        </is>
+      </c>
+      <c r="I116" s="2" t="inlineStr"/>
+      <c r="J116" s="2" t="inlineStr"/>
+      <c r="K116" s="2" t="inlineStr"/>
+      <c r="L116" s="2" t="inlineStr"/>
+      <c r="M116" s="2" t="inlineStr"/>
+      <c r="N116" s="2" t="inlineStr"/>
+      <c r="O116" s="2" t="inlineStr"/>
+      <c r="P116" s="2" t="inlineStr"/>
+      <c r="Q116" s="2" t="inlineStr"/>
+    </row>
+    <row r="117">
+      <c r="A117" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="B117" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="C117" s="2" t="inlineStr">
+        <is>
+          <t>Infectious Disease</t>
+        </is>
+      </c>
+      <c r="D117" s="2" t="inlineStr">
+        <is>
+          <t>Plasmodium Malaria</t>
+        </is>
+      </c>
+      <c r="E117" s="2" t="inlineStr">
+        <is>
+          <t>Note covers vaccine agents targeting *Plasmodium* malaria prevention in endemic settings. Current corpus references [[rts-s-vaccine]] subunit vaccine plus investigational multi-antigen multi-stage candidates. All claims `pending review`, expert_opinion grade only.</t>
+        </is>
+      </c>
+      <c r="F117" s="2" t="inlineStr"/>
+      <c r="G117" s="2" t="inlineStr"/>
+      <c r="H117" s="2" t="inlineStr">
+        <is>
+          <t>[[rts-s-vaccine]] = recombinant subunit vaccine targeting *P. falciparum* circumsporozoite protein (pre-erythrocytic stage). Induces antibody + T-cell response blocking sporozoite hepatocyte invasion [c:dc33498b] [c:a6845d45] (pending review). Multi-antigen multi-stage candidates target multiple parasite life-cycle stages simultaneously, theoretical edge over single-stage designs [c:0c13ffa9] (pending review).
+```mermaid
+graph LR
+    A[Sporozoite inoculation] --&gt; B[Anti-CSP antibody binding]
+    B --&gt; C[Blocked hepatocyte invasion]
+    C --&gt; D[No blood-stage parasitemia]
+    D --&gt; E[Clinical malaria prevented]
+```
+Cascade supported by [c:dc33498b].</t>
+        </is>
+      </c>
+      <c r="I117" s="2" t="inlineStr"/>
+      <c r="J117" s="2" t="inlineStr"/>
+      <c r="K117" s="2" t="inlineStr">
+        <is>
+          <t>**Therapeutic category:** Antimalarial prophylaxis
+**Drug group:** Malaria vaccine
+**Drug class:** Recombinant protein / multi-antigen subunit vaccine
+**Controlled substance:** No</t>
+        </is>
+      </c>
+      <c r="L117" s="2" t="inlineStr"/>
+      <c r="M117" s="2" t="inlineStr"/>
+      <c r="N117" s="2" t="inlineStr"/>
+      <c r="O117" s="2" t="inlineStr"/>
+      <c r="P117" s="2" t="inlineStr"/>
+      <c r="Q117" s="2" t="inlineStr"/>
+    </row>
+    <row r="118">
+      <c r="A118" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="B118" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="C118" s="2" t="inlineStr">
+        <is>
+          <t>Infectious Disease</t>
+        </is>
+      </c>
+      <c r="D118" s="2" t="inlineStr">
+        <is>
+          <t>Plasmodium Malariae</t>
+        </is>
+      </c>
+      <c r="E118" s="2" t="inlineStr">
+        <is>
+          <t>[[plasmodium-malariae]] is a protozoan parasite causing [[human-malaria]] [c:91506620] [c:f20e4cdb]. Distributed in endemic regions, often co-circulating with [[plasmodium-falciparum]] [c:800e40af] [c:faa1f249] and [[plasmodium-vivax]] [c:c0d51dcc]. Frequently subclinical ("bashful" parasite) [c:eec1071a]. No pharmacologic profile — entity is target organism, not therapeutic agent.</t>
+        </is>
+      </c>
+      <c r="F118" s="2" t="inlineStr"/>
+      <c r="G118" s="2" t="inlineStr"/>
+      <c r="H118" s="2" t="inlineStr">
+        <is>
+          <t>_Not applicable — pathogen, not drug._ Corpus describes disease causation only:
+```mermaid
+graph LR
+    A[P. malariae sporozoite] --&gt; B[hepatic schizogony]
+    B --&gt; C[erythrocytic cycle]
+    C --&gt; D[human malaria infection]
+    D --&gt; E[clinical malaria disease]
+```
+Claim chain: parasite → human malaria infection [c:f20e4cdb] → clinical malaria disease [c:f67b0e2b]. Detailed mechanistic steps not in current claim set.</t>
+        </is>
+      </c>
+      <c r="I118" s="2" t="inlineStr"/>
+      <c r="J118" s="2" t="inlineStr"/>
+      <c r="K118" s="2" t="inlineStr"/>
+      <c r="L118" s="2" t="inlineStr"/>
+      <c r="M118" s="2" t="inlineStr"/>
+      <c r="N118" s="2" t="inlineStr"/>
+      <c r="O118" s="2" t="inlineStr"/>
+      <c r="P118" s="2" t="inlineStr"/>
+      <c r="Q118" s="2" t="inlineStr"/>
+    </row>
+    <row r="119">
+      <c r="A119" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="B119" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="C119" s="2" t="inlineStr">
+        <is>
+          <t>Infectious Disease</t>
+        </is>
+      </c>
+      <c r="D119" s="2" t="inlineStr">
+        <is>
+          <t>Plasmodium Ovale Curtisi</t>
+        </is>
+      </c>
+      <c r="E119" s="2" t="inlineStr">
+        <is>
+          <t>*Plasmodium ovale curtisi* is one of two sympatric *P. ovale* sibling species causing human malaria [c:daed487c] [c:b264f3cc]. Entity is pathogen, not medication — note retained for graph linkage to [[malaria]], [[pyrimethamine]], and [[dhfr-gene]] resistance claims. Drug-style sections below intentionally empty where claim set offers no dose, mechanism, or safety data.</t>
+        </is>
+      </c>
+      <c r="F119" s="2" t="inlineStr"/>
+      <c r="G119" s="2" t="inlineStr"/>
+      <c r="H119" s="2" t="inlineStr">
+        <is>
+          <t>_No mechanism-of-action claims in current corpus._ Resistance mechanism for [[pyrimethamine]] supported:
+```mermaid
+flowchart LR
+  A[DHFR Ala15Ser + Ser58Arg double mutant] --&gt; B[reduced pyrimethamine binding]
+  B --&gt; C[~50-fold IC50 increase vs wild-type DHFR]
+  C --&gt; D[reduced clinical susceptibility, sub-Saharan Africa]
+```
+[c:1d121919] (pending review, expert_opinion grade, E. coli growth assay, sub-Saharan Africa endemic setting)</t>
+        </is>
+      </c>
+      <c r="I119" s="2" t="inlineStr"/>
+      <c r="J119" s="2" t="inlineStr"/>
+      <c r="K119" s="2" t="inlineStr"/>
+      <c r="L119" s="2" t="inlineStr"/>
+      <c r="M119" s="2" t="inlineStr"/>
+      <c r="N119" s="2" t="inlineStr"/>
+      <c r="O119" s="2" t="inlineStr"/>
+      <c r="P119" s="2" t="inlineStr"/>
+      <c r="Q119" s="2" t="inlineStr"/>
+    </row>
+    <row r="120">
+      <c r="A120" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="B120" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="C120" s="2" t="inlineStr">
+        <is>
+          <t>Infectious Disease</t>
+        </is>
+      </c>
+      <c r="D120" s="2" t="inlineStr">
+        <is>
+          <t>Plasmodium Ovale Spp</t>
+        </is>
+      </c>
+      <c r="E120" s="2" t="inlineStr">
+        <is>
+          <t>[[plasmodium-ovale]] spp. is a human malaria parasite, not a therapeutic agent. Classifier flagged it as `medication`; claim set is epidemiological. Co-circulates with [[plasmodium-falciparum]] in [[democratic-republic-of-congo]], causing both asymptomatic and symptomatic infection across age groups [c:4c59fd80] [c:6c7c29a6]. Note below records observed disease burden; no pharmacology applies. Antimalarial management belongs in notes for partner drugs (e.g. [[artemether-lumefantrine]], [[primaquine]]).</t>
+        </is>
+      </c>
+      <c r="F120" s="2" t="inlineStr"/>
+      <c r="G120" s="2" t="inlineStr"/>
+      <c r="H120" s="2" t="inlineStr">
+        <is>
+          <t>_Not applicable — no mechanism-of-action claims for a therapeutic agent._ Epidemiological co-occurrence only:
+- Co-occurs with [[plasmodium-falciparum]] in DRC community settings [c:b8bb34f8] (pending review).
+- Co-occurs with P. falciparum infection in Kinshasa school-age children [c:6c7c29a6] (pending review).
+```mermaid
+flowchart LR
+  Pov[P. ovale spp.] --&gt;|co-infection| Pf[P. falciparum]
+  Pov --&gt; Asym[Asymptomatic carriage 1%]
+  Pov --&gt; Sym[Symptomatic malaria 4.8–7%/yr]
+  Sym --&gt; SAC[School-age children 15%/2yr]
+```</t>
+        </is>
+      </c>
+      <c r="I120" s="2" t="inlineStr"/>
+      <c r="J120" s="2" t="inlineStr"/>
+      <c r="K120" s="2" t="inlineStr"/>
+      <c r="L120" s="2" t="inlineStr"/>
+      <c r="M120" s="2" t="inlineStr"/>
+      <c r="N120" s="2" t="inlineStr"/>
+      <c r="O120" s="2" t="inlineStr"/>
+      <c r="P120" s="2" t="inlineStr"/>
+      <c r="Q120" s="2" t="inlineStr"/>
+    </row>
+    <row r="121">
+      <c r="A121" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="B121" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="C121" s="2" t="inlineStr">
+        <is>
+          <t>Infectious Disease</t>
+        </is>
+      </c>
+      <c r="D121" s="2" t="inlineStr">
+        <is>
+          <t>Plasmodium Ovale Wallickeri</t>
+        </is>
+      </c>
+      <c r="E121" s="2" t="inlineStr">
+        <is>
+          <t>Plasmodium ovale wallickeri is a human malaria parasite (one of two sister species in the P. ovale complex), not a therapeutic agent. Current claim set describes it as causative agent of [[human-malaria-infection]] and [[clinical-malaria-disease]] [c:2d0c2e94] (pending review) [c:16a1b885] (pending review). Note generated under `medication` template due to upstream classifier mismatch; content reframed as etiologic agent.</t>
+        </is>
+      </c>
+      <c r="F121" s="2" t="inlineStr"/>
+      <c r="G121" s="2" t="inlineStr"/>
+      <c r="H121" s="2" t="inlineStr">
+        <is>
+          <t>_No mechanism-of-action claims in current corpus._ Pathogenesis claims limited to causation of malaria infection and clinical disease [c:2d0c2e94][c:16a1b885]; molecular/cellular steps (hepatocyte invasion, erythrocytic cycle, hypnozoite dormancy) absent from claim set.</t>
+        </is>
+      </c>
+      <c r="I121" s="2" t="inlineStr"/>
+      <c r="J121" s="2" t="inlineStr"/>
+      <c r="K121" s="2" t="inlineStr"/>
+      <c r="L121" s="2" t="inlineStr"/>
+      <c r="M121" s="2" t="inlineStr"/>
+      <c r="N121" s="2" t="inlineStr"/>
+      <c r="O121" s="2" t="inlineStr"/>
+      <c r="P121" s="2" t="inlineStr"/>
+      <c r="Q121" s="2" t="inlineStr"/>
+    </row>
+    <row r="122">
+      <c r="A122" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="B122" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="C122" s="2" t="inlineStr">
+        <is>
+          <t>Infectious Disease</t>
+        </is>
+      </c>
+      <c r="D122" s="2" t="inlineStr">
+        <is>
+          <t>Plasmodium Ovale</t>
+        </is>
+      </c>
+      <c r="E122" s="2" t="inlineStr">
+        <is>
+          <t>Plasmodium ovale is a human malaria parasite [c:a80fd411] causing [[malaria]] in endemic settings [c:bba1d3b2]. Current claim corpus classifies it as a pathogen, not a medication. No pharmacologic claims (mechanism, dose, contraindication, interaction) exist. Note retained in medication schema per pipeline contract but every drug-specific field is null. For treatment of P. ovale infection, see notes on [[chloroquine]], [[artemisinin-combination-therapy]], and [[primaquine]] (radical cure of hypnozoites) — sourced from separate claim sets.</t>
+        </is>
+      </c>
+      <c r="F122" s="2" t="inlineStr"/>
+      <c r="G122" s="2" t="inlineStr"/>
+      <c r="H122" s="2" t="inlineStr">
+        <is>
+          <t>_No mechanism-of-action claims in current corpus._ P. ovale is a pathogen; "mechanism" would describe pathogenesis (hepatocyte infection, erythrocytic schizogony, hypnozoite dormancy) — not represented in current claims.</t>
+        </is>
+      </c>
+      <c r="I122" s="2" t="inlineStr"/>
+      <c r="J122" s="2" t="inlineStr"/>
+      <c r="K122" s="2" t="inlineStr"/>
+      <c r="L122" s="2" t="inlineStr"/>
+      <c r="M122" s="2" t="inlineStr"/>
+      <c r="N122" s="2" t="inlineStr"/>
+      <c r="O122" s="2" t="inlineStr"/>
+      <c r="P122" s="2" t="inlineStr"/>
+      <c r="Q122" s="2" t="inlineStr"/>
+    </row>
+    <row r="123">
+      <c r="A123" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="B123" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="C123" s="2" t="inlineStr">
+        <is>
+          <t>Infectious Disease</t>
+        </is>
+      </c>
+      <c r="D123" s="2" t="inlineStr">
+        <is>
+          <t>Plasmodium Parasite Prevalence</t>
+        </is>
+      </c>
+      <c r="E123" s="2" t="inlineStr">
+        <is>
+          <t>Indoor residual spraying applies long-acting insecticide to interior wall surfaces of dwellings to kill resting *Anopheles* mosquitoes. Deployed adjunct to [[insecticide-treated-nets]] in [[sub-saharan-africa]] for [[falciparum-malaria]] control. Efficacy on [[plasmodium-parasite-prevalence]] depends on chemical class and local pyrethroid-resistance status.</t>
+        </is>
+      </c>
+      <c r="F123" s="2" t="inlineStr"/>
+      <c r="G123" s="2" t="inlineStr"/>
+      <c r="H123" s="2" t="inlineStr">
+        <is>
+          <t>Contact neurotoxicity on resting adult *Anopheles*. Pyrethroid-likes ([[ddt]], [[deltamethrin]]) — sodium-channel modulators; cross-resistance with ITN pyrethroids blunts marginal effect when ITNs present [c:dcd2688e]. Non-pyrethroid-likes ([[bendiocarb]], [[pirimiphos-methyl]], [[propoxur]]) — acetylcholinesterase inhibitors; distinct target site bypasses pyrethroid resistance, restoring vector kill on top of ITNs [c:b8dc9e27].
+```mermaid
+flowchart LR
+  A[Non-pyrethroid IRS on walls] --&gt; B[AChE inhibition in resting Anopheles]
+  B --&gt; C[Vector mortality + reduced biting]
+  C --&gt; D[↓ Plasmodium parasite prevalence vs ITNs alone]
+```
+Mechanism-to-outcome chain supported by [c:b8dc9e27].</t>
+        </is>
+      </c>
+      <c r="I123" s="2" t="inlineStr"/>
+      <c r="J123" s="2" t="inlineStr"/>
+      <c r="K123" s="2" t="inlineStr"/>
+      <c r="L123" s="2" t="inlineStr"/>
+      <c r="M123" s="2" t="inlineStr"/>
+      <c r="N123" s="2" t="inlineStr"/>
+      <c r="O123" s="2" t="inlineStr"/>
+      <c r="P123" s="2" t="inlineStr"/>
+      <c r="Q123" s="2" t="inlineStr"/>
+    </row>
+    <row r="124">
+      <c r="A124" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="B124" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="C124" s="2" t="inlineStr">
+        <is>
+          <t>Infectious Disease</t>
+        </is>
+      </c>
+      <c r="D124" s="2" t="inlineStr">
+        <is>
+          <t>Plasmodium Parasites</t>
+        </is>
+      </c>
+      <c r="E124" s="2" t="inlineStr">
+        <is>
+          <t>Plasmodium parasites are protozoan organisms that cause [[malaria]] in humans [c:960c7e26] (pending review) [c:c2024dda] (pending review). This entity is a pathogen and target of antimalarial therapy — not a medication itself. For therapeutic agents directed against Plasmodium, see [[artemether-lumefantrine]], [[artesunate]], [[chloroquine]], [[primaquine]].</t>
+        </is>
+      </c>
+      <c r="F124" s="2" t="inlineStr"/>
+      <c r="G124" s="2" t="inlineStr"/>
+      <c r="H124" s="2" t="inlineStr">
+        <is>
+          <t>_No mechanism-of-action claims in current corpus. Current claims establish etiologic role only: Plasmodium parasites cause malaria [c:960c7e26] (pending review) [c:c2024dda] (pending review)._</t>
+        </is>
+      </c>
+      <c r="I124" s="2" t="inlineStr"/>
+      <c r="J124" s="2" t="inlineStr"/>
+      <c r="K124" s="2" t="inlineStr"/>
+      <c r="L124" s="2" t="inlineStr"/>
+      <c r="M124" s="2" t="inlineStr"/>
+      <c r="N124" s="2" t="inlineStr"/>
+      <c r="O124" s="2" t="inlineStr"/>
+      <c r="P124" s="2" t="inlineStr"/>
+      <c r="Q124" s="2" t="inlineStr"/>
+    </row>
+    <row r="125">
+      <c r="A125" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="B125" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="C125" s="2" t="inlineStr">
+        <is>
+          <t>Infectious Disease</t>
+        </is>
+      </c>
+      <c r="D125" s="2" t="inlineStr">
+        <is>
+          <t>Plasmodium Vivax Hypnozoite</t>
+        </is>
+      </c>
+      <c r="E125" s="2" t="inlineStr">
+        <is>
+          <t>Dormant intrahepatic form of [[plasmodium-vivax]]. Persists in hepatocytes after primary infection and reactivates weeks–months later, driving [[relapsing-malaria]] [c:3bb0703e]. Refractory to most schizonticidal antimalarials [c:c1317ee2]; clearance ("radical cure") requires 8-aminoquinoline therapy.</t>
+        </is>
+      </c>
+      <c r="F125" s="2" t="inlineStr"/>
+      <c r="G125" s="2" t="inlineStr"/>
+      <c r="H125" s="2" t="inlineStr">
+        <is>
+          <t>Hypnozoite biology — not pharmacology. Anti-hypnozoite agents ([[tafenoquine]], [[primaquine]]) act via 8-aminoquinoline-mediated oxidative damage on liver-stage parasites; hypnozoite itself evades blood-schizonticides [c:c1317ee2].
+```mermaid
+graph LR
+  A[Sporozoite inoculation] --&gt; B[Hepatocyte invasion]
+  B --&gt; C[Dormant hypnozoite]
+  C --&gt;|weeks–months| D[Reactivation → merozoites]
+  D --&gt; E[Blood-stage relapse]
+  C -.resists.-&gt; F[Blood schizonticides]
+  G[8-aminoquinoline] -.clears.-&gt; C
+```
+Cascade supported by [c:c1317ee2] [c:3bb0703e].</t>
+        </is>
+      </c>
+      <c r="I125" s="2" t="inlineStr"/>
+      <c r="J125" s="2" t="inlineStr"/>
+      <c r="K125" s="2" t="inlineStr"/>
+      <c r="L125" s="2" t="inlineStr"/>
+      <c r="M125" s="2" t="inlineStr"/>
+      <c r="N125" s="2" t="inlineStr"/>
+      <c r="O125" s="2" t="inlineStr"/>
+      <c r="P125" s="2" t="inlineStr"/>
+      <c r="Q125" s="2" t="inlineStr"/>
+    </row>
+    <row r="126">
+      <c r="A126" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="B126" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="C126" s="2" t="inlineStr">
+        <is>
+          <t>Infectious Disease</t>
+        </is>
+      </c>
+      <c r="D126" s="2" t="inlineStr">
+        <is>
+          <t>Plasmodium Vivax Hypnozoites</t>
+        </is>
+      </c>
+      <c r="E126" s="2" t="inlineStr">
+        <is>
+          <t>Hypnozoites are dormant liver-stage forms of [[plasmodium-vivax]] that cause relapsing vivax malaria in endemic settings [c:97bc41e7] (pending review). They are a **drug target**, not a drug. Current claim corpus describes agents acting against them: [[primaquine]] [c:e7a14608] and the broader [[8-aminoquinolines]] class [c:e637b70b].</t>
+        </is>
+      </c>
+      <c r="F126" s="2" t="inlineStr"/>
+      <c r="G126" s="2" t="inlineStr"/>
+      <c r="H126" s="2" t="inlineStr">
+        <is>
+          <t>_Not applicable._ Mechanism of action belongs to the killing agents, not the target. Claim set supports drug→target relationship only:
+```mermaid
+flowchart LR
+  A[primaquine / 8-aminoquinolines] --&gt;|kills| B[P. vivax hypnozoites]
+  B --&gt;|reactivation| C[relapsing vivax malaria]
+```
+[c:e7a14608] [c:e637b70b] [c:97bc41e7] (all pending review; evidence_grade: expert_opinion).</t>
+        </is>
+      </c>
+      <c r="I126" s="2" t="inlineStr"/>
+      <c r="J126" s="2" t="inlineStr"/>
+      <c r="K126" s="2" t="inlineStr"/>
+      <c r="L126" s="2" t="inlineStr"/>
+      <c r="M126" s="2" t="inlineStr"/>
+      <c r="N126" s="2" t="inlineStr"/>
+      <c r="O126" s="2" t="inlineStr"/>
+      <c r="P126" s="2" t="inlineStr"/>
+      <c r="Q126" s="2" t="inlineStr"/>
+    </row>
+    <row r="127">
+      <c r="A127" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="B127" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="C127" s="2" t="inlineStr">
+        <is>
+          <t>Infectious Disease</t>
+        </is>
+      </c>
+      <c r="D127" s="2" t="inlineStr">
+        <is>
+          <t>Plasmodium Vivax Infection</t>
+        </is>
+      </c>
+      <c r="E127" s="2" t="inlineStr">
+        <is>
+          <t>[[plasmodium-vivax-infection]] is a protozoal malaria caused by *Plasmodium vivax*. Entity flagged as `medication` but corpus contains only disease-course claims, not therapeutic agent data. Surfaced claims describe complications, not pharmacotherapy.</t>
+        </is>
+      </c>
+      <c r="F127" s="2" t="inlineStr"/>
+      <c r="G127" s="2" t="inlineStr"/>
+      <c r="H127" s="2" t="inlineStr">
+        <is>
+          <t>_No mechanism claims in current corpus._</t>
+        </is>
+      </c>
+      <c r="I127" s="2" t="inlineStr"/>
+      <c r="J127" s="2" t="inlineStr"/>
+      <c r="K127" s="2" t="inlineStr"/>
+      <c r="L127" s="2" t="inlineStr"/>
+      <c r="M127" s="2" t="inlineStr"/>
+      <c r="N127" s="2" t="inlineStr"/>
+      <c r="O127" s="2" t="inlineStr"/>
+      <c r="P127" s="2" t="inlineStr"/>
+      <c r="Q127" s="2" t="inlineStr"/>
+    </row>
+    <row r="128">
+      <c r="A128" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="B128" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="C128" s="2" t="inlineStr">
+        <is>
+          <t>Infectious Disease</t>
+        </is>
+      </c>
+      <c r="D128" s="2" t="inlineStr">
+        <is>
+          <t>Plasmodium Vivax</t>
+        </is>
+      </c>
+      <c r="E128" s="2" t="inlineStr">
+        <is>
+          <t>Plasmodium vivax is a human malaria parasite, second leading global cause of malaria and dominant species outside Africa [c:c7f61af5][c:eda535c4]. Caused ~12.4 M clinical cases in 2022 (CI 10.7–14.8 M) [c:9ce5aeea] and ~2.8% of global malaria cases in 2019 [c:931b8553], with ~2.5 B people at risk [c:5ccb9556]. Distinct from [[plasmodium-falciparum]] via dormant liver-stage hypnozoites driving relapse [c:84748987][c:611d742a].</t>
+        </is>
+      </c>
+      <c r="F128" s="2" t="inlineStr"/>
+      <c r="G128" s="2" t="inlineStr"/>
+      <c r="H128" s="2" t="inlineStr">
+        <is>
+          <t>_Not pharmacologic._ Pathogenesis cascade:
+```mermaid
+graph LR
+    A[Sporozoite inoculation] --&gt; B[Liver hepatocyte invasion]
+    B --&gt; C[Schizont — acute blood stage]
+    B --&gt; D[Hypnozoite — dormant liver stage]
+    D --&gt; E[Reactivation]
+    E --&gt; C
+    C --&gt; F[Erythrocytic cycle]
+    F --&gt; G[Clinical malaria: fever, anemia, coma]
+    F --&gt; H[Gametocyte — mosquito transmission]
+```
+Lifecycle stages: gametocyte [c:8ea029a7], dormant liver-stage hypnozoite [c:84748987]. Hypnozoite reservoir → relapse [c:611d742a] and superinfection (multiple concurrent blood-stage clones) [c:e8023336]. Same-clone recurrent parasitemia documented at 23.9% in twice-sampled [[guyana]] patients [c:47a16126]. Polyclonality ~2.1× P. falciparum in sympatric setting [c:d2e1aa34]. Local relapse without recent endemic travel — 11% of P. vivax patients in Greater Georgetown [c:05a2e5c3].</t>
+        </is>
+      </c>
+      <c r="I128" s="2" t="inlineStr"/>
+      <c r="J128" s="2" t="inlineStr"/>
+      <c r="K128" s="2" t="inlineStr"/>
+      <c r="L128" s="2" t="inlineStr"/>
+      <c r="M128" s="2" t="inlineStr"/>
+      <c r="N128" s="2" t="inlineStr"/>
+      <c r="O128" s="2" t="inlineStr"/>
+      <c r="P128" s="2" t="inlineStr"/>
+      <c r="Q128" s="2" t="inlineStr"/>
+    </row>
+    <row r="129">
+      <c r="A129" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="B129" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="C129" s="2" t="inlineStr">
+        <is>
+          <t>Infectious Disease</t>
+        </is>
+      </c>
+      <c r="D129" s="2" t="inlineStr">
+        <is>
+          <t>Plasmodium</t>
+        </is>
+      </c>
+      <c r="E129" s="2" t="inlineStr">
+        <is>
+          <t>Plasmodium = protozoan intracellular parasite causing human malaria [c:e94c6ad7][c:ce7540a2][c:c42ef453]. Affects red blood cells [c:472ff9fc]. ~240 million annual cases globally [c:c9ad9ecd], ~500,000 annual deaths worldwide [c:a131b5d2], 438,000 deaths/yr in endemic areas [c:1a33d1bf], 429,000 deaths/yr in children &lt;5 (2015) [c:44076d58]. Entity belongs in pathogen sheet, not Medications. _Note: classifier hint flagged this as `medication` — likely mislabeled. Treat downstream as organism record._</t>
+        </is>
+      </c>
+      <c r="F129" s="2" t="inlineStr"/>
+      <c r="G129" s="2" t="inlineStr"/>
+      <c r="H129" s="2" t="inlineStr">
+        <is>
+          <t>Plasmodium is the disease-causing agent, not a drug. Lifecycle stages relevant to drug targeting: sporozoite [c:06586eb0], merozoite [c:216e82ba], gametocyte [c:22b09015]. Parasite requires host cell egress for life cycle completion [c:b5cf2484]. Invades [[red-blood-cells]] during blood stage [c:472ff9fc].
+```mermaid
+flowchart LR
+  A[Sporozoite&lt;br/&gt;mosquito inoculation] --&gt; B[Liver hepatocyte stage]
+  B --&gt; C[Merozoite&lt;br/&gt;RBC invasion]
+  C --&gt; D[Asexual blood-stage&lt;br/&gt;cycle + egress]
+  D --&gt; E[Gametocyte&lt;br/&gt;transmission stage]
+  D --&gt; F[Clinical malaria&lt;br/&gt;anemia / cerebral]
+```
+Egress across stages = pan-lifecycle drug target [c:b5cf2484][c:06586eb0][c:216e82ba][c:22b09015].</t>
+        </is>
+      </c>
+      <c r="I129" s="2" t="inlineStr"/>
+      <c r="J129" s="2" t="inlineStr"/>
+      <c r="K129" s="2" t="inlineStr"/>
+      <c r="L129" s="2" t="inlineStr"/>
+      <c r="M129" s="2" t="inlineStr"/>
+      <c r="N129" s="2" t="inlineStr"/>
+      <c r="O129" s="2" t="inlineStr"/>
+      <c r="P129" s="2" t="inlineStr"/>
+      <c r="Q129" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
